--- a/cocktail_source.xlsx
+++ b/cocktail_source.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\06GBA\OneDrive - Bain\Documents\GitHub\Gregs Bar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bainandcompany-my.sharepoint.com/personal/gregoire_baudry_bain_com/Documents/Documents/GitHub/Greg's Bar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55666991-13C5-43F9-9A70-97D3BDF1EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{55666991-13C5-43F9-9A70-97D3BDF1EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B509AAA-35B8-4D19-BA96-4EBAC9316F9E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="1039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="1040">
   <si>
     <t>Abbey</t>
   </si>
@@ -1658,16 +1658,6 @@
     <t>Michelada</t>
   </si>
   <si>
-    <t>Cayenne Pepper
-Salt
-Lime Juice – 15 ml
-Hot Sauce – 2 drop
-Worcestershire Sauce – 2 dash
-Black Pepper – 1 pinch
-Celery Salt – 1 pinch
-Lime – 1 wedge</t>
-  </si>
-  <si>
     <t>Michelada.jpg</t>
   </si>
   <si>
@@ -3893,14 +3883,29 @@
   <si>
     <t>Total Quantity</t>
   </si>
+  <si>
+    <t>Alcohol Content (ml)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Beer– 360 ml
+Cayenne Pepper
+Salt
+Lime Juice – 15 ml
+Hot Sauce – 2 drop
+Worcestershire Sauce – 2 dash
+Black Pepper – 1 pinch
+Celery Salt – 1 pinch
+Lime – 1 wedge</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.#"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -3958,7 +3963,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3979,6 +3984,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E2F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4013,7 +4024,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4027,7 +4038,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -4039,6 +4049,10 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4232,7 +4246,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="3">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -4244,7 +4258,9 @@
   <we:alternateReferences>
     <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
   </we:alternateReferences>
-  <we:properties/>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;44f09ac1-a6f9-4671-a0ee-b81fce7a7e7e&quot;"/>
+  </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </we:webextension>
@@ -4260,23 +4276,27 @@
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>876</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>879</v>
+      <c r="F1" s="17" t="s">
+        <v>1038</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="75" x14ac:dyDescent="0.25">
@@ -4284,7 +4304,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -4295,14 +4315,16 @@
       <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="5"/>
+      <c r="F2" s="16">
+        <v>21.4</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
@@ -4313,7 +4335,9 @@
       <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="F3" s="16">
+        <v>30.4</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -4331,14 +4355,16 @@
       <c r="E4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="5"/>
+      <c r="F4" s="16">
+        <v>10.9</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
@@ -4349,14 +4375,16 @@
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="16">
+        <v>42</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>14</v>
@@ -4367,14 +4395,16 @@
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="5"/>
+      <c r="F6" s="16">
+        <v>27.5</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
@@ -4385,14 +4415,16 @@
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="5"/>
+      <c r="F7" s="16">
+        <v>30</v>
+      </c>
     </row>
     <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
@@ -4403,14 +4435,16 @@
       <c r="E8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F8" s="5"/>
+      <c r="F8" s="16">
+        <v>16.600000000000001</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>23</v>
@@ -4421,14 +4455,16 @@
       <c r="E9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="5"/>
+      <c r="F9" s="16">
+        <v>29.4</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>26</v>
@@ -4439,14 +4475,16 @@
       <c r="E10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="5"/>
+      <c r="F10" s="16">
+        <v>16.8</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>29</v>
@@ -4457,14 +4495,16 @@
       <c r="E11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="5"/>
+      <c r="F11" s="16">
+        <v>36</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
@@ -4475,14 +4515,16 @@
       <c r="E12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="5"/>
+      <c r="F12" s="16">
+        <v>30</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>35</v>
@@ -4493,14 +4535,16 @@
       <c r="E13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="5"/>
+      <c r="F13" s="16">
+        <v>18.5</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>38</v>
@@ -4511,14 +4555,16 @@
       <c r="E14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="5"/>
+      <c r="F14" s="16">
+        <v>13.4</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>41</v>
@@ -4529,14 +4575,16 @@
       <c r="E15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="5"/>
+      <c r="F15" s="16">
+        <v>33</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>44</v>
@@ -4547,14 +4595,16 @@
       <c r="E16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F16" s="5"/>
+      <c r="F16" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>47</v>
@@ -4565,14 +4615,16 @@
       <c r="E17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F17" s="5"/>
+      <c r="F17" s="16">
+        <v>20</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>50</v>
@@ -4583,14 +4635,16 @@
       <c r="E18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="5"/>
+      <c r="F18" s="16">
+        <v>15</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>53</v>
@@ -4601,57 +4655,68 @@
       <c r="E19" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="5"/>
+      <c r="F19" s="16">
+        <v>15</v>
+      </c>
     </row>
     <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="B20" t="s">
+        <v>868</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>862</v>
-      </c>
-      <c r="B20" t="s">
-        <v>869</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>863</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
+      </c>
+      <c r="F20" s="16">
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>859</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>868</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>860</v>
       </c>
       <c r="D21" s="3">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
+      </c>
+      <c r="F21" s="16">
+        <v>26.4</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>851</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>857</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>852</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
+      </c>
+      <c r="F22" s="16">
+        <v>18.600000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -4659,7 +4724,7 @@
         <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>56</v>
@@ -4670,23 +4735,28 @@
       <c r="E23" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="5"/>
+      <c r="F23" s="16">
+        <v>15.6</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
+      </c>
+      <c r="F24" s="16">
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -4694,7 +4764,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>59</v>
@@ -4705,14 +4775,16 @@
       <c r="E25" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F25" s="5"/>
+      <c r="F25" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>62</v>
@@ -4723,14 +4795,16 @@
       <c r="E26" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="F26" s="5"/>
+      <c r="F26" s="16">
+        <v>24.5</v>
+      </c>
     </row>
     <row r="27" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>65</v>
@@ -4741,14 +4815,16 @@
       <c r="E27" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F27" s="5"/>
+      <c r="F27" s="16">
+        <v>23.1</v>
+      </c>
     </row>
     <row r="28" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>68</v>
@@ -4759,14 +4835,16 @@
       <c r="E28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F28" s="5"/>
+      <c r="F28" s="16">
+        <v>30</v>
+      </c>
     </row>
     <row r="29" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>71</v>
@@ -4777,14 +4855,16 @@
       <c r="E29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F29" s="5"/>
+      <c r="F29" s="16">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="30" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>73</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>74</v>
@@ -4795,14 +4875,16 @@
       <c r="E30" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F30" s="5"/>
+      <c r="F30" s="16">
+        <v>23.8</v>
+      </c>
     </row>
     <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>77</v>
@@ -4813,14 +4895,16 @@
       <c r="E31" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F31" s="5"/>
+      <c r="F31" s="16">
+        <v>5</v>
+      </c>
     </row>
     <row r="32" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>79</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>80</v>
@@ -4831,14 +4915,16 @@
       <c r="E32" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F32" s="5"/>
+      <c r="F32" s="16">
+        <v>30</v>
+      </c>
     </row>
     <row r="33" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>82</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>83</v>
@@ -4849,14 +4935,16 @@
       <c r="E33" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F33" s="5"/>
+      <c r="F33" s="16">
+        <v>28.8</v>
+      </c>
     </row>
     <row r="34" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>85</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>86</v>
@@ -4867,14 +4955,16 @@
       <c r="E34" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F34" s="5"/>
+      <c r="F34" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="35" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>88</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>89</v>
@@ -4885,14 +4975,16 @@
       <c r="E35" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F35" s="5"/>
+      <c r="F35" s="16">
+        <v>20.3</v>
+      </c>
     </row>
     <row r="36" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>91</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>92</v>
@@ -4903,14 +4995,16 @@
       <c r="E36" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F36" s="5"/>
+      <c r="F36" s="16">
+        <v>27.2</v>
+      </c>
     </row>
     <row r="37" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>94</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>95</v>
@@ -4921,14 +5015,16 @@
       <c r="E37" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F37" s="5"/>
+      <c r="F37" s="16">
+        <v>12.6</v>
+      </c>
     </row>
     <row r="38" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>97</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>98</v>
@@ -4939,14 +5035,16 @@
       <c r="E38" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F38" s="5"/>
+      <c r="F38" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="39" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>100</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>101</v>
@@ -4957,14 +5055,16 @@
       <c r="E39" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F39" s="5"/>
+      <c r="F39" s="16">
+        <v>30.3</v>
+      </c>
     </row>
     <row r="40" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>103</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>104</v>
@@ -4975,14 +5075,16 @@
       <c r="E40" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F40" s="5"/>
+      <c r="F40" s="16">
+        <v>30.3</v>
+      </c>
     </row>
     <row r="41" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>107</v>
@@ -4993,14 +5095,16 @@
       <c r="E41" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F41" s="5"/>
+      <c r="F41" s="16">
+        <v>31.4</v>
+      </c>
     </row>
     <row r="42" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>109</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>110</v>
@@ -5011,14 +5115,16 @@
       <c r="E42" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F42" s="5"/>
+      <c r="F42" s="16">
+        <v>25.5</v>
+      </c>
     </row>
     <row r="43" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>113</v>
@@ -5029,14 +5135,16 @@
       <c r="E43" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F43" s="5"/>
+      <c r="F43" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="44" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>115</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>116</v>
@@ -5047,14 +5155,16 @@
       <c r="E44" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F44" s="5"/>
+      <c r="F44" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="45" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>119</v>
@@ -5065,14 +5175,16 @@
       <c r="E45" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F45" s="5"/>
+      <c r="F45" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="46" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>121</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>122</v>
@@ -5083,14 +5195,16 @@
       <c r="E46" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="F46" s="5"/>
+      <c r="F46" s="16">
+        <v>29.1</v>
+      </c>
     </row>
     <row r="47" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>124</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>125</v>
@@ -5101,14 +5215,16 @@
       <c r="E47" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F47" s="5"/>
+      <c r="F47" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="48" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>128</v>
@@ -5119,14 +5235,16 @@
       <c r="E48" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F48" s="5"/>
+      <c r="F48" s="16">
+        <v>15.8</v>
+      </c>
     </row>
     <row r="49" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>131</v>
@@ -5137,14 +5255,16 @@
       <c r="E49" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F49" s="5"/>
+      <c r="F49" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="50" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>133</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>134</v>
@@ -5155,14 +5275,16 @@
       <c r="E50" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F50" s="5"/>
+      <c r="F50" s="16">
+        <v>33</v>
+      </c>
     </row>
     <row r="51" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>137</v>
@@ -5173,14 +5295,16 @@
       <c r="E51" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F51" s="5"/>
+      <c r="F51" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="52" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>140</v>
@@ -5191,14 +5315,16 @@
       <c r="E52" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F52" s="5"/>
+      <c r="F52" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="53" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>142</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>143</v>
@@ -5209,14 +5335,16 @@
       <c r="E53" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F53" s="5"/>
+      <c r="F53" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="54" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>145</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>146</v>
@@ -5227,14 +5355,16 @@
       <c r="E54" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F54" s="5"/>
+      <c r="F54" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="55" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>148</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>149</v>
@@ -5245,14 +5375,16 @@
       <c r="E55" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F55" s="5"/>
+      <c r="F55" s="16">
+        <v>31.2</v>
+      </c>
     </row>
     <row r="56" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>151</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>152</v>
@@ -5263,14 +5395,16 @@
       <c r="E56" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F56" s="5"/>
+      <c r="F56" s="16">
+        <v>15</v>
+      </c>
     </row>
     <row r="57" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>154</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>155</v>
@@ -5281,14 +5415,16 @@
       <c r="E57" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F57" s="5"/>
+      <c r="F57" s="16">
+        <v>26.8</v>
+      </c>
     </row>
     <row r="58" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>157</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>158</v>
@@ -5299,14 +5435,16 @@
       <c r="E58" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F58" s="5"/>
+      <c r="F58" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="59" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>160</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>161</v>
@@ -5317,14 +5455,16 @@
       <c r="E59" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="F59" s="5"/>
+      <c r="F59" s="16">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="60" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>163</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>164</v>
@@ -5335,14 +5475,16 @@
       <c r="E60" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F60" s="5"/>
+      <c r="F60" s="16">
+        <v>26.1</v>
+      </c>
     </row>
     <row r="61" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>166</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>167</v>
@@ -5353,14 +5495,16 @@
       <c r="E61" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F61" s="5"/>
+      <c r="F61" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="62" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>169</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>170</v>
@@ -5371,14 +5515,16 @@
       <c r="E62" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="F62" s="5"/>
+      <c r="F62" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="63" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>172</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>173</v>
@@ -5389,14 +5535,16 @@
       <c r="E63" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F63" s="5"/>
+      <c r="F63" s="16">
+        <v>27</v>
+      </c>
     </row>
     <row r="64" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>175</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>176</v>
@@ -5407,14 +5555,16 @@
       <c r="E64" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F64" s="5"/>
+      <c r="F64" s="16">
+        <v>16.8</v>
+      </c>
     </row>
     <row r="65" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>178</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>179</v>
@@ -5425,14 +5575,16 @@
       <c r="E65" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F65" s="5"/>
+      <c r="F65" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="66" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>181</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>182</v>
@@ -5443,14 +5595,16 @@
       <c r="E66" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F66" s="5"/>
+      <c r="F66" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="67" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>184</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>185</v>
@@ -5461,14 +5615,16 @@
       <c r="E67" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F67" s="5"/>
+      <c r="F67" s="16">
+        <v>19.399999999999999</v>
+      </c>
     </row>
     <row r="68" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>187</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>188</v>
@@ -5479,14 +5635,16 @@
       <c r="E68" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F68" s="5"/>
+      <c r="F68" s="16">
+        <v>30</v>
+      </c>
     </row>
     <row r="69" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>190</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>191</v>
@@ -5497,14 +5655,16 @@
       <c r="E69" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="F69" s="5"/>
+      <c r="F69" s="16">
+        <v>27</v>
+      </c>
     </row>
     <row r="70" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>193</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>194</v>
@@ -5515,14 +5675,16 @@
       <c r="E70" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F70" s="5"/>
+      <c r="F70" s="16">
+        <v>16.899999999999999</v>
+      </c>
     </row>
     <row r="71" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>196</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>197</v>
@@ -5533,14 +5695,16 @@
       <c r="E71" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="F71" s="5"/>
+      <c r="F71" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>199</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>200</v>
@@ -5551,14 +5715,16 @@
       <c r="E72" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F72" s="5"/>
+      <c r="F72" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="73" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>202</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>203</v>
@@ -5569,14 +5735,16 @@
       <c r="E73" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="F73" s="5"/>
+      <c r="F73" s="16">
+        <v>16.399999999999999</v>
+      </c>
     </row>
     <row r="74" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>205</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>206</v>
@@ -5587,14 +5755,16 @@
       <c r="E74" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="F74" s="5"/>
+      <c r="F74" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="75" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>208</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>209</v>
@@ -5605,7 +5775,9 @@
       <c r="E75" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F75" s="5"/>
+      <c r="F75" s="16">
+        <v>31.6</v>
+      </c>
     </row>
     <row r="76" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
@@ -5623,14 +5795,16 @@
       <c r="E76" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="F76" s="5"/>
+      <c r="F76" s="16">
+        <v>18.899999999999999</v>
+      </c>
     </row>
     <row r="77" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>215</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>216</v>
@@ -5641,14 +5815,16 @@
       <c r="E77" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F77" s="5"/>
+      <c r="F77" s="16">
+        <v>34</v>
+      </c>
     </row>
     <row r="78" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>218</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>219</v>
@@ -5659,14 +5835,16 @@
       <c r="E78" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="F78" s="5"/>
+      <c r="F78" s="16">
+        <v>15.3</v>
+      </c>
     </row>
     <row r="79" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>221</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>222</v>
@@ -5677,14 +5855,16 @@
       <c r="E79" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="F79" s="5"/>
+      <c r="F79" s="16">
+        <v>19</v>
+      </c>
     </row>
     <row r="80" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>224</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>225</v>
@@ -5695,14 +5875,16 @@
       <c r="E80" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="F80" s="5"/>
+      <c r="F80" s="16">
+        <v>35.4</v>
+      </c>
     </row>
     <row r="81" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>227</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>228</v>
@@ -5713,14 +5895,16 @@
       <c r="E81" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F81" s="5"/>
+      <c r="F81" s="16">
+        <v>24.5</v>
+      </c>
     </row>
     <row r="82" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>230</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>231</v>
@@ -5731,14 +5915,16 @@
       <c r="E82" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="F82" s="5"/>
+      <c r="F82" s="16">
+        <v>20</v>
+      </c>
     </row>
     <row r="83" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>233</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>234</v>
@@ -5749,14 +5935,16 @@
       <c r="E83" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="F83" s="5"/>
+      <c r="F83" s="16">
+        <v>30</v>
+      </c>
     </row>
     <row r="84" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>236</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>237</v>
@@ -5767,14 +5955,16 @@
       <c r="E84" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="F84" s="5"/>
+      <c r="F84" s="16">
+        <v>30</v>
+      </c>
     </row>
     <row r="85" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>239</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>240</v>
@@ -5785,14 +5975,16 @@
       <c r="E85" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="F85" s="5"/>
+      <c r="F85" s="16">
+        <v>28.8</v>
+      </c>
     </row>
     <row r="86" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>242</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>243</v>
@@ -5803,14 +5995,16 @@
       <c r="E86" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="F86" s="5"/>
+      <c r="F86" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="87" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>245</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>246</v>
@@ -5821,14 +6015,16 @@
       <c r="E87" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F87" s="5"/>
+      <c r="F87" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="88" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>248</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>249</v>
@@ -5839,14 +6035,16 @@
       <c r="E88" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F88" s="5"/>
+      <c r="F88" s="16">
+        <v>14.3</v>
+      </c>
     </row>
     <row r="89" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>251</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>252</v>
@@ -5857,14 +6055,16 @@
       <c r="E89" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="F89" s="5"/>
+      <c r="F89" s="16">
+        <v>25.4</v>
+      </c>
     </row>
     <row r="90" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>254</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>255</v>
@@ -5875,14 +6075,16 @@
       <c r="E90" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="F90" s="5"/>
+      <c r="F90" s="16">
+        <v>18.2</v>
+      </c>
     </row>
     <row r="91" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>257</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>258</v>
@@ -5893,14 +6095,16 @@
       <c r="E91" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F91" s="5"/>
+      <c r="F91" s="16">
+        <v>18.399999999999999</v>
+      </c>
     </row>
     <row r="92" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>260</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>261</v>
@@ -5911,14 +6115,16 @@
       <c r="E92" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F92" s="5"/>
+      <c r="F92" s="16">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="93" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>263</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>264</v>
@@ -5929,14 +6135,16 @@
       <c r="E93" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F93" s="5"/>
+      <c r="F93" s="16">
+        <v>24.8</v>
+      </c>
     </row>
     <row r="94" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>266</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>267</v>
@@ -5947,14 +6155,16 @@
       <c r="E94" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F94" s="5"/>
+      <c r="F94" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="95" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>270</v>
@@ -5965,32 +6175,36 @@
       <c r="E95" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="F95" s="5"/>
+      <c r="F95" s="16">
+        <v>19.8</v>
+      </c>
     </row>
     <row r="96" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="C96" s="4" t="s">
         <v>637</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>638</v>
       </c>
       <c r="D96" s="3">
         <v>1</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F96" s="5"/>
+        <v>638</v>
+      </c>
+      <c r="F96" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="97" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>272</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>273</v>
@@ -6001,14 +6215,16 @@
       <c r="E97" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="F97" s="5"/>
+      <c r="F97" s="16">
+        <v>16</v>
+      </c>
     </row>
     <row r="98" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>276</v>
@@ -6019,14 +6235,16 @@
       <c r="E98" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="F98" s="5"/>
+      <c r="F98" s="16">
+        <v>14</v>
+      </c>
     </row>
     <row r="99" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>278</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>279</v>
@@ -6037,14 +6255,16 @@
       <c r="E99" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="F99" s="5"/>
+      <c r="F99" s="16">
+        <v>32.4</v>
+      </c>
     </row>
     <row r="100" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>281</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>282</v>
@@ -6055,14 +6275,16 @@
       <c r="E100" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F100" s="5"/>
+      <c r="F100" s="16">
+        <v>32.4</v>
+      </c>
     </row>
     <row r="101" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>284</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>285</v>
@@ -6073,14 +6295,16 @@
       <c r="E101" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F101" s="5"/>
+      <c r="F101" s="16">
+        <v>20</v>
+      </c>
     </row>
     <row r="102" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>287</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>288</v>
@@ -6091,14 +6315,16 @@
       <c r="E102" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="F102" s="5"/>
+      <c r="F102" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="103" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>290</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>291</v>
@@ -6109,14 +6335,16 @@
       <c r="E103" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="F103" s="5"/>
+      <c r="F103" s="16">
+        <v>18.399999999999999</v>
+      </c>
     </row>
     <row r="104" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>293</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>294</v>
@@ -6127,14 +6355,16 @@
       <c r="E104" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="F104" s="5"/>
+      <c r="F104" s="16">
+        <v>28.8</v>
+      </c>
     </row>
     <row r="105" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>296</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>297</v>
@@ -6145,14 +6375,16 @@
       <c r="E105" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="F105" s="5"/>
+      <c r="F105" s="16">
+        <v>22.5</v>
+      </c>
     </row>
     <row r="106" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>299</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>300</v>
@@ -6163,14 +6395,16 @@
       <c r="E106" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="F106" s="5"/>
+      <c r="F106" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="107" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>302</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>303</v>
@@ -6181,14 +6415,16 @@
       <c r="E107" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="F107" s="5"/>
+      <c r="F107" s="16">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="108" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>305</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>306</v>
@@ -6199,14 +6435,16 @@
       <c r="E108" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F108" s="5"/>
+      <c r="F108" s="16">
+        <v>17.100000000000001</v>
+      </c>
     </row>
     <row r="109" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>308</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>309</v>
@@ -6217,14 +6455,16 @@
       <c r="E109" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="F109" s="5"/>
+      <c r="F109" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="110" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>311</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>312</v>
@@ -6235,14 +6475,16 @@
       <c r="E110" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="F110" s="5"/>
+      <c r="F110" s="16">
+        <v>33.299999999999997</v>
+      </c>
     </row>
     <row r="111" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>314</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>315</v>
@@ -6253,14 +6495,16 @@
       <c r="E111" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F111" s="5"/>
+      <c r="F111" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="112" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>317</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>318</v>
@@ -6271,32 +6515,36 @@
       <c r="E112" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="F112" s="5"/>
+      <c r="F112" s="16">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="113" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>871</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>872</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>873</v>
       </c>
       <c r="D113" s="3">
         <v>0</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="F113" s="5"/>
+        <v>873</v>
+      </c>
+      <c r="F113" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="114" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>320</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>321</v>
@@ -6307,14 +6555,16 @@
       <c r="E114" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F114" s="5"/>
+      <c r="F114" s="16">
+        <v>29.2</v>
+      </c>
     </row>
     <row r="115" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>323</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>324</v>
@@ -6325,14 +6575,16 @@
       <c r="E115" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="F115" s="5"/>
+      <c r="F115" s="16">
+        <v>32</v>
+      </c>
     </row>
     <row r="116" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>326</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>327</v>
@@ -6343,14 +6595,16 @@
       <c r="E116" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="F116" s="5"/>
+      <c r="F116" s="16">
+        <v>20.6</v>
+      </c>
     </row>
     <row r="117" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>329</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>330</v>
@@ -6361,14 +6615,16 @@
       <c r="E117" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="F117" s="5"/>
+      <c r="F117" s="16">
+        <v>26</v>
+      </c>
     </row>
     <row r="118" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>332</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>333</v>
@@ -6379,14 +6635,16 @@
       <c r="E118" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="F118" s="5"/>
+      <c r="F118" s="16">
+        <v>15</v>
+      </c>
     </row>
     <row r="119" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>335</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>336</v>
@@ -6397,14 +6655,16 @@
       <c r="E119" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="F119" s="5"/>
+      <c r="F119" s="16">
+        <v>33</v>
+      </c>
     </row>
     <row r="120" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>338</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>339</v>
@@ -6415,14 +6675,16 @@
       <c r="E120" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="F120" s="5"/>
+      <c r="F120" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="121" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>341</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>342</v>
@@ -6433,14 +6695,16 @@
       <c r="E121" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="F121" s="5"/>
+      <c r="F121" s="16">
+        <v>21</v>
+      </c>
     </row>
     <row r="122" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>345</v>
@@ -6451,14 +6715,16 @@
       <c r="E122" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="F122" s="5"/>
+      <c r="F122" s="16">
+        <v>19.2</v>
+      </c>
     </row>
     <row r="123" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>347</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>348</v>
@@ -6469,14 +6735,16 @@
       <c r="E123" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="F123" s="5"/>
+      <c r="F123" s="16">
+        <v>32</v>
+      </c>
     </row>
     <row r="124" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>350</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>351</v>
@@ -6487,14 +6755,16 @@
       <c r="E124" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="F124" s="5"/>
+      <c r="F124" s="16">
+        <v>25.4</v>
+      </c>
     </row>
     <row r="125" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>353</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>354</v>
@@ -6505,14 +6775,16 @@
       <c r="E125" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="F125" s="5"/>
+      <c r="F125" s="16">
+        <v>31.5</v>
+      </c>
     </row>
     <row r="126" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>356</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>357</v>
@@ -6523,14 +6795,16 @@
       <c r="E126" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="F126" s="5"/>
+      <c r="F126" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="127" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>359</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>360</v>
@@ -6541,14 +6815,16 @@
       <c r="E127" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="F127" s="5"/>
+      <c r="F127" s="16">
+        <v>38</v>
+      </c>
     </row>
     <row r="128" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>362</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>363</v>
@@ -6559,14 +6835,16 @@
       <c r="E128" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="F128" s="5"/>
+      <c r="F128" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="129" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>365</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>366</v>
@@ -6577,14 +6855,16 @@
       <c r="E129" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="F129" s="5"/>
+      <c r="F129" s="16">
+        <v>28.5</v>
+      </c>
     </row>
     <row r="130" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>368</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>369</v>
@@ -6595,14 +6875,16 @@
       <c r="E130" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="F130" s="5"/>
+      <c r="F130" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="131" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>371</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>372</v>
@@ -6613,14 +6895,16 @@
       <c r="E131" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F131" s="5"/>
+      <c r="F131" s="16">
+        <v>28.8</v>
+      </c>
     </row>
     <row r="132" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>374</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>375</v>
@@ -6631,14 +6915,16 @@
       <c r="E132" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="F132" s="5"/>
+      <c r="F132" s="16">
+        <v>28.8</v>
+      </c>
     </row>
     <row r="133" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>377</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>378</v>
@@ -6649,14 +6935,16 @@
       <c r="E133" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="F133" s="5"/>
+      <c r="F133" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="134" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>380</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>381</v>
@@ -6667,14 +6955,16 @@
       <c r="E134" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="F134" s="5"/>
+      <c r="F134" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="135" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>383</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>384</v>
@@ -6685,14 +6975,16 @@
       <c r="E135" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="F135" s="5"/>
+      <c r="F135" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="136" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>386</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>387</v>
@@ -6703,23 +6995,28 @@
       <c r="E136" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="F136" s="5"/>
+      <c r="F136" s="16">
+        <v>33.6</v>
+      </c>
     </row>
     <row r="137" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="C137" s="4" t="s">
         <v>865</v>
-      </c>
-      <c r="B137" s="4" t="s">
-        <v>870</v>
-      </c>
-      <c r="C137" s="4" t="s">
-        <v>866</v>
       </c>
       <c r="D137" s="3">
         <v>0</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
+      </c>
+      <c r="F137" s="16">
+        <v>23</v>
       </c>
     </row>
     <row r="138" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -6727,7 +7024,7 @@
         <v>389</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>390</v>
@@ -6738,1436 +7035,1596 @@
       <c r="E138" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="F138" s="5"/>
-    </row>
-    <row r="139" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="F138" s="16">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>392</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>393</v>
+        <v>1039</v>
       </c>
       <c r="D139" s="3">
         <v>0</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="F139" s="5"/>
+        <v>393</v>
+      </c>
+      <c r="F139" s="16">
+        <v>0</v>
+      </c>
     </row>
     <row r="140" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="C140" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>770</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="D140" s="3">
         <v>1</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="F140" s="5"/>
+        <v>396</v>
+      </c>
+      <c r="F140" s="16">
+        <v>24.6</v>
+      </c>
     </row>
     <row r="141" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="C141" s="2" t="s">
         <v>398</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>399</v>
       </c>
       <c r="D141" s="3">
         <v>1</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="F141" s="5"/>
+        <v>399</v>
+      </c>
+      <c r="F141" s="16">
+        <v>20.399999999999999</v>
+      </c>
     </row>
     <row r="142" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="D142" s="3">
         <v>0</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F142" s="5"/>
+        <v>402</v>
+      </c>
+      <c r="F142" s="16">
+        <v>12</v>
+      </c>
     </row>
     <row r="143" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="C143" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="D143" s="3">
         <v>11</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="F143" s="5"/>
+        <v>405</v>
+      </c>
+      <c r="F143" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="144" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>774</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>408</v>
       </c>
       <c r="D144" s="3">
         <v>331</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F144" s="5"/>
+        <v>408</v>
+      </c>
+      <c r="F144" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="145" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="C145" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>775</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>411</v>
       </c>
       <c r="D145" s="3">
         <v>0</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="F145" s="5"/>
+        <v>411</v>
+      </c>
+      <c r="F145" s="16">
+        <v>35.1</v>
+      </c>
     </row>
     <row r="146" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>776</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="D146" s="3">
         <v>5</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="F146" s="5"/>
+        <v>414</v>
+      </c>
+      <c r="F146" s="16">
+        <v>18.2</v>
+      </c>
     </row>
     <row r="147" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>777</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="D147" s="3">
         <v>33</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="F147" s="5"/>
+        <v>417</v>
+      </c>
+      <c r="F147" s="16">
+        <v>24.3</v>
+      </c>
     </row>
     <row r="148" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>778</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>420</v>
       </c>
       <c r="D148" s="3">
         <v>5</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="F148" s="5"/>
+        <v>420</v>
+      </c>
+      <c r="F148" s="16">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="149" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>422</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>779</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>423</v>
       </c>
       <c r="D149" s="3">
         <v>1</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F149" s="5"/>
+        <v>423</v>
+      </c>
+      <c r="F149" s="16">
+        <v>24.3</v>
+      </c>
     </row>
     <row r="150" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>425</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>780</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>426</v>
       </c>
       <c r="D150" s="3">
         <v>1</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="F150" s="5"/>
+        <v>426</v>
+      </c>
+      <c r="F150" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="151" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>428</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>781</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>429</v>
       </c>
       <c r="D151" s="3">
         <v>0</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="F151" s="5"/>
+        <v>429</v>
+      </c>
+      <c r="F151" s="16">
+        <v>26.4</v>
+      </c>
     </row>
     <row r="152" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>782</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="D152" s="3">
         <v>14</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="F152" s="5"/>
+        <v>432</v>
+      </c>
+      <c r="F152" s="16">
+        <v>12</v>
+      </c>
     </row>
     <row r="153" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>782</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>434</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>783</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>435</v>
       </c>
       <c r="D153" s="3">
         <v>1</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="F153" s="5"/>
+        <v>435</v>
+      </c>
+      <c r="F153" s="16">
+        <v>30</v>
+      </c>
     </row>
     <row r="154" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>784</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>438</v>
       </c>
       <c r="D154" s="3">
         <v>10</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="F154" s="5"/>
+        <v>438</v>
+      </c>
+      <c r="F154" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="155" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>785</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="D155" s="3">
         <v>12</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="F155" s="5"/>
+        <v>441</v>
+      </c>
+      <c r="F155" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="156" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>786</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>444</v>
       </c>
       <c r="D156" s="3">
         <v>3</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="F156" s="5"/>
+        <v>444</v>
+      </c>
+      <c r="F156" s="16">
+        <v>27.2</v>
+      </c>
     </row>
     <row r="157" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>446</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>787</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="D157" s="3">
         <v>1</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="F157" s="5"/>
+        <v>447</v>
+      </c>
+      <c r="F157" s="16">
+        <v>16.2</v>
+      </c>
     </row>
     <row r="158" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>788</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="D158" s="3">
         <v>4</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="F158" s="5"/>
+        <v>450</v>
+      </c>
+      <c r="F158" s="16">
+        <v>20</v>
+      </c>
     </row>
     <row r="159" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="D159" s="3">
         <v>1</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="F159" s="5"/>
+        <v>453</v>
+      </c>
+      <c r="F159" s="16">
+        <v>5</v>
+      </c>
     </row>
     <row r="160" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="D160" s="3">
         <v>5</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="F160" s="5"/>
+        <v>456</v>
+      </c>
+      <c r="F160" s="16">
+        <v>35.1</v>
+      </c>
     </row>
     <row r="161" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>791</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>459</v>
       </c>
       <c r="D161" s="3">
         <v>3</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="F161" s="5"/>
+        <v>459</v>
+      </c>
+      <c r="F161" s="16">
+        <v>15</v>
+      </c>
     </row>
     <row r="162" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="D162" s="3">
         <v>14</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="F162" s="5"/>
+        <v>462</v>
+      </c>
+      <c r="F162" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="163" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="C163" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="D163" s="3">
         <v>1</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="F163" s="5"/>
+        <v>465</v>
+      </c>
+      <c r="F163" s="16">
+        <v>25.9</v>
+      </c>
     </row>
     <row r="164" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="B164" s="2" t="s">
-        <v>794</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="D164" s="3">
         <v>0</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F164" s="5"/>
+        <v>468</v>
+      </c>
+      <c r="F164" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="165" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="B165" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="D165" s="3">
         <v>2</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F165" s="5"/>
+        <v>471</v>
+      </c>
+      <c r="F165" s="16">
+        <v>15.6</v>
+      </c>
     </row>
     <row r="166" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="B166" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>474</v>
       </c>
       <c r="D166" s="3">
         <v>12</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F166" s="5"/>
+        <v>474</v>
+      </c>
+      <c r="F166" s="16">
+        <v>16.100000000000001</v>
+      </c>
     </row>
     <row r="167" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>796</v>
+      </c>
+      <c r="C167" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="B167" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="D167" s="3">
         <v>0</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F167" s="5"/>
+        <v>477</v>
+      </c>
+      <c r="F167" s="16">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="168" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="C168" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="B168" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>480</v>
       </c>
       <c r="D168" s="3">
         <v>10</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="F168" s="5"/>
+        <v>480</v>
+      </c>
+      <c r="F168" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="169" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="C169" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="D169" s="3">
         <v>7</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="F169" s="5"/>
+        <v>483</v>
+      </c>
+      <c r="F169" s="16">
+        <v>21</v>
+      </c>
     </row>
     <row r="170" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>799</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>485</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>800</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>486</v>
       </c>
       <c r="D170" s="3">
         <v>0</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="F170" s="5"/>
+        <v>486</v>
+      </c>
+      <c r="F170" s="16">
+        <v>9</v>
+      </c>
     </row>
     <row r="171" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="C171" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="B171" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="D171" s="3">
         <v>2</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="F171" s="5"/>
+        <v>489</v>
+      </c>
+      <c r="F171" s="16">
+        <v>19.5</v>
+      </c>
     </row>
     <row r="172" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="B172" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="D172" s="3">
         <v>2</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="F172" s="5"/>
+        <v>492</v>
+      </c>
+      <c r="F172" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="173" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C173" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>495</v>
       </c>
       <c r="D173" s="3">
         <v>1</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="F173" s="5"/>
+        <v>495</v>
+      </c>
+      <c r="F173" s="16">
+        <v>9</v>
+      </c>
     </row>
     <row r="174" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>804</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="D174" s="3">
         <v>2</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F174" s="5"/>
+        <v>498</v>
+      </c>
+      <c r="F174" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="175" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>804</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>805</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>501</v>
       </c>
       <c r="D175" s="3">
         <v>0</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="F175" s="5"/>
+        <v>501</v>
+      </c>
+      <c r="F175" s="16">
+        <v>28.8</v>
+      </c>
     </row>
     <row r="176" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="C176" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="D176" s="3">
         <v>0</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="F176" s="5"/>
+        <v>504</v>
+      </c>
+      <c r="F176" s="16">
+        <v>30.6</v>
+      </c>
     </row>
     <row r="177" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="C177" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>807</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="D177" s="3">
         <v>2</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="F177" s="5"/>
+        <v>507</v>
+      </c>
+      <c r="F177" s="16">
+        <v>32</v>
+      </c>
     </row>
     <row r="178" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>808</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="D178" s="3">
         <v>1</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="F178" s="5"/>
+        <v>510</v>
+      </c>
+      <c r="F178" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="179" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="C179" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>809</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>513</v>
       </c>
       <c r="D179" s="3">
         <v>0</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="F179" s="5"/>
+        <v>513</v>
+      </c>
+      <c r="F179" s="16">
+        <v>27.6</v>
+      </c>
     </row>
     <row r="180" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="B180" s="2" t="s">
-        <v>810</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>516</v>
       </c>
       <c r="D180" s="3">
         <v>0</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="F180" s="5"/>
+        <v>516</v>
+      </c>
+      <c r="F180" s="16">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="181" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="D181" s="3">
         <v>0</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="F181" s="5"/>
+        <v>519</v>
+      </c>
+      <c r="F181" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="182" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="B182" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="D182" s="3">
         <v>0</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="F182" s="5"/>
+        <v>522</v>
+      </c>
+      <c r="F182" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="183" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="D183" s="3">
         <v>0</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="F183" s="5"/>
+        <v>525</v>
+      </c>
+      <c r="F183" s="16">
+        <v>32.4</v>
+      </c>
     </row>
     <row r="184" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>527</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>814</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>528</v>
       </c>
       <c r="D184" s="3">
         <v>2</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F184" s="5"/>
+        <v>528</v>
+      </c>
+      <c r="F184" s="16">
+        <v>12</v>
+      </c>
     </row>
     <row r="185" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="C185" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="D185" s="3">
         <v>2</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="F185" s="5"/>
+        <v>531</v>
+      </c>
+      <c r="F185" s="16">
+        <v>33</v>
+      </c>
     </row>
     <row r="186" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="C186" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>816</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="D186" s="3">
         <v>1</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="F186" s="5"/>
+        <v>534</v>
+      </c>
+      <c r="F186" s="16">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="187" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>536</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>817</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>537</v>
       </c>
       <c r="D187" s="3">
         <v>61</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="F187" s="5"/>
+        <v>537</v>
+      </c>
+      <c r="F187" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="188" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="C188" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="D188" s="3">
         <v>2</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="F188" s="5"/>
+        <v>540</v>
+      </c>
+      <c r="F188" s="16">
+        <v>32</v>
+      </c>
     </row>
     <row r="189" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C189" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>543</v>
       </c>
       <c r="D189" s="3">
         <v>54</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="F189" s="5"/>
+        <v>543</v>
+      </c>
+      <c r="F189" s="16">
+        <v>16</v>
+      </c>
     </row>
     <row r="190" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="C190" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>820</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="D190" s="3">
         <v>49</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="F190" s="5"/>
+        <v>546</v>
+      </c>
+      <c r="F190" s="16">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="191" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="C191" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="D191" s="3">
         <v>0</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="F191" s="5"/>
+        <v>549</v>
+      </c>
+      <c r="F191" s="16">
+        <v>25.7</v>
+      </c>
     </row>
     <row r="192" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C192" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="D192" s="3">
         <v>1</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="F192" s="5"/>
+        <v>552</v>
+      </c>
+      <c r="F192" s="16">
+        <v>31.7</v>
+      </c>
     </row>
     <row r="193" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="C193" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="D193" s="3">
         <v>98</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="F193" s="5"/>
+        <v>555</v>
+      </c>
+      <c r="F193" s="16">
+        <v>11.6</v>
+      </c>
     </row>
     <row r="194" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C194" s="2" t="s">
         <v>557</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="D194" s="3">
         <v>0</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="F194" s="5"/>
+        <v>558</v>
+      </c>
+      <c r="F194" s="16">
+        <v>16.2</v>
+      </c>
     </row>
     <row r="195" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="C195" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>825</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>561</v>
       </c>
       <c r="D195" s="3">
         <v>5</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="F195" s="5"/>
+        <v>561</v>
+      </c>
+      <c r="F195" s="16">
+        <v>21.3</v>
+      </c>
     </row>
     <row r="196" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>825</v>
+      </c>
+      <c r="C196" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="D196" s="3">
         <v>0</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="F196" s="5"/>
+        <v>564</v>
+      </c>
+      <c r="F196" s="16">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="197" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="C197" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="D197" s="3">
         <v>2</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="F197" s="5"/>
+        <v>567</v>
+      </c>
+      <c r="F197" s="16">
+        <v>13.5</v>
+      </c>
     </row>
     <row r="198" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>828</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="D198" s="3">
         <v>4</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="F198" s="5"/>
+        <v>570</v>
+      </c>
+      <c r="F198" s="16">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="199" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="C199" s="2" t="s">
         <v>572</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>573</v>
       </c>
       <c r="D199" s="3">
         <v>1</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="F199" s="5"/>
+        <v>573</v>
+      </c>
+      <c r="F199" s="16">
+        <v>36</v>
+      </c>
     </row>
     <row r="200" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C200" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>576</v>
       </c>
       <c r="D200" s="3">
         <v>1</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="F200" s="5"/>
+        <v>576</v>
+      </c>
+      <c r="F200" s="16">
+        <v>23</v>
+      </c>
     </row>
     <row r="201" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>578</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>831</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>579</v>
       </c>
       <c r="D201" s="3">
         <v>2</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="F201" s="5"/>
+        <v>579</v>
+      </c>
+      <c r="F201" s="16">
+        <v>36.1</v>
+      </c>
     </row>
     <row r="202" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>832</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>582</v>
       </c>
       <c r="D202" s="3">
         <v>81</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="F202" s="5"/>
+        <v>582</v>
+      </c>
+      <c r="F202" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="203" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="C203" s="2" t="s">
         <v>584</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>585</v>
       </c>
       <c r="D203" s="3">
         <v>1</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="F203" s="5"/>
+        <v>585</v>
+      </c>
+      <c r="F203" s="16">
+        <v>28.5</v>
+      </c>
     </row>
     <row r="204" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="D204" s="3">
         <v>1</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="F204" s="5"/>
+        <v>588</v>
+      </c>
+      <c r="F204" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="205" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="C205" s="2" t="s">
         <v>590</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>835</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>591</v>
       </c>
       <c r="D205" s="3">
         <v>1</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="F205" s="5"/>
+        <v>591</v>
+      </c>
+      <c r="F205" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="206" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>593</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>594</v>
       </c>
       <c r="D206" s="3">
         <v>7</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="F206" s="5"/>
+        <v>594</v>
+      </c>
+      <c r="F206" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="207" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="C207" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="D207" s="3">
         <v>1</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="F207" s="5"/>
+        <v>597</v>
+      </c>
+      <c r="F207" s="16">
+        <v>21.8</v>
+      </c>
     </row>
     <row r="208" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="C208" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>838</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>600</v>
       </c>
       <c r="D208" s="3">
         <v>2</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="F208" s="5"/>
+        <v>600</v>
+      </c>
+      <c r="F208" s="16">
+        <v>38.6</v>
+      </c>
     </row>
     <row r="209" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="C209" s="2" t="s">
         <v>602</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>839</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>603</v>
       </c>
       <c r="D209" s="3">
         <v>2</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="F209" s="5"/>
+        <v>603</v>
+      </c>
+      <c r="F209" s="16">
+        <v>30.8</v>
+      </c>
     </row>
     <row r="210" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="C210" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>840</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>606</v>
       </c>
       <c r="D210" s="3">
         <v>2</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="F210" s="5"/>
+        <v>606</v>
+      </c>
+      <c r="F210" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="211" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>608</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>609</v>
       </c>
       <c r="D211" s="3">
         <v>0</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="F211" s="5"/>
+        <v>609</v>
+      </c>
+      <c r="F211" s="16">
+        <v>33.6</v>
+      </c>
     </row>
     <row r="212" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="C212" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="D212" s="3">
         <v>4</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F212" s="5"/>
+        <v>612</v>
+      </c>
+      <c r="F212" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="213" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="C213" s="2" t="s">
         <v>614</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>843</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>615</v>
       </c>
       <c r="D213" s="3">
         <v>3</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="F213" s="5"/>
+        <v>615</v>
+      </c>
+      <c r="F213" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="214" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="C214" s="2" t="s">
         <v>617</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>844</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>618</v>
       </c>
       <c r="D214" s="3">
         <v>23</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="F214" s="5"/>
+        <v>618</v>
+      </c>
+      <c r="F214" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="215" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>620</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>845</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>621</v>
       </c>
       <c r="D215" s="3">
         <v>22</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="F215" s="5"/>
+        <v>621</v>
+      </c>
+      <c r="F215" s="16">
+        <v>24</v>
+      </c>
     </row>
     <row r="216" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="C216" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>846</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>627</v>
       </c>
       <c r="D216" s="3">
         <v>8</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="F216" s="5"/>
+        <v>627</v>
+      </c>
+      <c r="F216" s="16">
+        <v>21.6</v>
+      </c>
     </row>
     <row r="217" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="C217" s="2" t="s">
         <v>623</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>624</v>
       </c>
       <c r="D217" s="3">
         <v>0</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>625</v>
-      </c>
-      <c r="F217" s="5"/>
+        <v>624</v>
+      </c>
+      <c r="F217" s="16">
+        <v>21.9</v>
+      </c>
     </row>
     <row r="218" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>182</v>
@@ -8176,45 +8633,51 @@
         <v>14</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="F218" s="5"/>
+        <v>629</v>
+      </c>
+      <c r="F218" s="16">
+        <v>18</v>
+      </c>
     </row>
     <row r="219" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="C219" s="2" t="s">
         <v>631</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="D219" s="3">
         <v>2</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="F219" s="5"/>
+        <v>632</v>
+      </c>
+      <c r="F219" s="16">
+        <v>22.8</v>
+      </c>
     </row>
     <row r="220" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="C220" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="D220" s="3">
         <v>2</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="F220" s="5"/>
+        <v>635</v>
+      </c>
+      <c r="F220" s="16">
+        <v>28.9</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F220">
@@ -8236,1568 +8699,1568 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>880</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>881</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>882</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1026</v>
+      <c r="E1" s="7" t="s">
+        <v>1025</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>883</v>
-      </c>
-      <c r="B2" s="7">
+        <v>882</v>
+      </c>
+      <c r="B2" s="6">
         <v>48600</v>
       </c>
       <c r="C2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>885</v>
-      </c>
-      <c r="B3" s="7">
+        <v>884</v>
+      </c>
+      <c r="B3" s="6">
         <v>27380</v>
       </c>
       <c r="C3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>886</v>
-      </c>
-      <c r="B4" s="7">
+        <v>885</v>
+      </c>
+      <c r="B4" s="6">
         <v>22740</v>
       </c>
       <c r="C4" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>887</v>
-      </c>
-      <c r="B5" s="7">
+        <v>886</v>
+      </c>
+      <c r="B5" s="6">
         <v>12510</v>
       </c>
       <c r="C5" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>888</v>
-      </c>
-      <c r="B6" s="7">
+        <v>887</v>
+      </c>
+      <c r="B6" s="6">
         <v>10950</v>
       </c>
       <c r="C6" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>889</v>
-      </c>
-      <c r="B7" s="7">
+        <v>888</v>
+      </c>
+      <c r="B7" s="6">
         <v>10830</v>
       </c>
       <c r="C7" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>890</v>
-      </c>
-      <c r="B8" s="7">
+        <v>889</v>
+      </c>
+      <c r="B8" s="6">
         <v>9631</v>
       </c>
       <c r="C8" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>891</v>
-      </c>
-      <c r="B9" s="7">
+        <v>890</v>
+      </c>
+      <c r="B9" s="6">
         <v>8380</v>
       </c>
       <c r="C9" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>892</v>
-      </c>
-      <c r="B10" s="7">
+        <v>891</v>
+      </c>
+      <c r="B10" s="6">
         <v>5568</v>
       </c>
       <c r="C10" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>893</v>
-      </c>
-      <c r="B11" s="7">
+        <v>892</v>
+      </c>
+      <c r="B11" s="6">
         <v>5400</v>
       </c>
       <c r="C11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>894</v>
-      </c>
-      <c r="B12" s="7">
+        <v>893</v>
+      </c>
+      <c r="B12" s="6">
         <v>4395</v>
       </c>
       <c r="C12" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>895</v>
-      </c>
-      <c r="B13" s="7">
+        <v>894</v>
+      </c>
+      <c r="B13" s="6">
         <v>4110</v>
       </c>
       <c r="C13" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>896</v>
-      </c>
-      <c r="B14" s="7">
+        <v>895</v>
+      </c>
+      <c r="B14" s="6">
         <v>4080</v>
       </c>
       <c r="C14" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>897</v>
-      </c>
-      <c r="B15" s="7">
+        <v>896</v>
+      </c>
+      <c r="B15" s="6">
         <v>3660</v>
       </c>
       <c r="C15" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>898</v>
-      </c>
-      <c r="B16" s="7">
+        <v>897</v>
+      </c>
+      <c r="B16" s="6">
         <v>3200</v>
       </c>
       <c r="C16" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>899</v>
-      </c>
-      <c r="B17" s="7">
+        <v>898</v>
+      </c>
+      <c r="B17" s="6">
         <v>3165</v>
       </c>
       <c r="C17" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>900</v>
-      </c>
-      <c r="B18" s="7">
+        <v>899</v>
+      </c>
+      <c r="B18" s="6">
         <v>2765</v>
       </c>
       <c r="C18" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>901</v>
-      </c>
-      <c r="B19" s="7">
+        <v>900</v>
+      </c>
+      <c r="B19" s="6">
         <v>2265</v>
       </c>
       <c r="C19" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>902</v>
-      </c>
-      <c r="B20" s="7">
+        <v>901</v>
+      </c>
+      <c r="B20" s="6">
         <v>2185</v>
       </c>
       <c r="C20" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>903</v>
-      </c>
-      <c r="B21" s="7">
+        <v>902</v>
+      </c>
+      <c r="B21" s="6">
         <v>2070</v>
       </c>
       <c r="C21" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>904</v>
-      </c>
-      <c r="B22" s="7">
+        <v>903</v>
+      </c>
+      <c r="B22" s="6">
         <v>1925</v>
       </c>
       <c r="C22" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>905</v>
-      </c>
-      <c r="B23" s="7">
+        <v>904</v>
+      </c>
+      <c r="B23" s="6">
         <v>1895</v>
       </c>
       <c r="C23" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>906</v>
-      </c>
-      <c r="B24" s="7">
+        <v>905</v>
+      </c>
+      <c r="B24" s="6">
         <v>1370</v>
       </c>
       <c r="C24" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>907</v>
-      </c>
-      <c r="B25" s="7">
+        <v>906</v>
+      </c>
+      <c r="B25" s="6">
         <v>1300</v>
       </c>
       <c r="C25" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>908</v>
-      </c>
-      <c r="B26" s="7">
+        <v>907</v>
+      </c>
+      <c r="B26" s="6">
         <v>1215</v>
       </c>
       <c r="C26" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>909</v>
-      </c>
-      <c r="B27" s="7">
+        <v>908</v>
+      </c>
+      <c r="B27" s="6">
         <v>1020</v>
       </c>
       <c r="C27" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>910</v>
-      </c>
-      <c r="B28" s="7">
+        <v>909</v>
+      </c>
+      <c r="B28" s="6">
         <v>1010</v>
       </c>
       <c r="C28" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>911</v>
-      </c>
-      <c r="B29" s="7">
+        <v>910</v>
+      </c>
+      <c r="B29" s="6">
         <v>945</v>
       </c>
       <c r="C29" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>912</v>
-      </c>
-      <c r="B30" s="7">
+        <v>911</v>
+      </c>
+      <c r="B30" s="6">
         <v>840</v>
       </c>
       <c r="C30" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>913</v>
-      </c>
-      <c r="B31" s="7">
+        <v>912</v>
+      </c>
+      <c r="B31" s="6">
         <v>780</v>
       </c>
       <c r="C31" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>914</v>
-      </c>
-      <c r="B32" s="7">
+        <v>913</v>
+      </c>
+      <c r="B32" s="6">
         <v>770</v>
       </c>
       <c r="C32" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>915</v>
-      </c>
-      <c r="B33" s="7">
+        <v>914</v>
+      </c>
+      <c r="B33" s="6">
         <v>730</v>
       </c>
       <c r="C33" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>916</v>
-      </c>
-      <c r="B34" s="7">
+        <v>915</v>
+      </c>
+      <c r="B34" s="6">
         <v>630</v>
       </c>
       <c r="C34" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>917</v>
-      </c>
-      <c r="B35" s="7">
+        <v>916</v>
+      </c>
+      <c r="B35" s="6">
         <v>630</v>
       </c>
       <c r="C35" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>918</v>
-      </c>
-      <c r="B36" s="7">
+        <v>917</v>
+      </c>
+      <c r="B36" s="6">
         <v>580</v>
       </c>
       <c r="C36" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>919</v>
-      </c>
-      <c r="B37" s="7">
+        <v>918</v>
+      </c>
+      <c r="B37" s="6">
         <v>540</v>
       </c>
       <c r="C37" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>920</v>
-      </c>
-      <c r="B38" s="7">
+        <v>919</v>
+      </c>
+      <c r="B38" s="6">
         <v>525</v>
       </c>
       <c r="C38" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>921</v>
-      </c>
-      <c r="B39" s="7">
+        <v>920</v>
+      </c>
+      <c r="B39" s="6">
         <v>525</v>
       </c>
       <c r="C39" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>922</v>
-      </c>
-      <c r="B40" s="7">
+        <v>921</v>
+      </c>
+      <c r="B40" s="6">
         <v>524</v>
       </c>
       <c r="C40" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>923</v>
-      </c>
-      <c r="B41" s="7">
+        <v>922</v>
+      </c>
+      <c r="B41" s="6">
         <v>495</v>
       </c>
       <c r="C41" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>924</v>
-      </c>
-      <c r="B42" s="7">
+        <v>923</v>
+      </c>
+      <c r="B42" s="6">
         <v>495</v>
       </c>
       <c r="C42" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>925</v>
-      </c>
-      <c r="B43" s="7">
+        <v>924</v>
+      </c>
+      <c r="B43" s="6">
         <v>490</v>
       </c>
       <c r="C43" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>926</v>
-      </c>
-      <c r="B44" s="7">
+        <v>925</v>
+      </c>
+      <c r="B44" s="6">
         <v>450</v>
       </c>
       <c r="C44" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>927</v>
-      </c>
-      <c r="B45" s="7">
+        <v>926</v>
+      </c>
+      <c r="B45" s="6">
         <v>450</v>
       </c>
       <c r="C45" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>928</v>
-      </c>
-      <c r="B46" s="7">
+        <v>927</v>
+      </c>
+      <c r="B46" s="6">
         <v>360</v>
       </c>
       <c r="C46" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>929</v>
-      </c>
-      <c r="B47" s="7">
+        <v>928</v>
+      </c>
+      <c r="B47" s="6">
         <v>345</v>
       </c>
       <c r="C47" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>930</v>
-      </c>
-      <c r="B48" s="7">
+        <v>929</v>
+      </c>
+      <c r="B48" s="6">
         <v>330</v>
       </c>
       <c r="C48" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>930</v>
+      </c>
+      <c r="B49" s="6">
+        <v>300</v>
+      </c>
+      <c r="C49" t="s">
         <v>931</v>
-      </c>
-      <c r="B49" s="7">
-        <v>300</v>
-      </c>
-      <c r="C49" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>933</v>
-      </c>
-      <c r="B50" s="7">
+        <v>932</v>
+      </c>
+      <c r="B50" s="6">
         <v>300</v>
       </c>
       <c r="C50" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>934</v>
-      </c>
-      <c r="B51" s="7">
+        <v>933</v>
+      </c>
+      <c r="B51" s="6">
         <v>285</v>
       </c>
       <c r="C51" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>935</v>
-      </c>
-      <c r="B52" s="7">
+        <v>934</v>
+      </c>
+      <c r="B52" s="6">
         <v>265</v>
       </c>
       <c r="C52" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>935</v>
+      </c>
+      <c r="B53" s="6">
+        <v>260</v>
+      </c>
+      <c r="C53" t="s">
         <v>936</v>
-      </c>
-      <c r="B53" s="7">
-        <v>260</v>
-      </c>
-      <c r="C53" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>938</v>
-      </c>
-      <c r="B54" s="7">
+        <v>937</v>
+      </c>
+      <c r="B54" s="6">
         <v>245</v>
       </c>
       <c r="C54" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>939</v>
-      </c>
-      <c r="B55" s="7">
+        <v>938</v>
+      </c>
+      <c r="B55" s="6">
         <v>240</v>
       </c>
       <c r="C55" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>940</v>
-      </c>
-      <c r="B56" s="7">
+        <v>939</v>
+      </c>
+      <c r="B56" s="6">
         <v>240</v>
       </c>
       <c r="C56" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>941</v>
-      </c>
-      <c r="B57" s="7">
+        <v>940</v>
+      </c>
+      <c r="B57" s="6">
         <v>240</v>
       </c>
       <c r="C57" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>942</v>
-      </c>
-      <c r="B58" s="7">
+        <v>941</v>
+      </c>
+      <c r="B58" s="6">
         <v>210</v>
       </c>
       <c r="C58" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>943</v>
-      </c>
-      <c r="B59" s="7">
+        <v>942</v>
+      </c>
+      <c r="B59" s="6">
         <v>210</v>
       </c>
       <c r="C59" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>944</v>
-      </c>
-      <c r="B60" s="7">
+        <v>943</v>
+      </c>
+      <c r="B60" s="6">
         <v>200</v>
       </c>
       <c r="C60" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>945</v>
-      </c>
-      <c r="B61" s="7">
+        <v>944</v>
+      </c>
+      <c r="B61" s="6">
         <v>194</v>
       </c>
       <c r="C61" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>946</v>
-      </c>
-      <c r="B62" s="7">
+        <v>945</v>
+      </c>
+      <c r="B62" s="6">
         <v>180</v>
       </c>
       <c r="C62" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>947</v>
-      </c>
-      <c r="B63" s="7">
+        <v>946</v>
+      </c>
+      <c r="B63" s="6">
         <v>180</v>
       </c>
       <c r="C63" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>948</v>
-      </c>
-      <c r="B64" s="7">
+        <v>947</v>
+      </c>
+      <c r="B64" s="6">
         <v>180</v>
       </c>
       <c r="C64" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>949</v>
-      </c>
-      <c r="B65" s="7">
+        <v>948</v>
+      </c>
+      <c r="B65" s="6">
         <v>180</v>
       </c>
       <c r="C65" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>950</v>
-      </c>
-      <c r="B66" s="7">
+        <v>949</v>
+      </c>
+      <c r="B66" s="6">
         <v>175</v>
       </c>
       <c r="C66" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>951</v>
-      </c>
-      <c r="B67" s="7">
+        <v>950</v>
+      </c>
+      <c r="B67" s="6">
         <v>170</v>
       </c>
       <c r="C67" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>952</v>
-      </c>
-      <c r="B68" s="7">
+        <v>951</v>
+      </c>
+      <c r="B68" s="6">
         <v>160</v>
       </c>
       <c r="C68" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>953</v>
-      </c>
-      <c r="B69" s="7">
+        <v>952</v>
+      </c>
+      <c r="B69" s="6">
         <v>155</v>
       </c>
       <c r="C69" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>953</v>
+      </c>
+      <c r="B70" s="6">
+        <v>150</v>
+      </c>
+      <c r="C70" t="s">
         <v>954</v>
-      </c>
-      <c r="B70" s="7">
-        <v>150</v>
-      </c>
-      <c r="C70" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>956</v>
-      </c>
-      <c r="B71" s="7">
+        <v>955</v>
+      </c>
+      <c r="B71" s="6">
         <v>150</v>
       </c>
       <c r="C71" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>957</v>
-      </c>
-      <c r="B72" s="7">
+        <v>956</v>
+      </c>
+      <c r="B72" s="6">
         <v>145</v>
       </c>
       <c r="C72" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>958</v>
-      </c>
-      <c r="B73" s="7">
+        <v>957</v>
+      </c>
+      <c r="B73" s="6">
         <v>135</v>
       </c>
       <c r="C73" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>958</v>
+      </c>
+      <c r="B74" s="6">
+        <v>132</v>
+      </c>
+      <c r="C74" t="s">
         <v>959</v>
-      </c>
-      <c r="B74" s="7">
-        <v>132</v>
-      </c>
-      <c r="C74" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>960</v>
+      </c>
+      <c r="B75" s="6">
+        <v>131</v>
+      </c>
+      <c r="C75" t="s">
         <v>961</v>
-      </c>
-      <c r="B75" s="7">
-        <v>131</v>
-      </c>
-      <c r="C75" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>963</v>
-      </c>
-      <c r="B76" s="7">
+        <v>962</v>
+      </c>
+      <c r="B76" s="6">
         <v>120</v>
       </c>
       <c r="C76" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>964</v>
-      </c>
-      <c r="B77" s="7">
+        <v>963</v>
+      </c>
+      <c r="B77" s="6">
         <v>120</v>
       </c>
       <c r="C77" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>965</v>
-      </c>
-      <c r="B78" s="7">
+        <v>964</v>
+      </c>
+      <c r="B78" s="6">
         <v>120</v>
       </c>
       <c r="C78" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>966</v>
-      </c>
-      <c r="B79" s="7">
+        <v>965</v>
+      </c>
+      <c r="B79" s="6">
         <v>120</v>
       </c>
       <c r="C79" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>967</v>
-      </c>
-      <c r="B80" s="7">
+        <v>966</v>
+      </c>
+      <c r="B80" s="6">
         <v>120</v>
       </c>
       <c r="C80" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>968</v>
-      </c>
-      <c r="B81" s="7">
+        <v>967</v>
+      </c>
+      <c r="B81" s="6">
         <v>120</v>
       </c>
       <c r="C81" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>969</v>
-      </c>
-      <c r="B82" s="7">
+        <v>968</v>
+      </c>
+      <c r="B82" s="6">
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>970</v>
-      </c>
-      <c r="B83" s="7">
+        <v>969</v>
+      </c>
+      <c r="B83" s="6">
         <v>100</v>
       </c>
       <c r="C83" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>971</v>
-      </c>
-      <c r="B84" s="7">
+        <v>970</v>
+      </c>
+      <c r="B84" s="6">
         <v>100</v>
       </c>
       <c r="C84" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>972</v>
-      </c>
-      <c r="B85" s="7">
+        <v>971</v>
+      </c>
+      <c r="B85" s="6">
         <v>95</v>
       </c>
       <c r="C85" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>973</v>
-      </c>
-      <c r="B86" s="7">
+        <v>972</v>
+      </c>
+      <c r="B86" s="6">
         <v>93</v>
       </c>
       <c r="C86" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>974</v>
-      </c>
-      <c r="B87" s="7">
+        <v>973</v>
+      </c>
+      <c r="B87" s="6">
         <v>90</v>
       </c>
       <c r="C87" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>975</v>
-      </c>
-      <c r="B88" s="7">
+        <v>974</v>
+      </c>
+      <c r="B88" s="6">
         <v>90</v>
       </c>
       <c r="C88" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>976</v>
-      </c>
-      <c r="B89" s="7">
+        <v>975</v>
+      </c>
+      <c r="B89" s="6">
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>977</v>
-      </c>
-      <c r="B90" s="7">
+        <v>976</v>
+      </c>
+      <c r="B90" s="6">
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>978</v>
-      </c>
-      <c r="B91" s="7">
+        <v>977</v>
+      </c>
+      <c r="B91" s="6">
         <v>64</v>
       </c>
       <c r="C91" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>979</v>
-      </c>
-      <c r="B92" s="7">
+        <v>978</v>
+      </c>
+      <c r="B92" s="6">
         <v>60</v>
       </c>
       <c r="C92" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>980</v>
-      </c>
-      <c r="B93" s="7">
+        <v>979</v>
+      </c>
+      <c r="B93" s="6">
         <v>60</v>
       </c>
       <c r="C93" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>903</v>
-      </c>
-      <c r="B94" s="7">
+        <v>902</v>
+      </c>
+      <c r="B94" s="6">
         <v>60</v>
       </c>
       <c r="C94" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>981</v>
-      </c>
-      <c r="B95" s="7">
+        <v>980</v>
+      </c>
+      <c r="B95" s="6">
         <v>60</v>
       </c>
       <c r="C95" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>982</v>
-      </c>
-      <c r="B96" s="7">
+        <v>981</v>
+      </c>
+      <c r="B96" s="6">
         <v>50</v>
       </c>
       <c r="C96" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>983</v>
-      </c>
-      <c r="B97" s="7">
+        <v>982</v>
+      </c>
+      <c r="B97" s="6">
         <v>50</v>
       </c>
       <c r="C97" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>984</v>
-      </c>
-      <c r="B98" s="7">
+        <v>983</v>
+      </c>
+      <c r="B98" s="6">
         <v>49</v>
       </c>
       <c r="C98" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>985</v>
-      </c>
-      <c r="B99" s="7">
+        <v>984</v>
+      </c>
+      <c r="B99" s="6">
         <v>45</v>
       </c>
       <c r="C99" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>986</v>
-      </c>
-      <c r="B100" s="7">
+        <v>985</v>
+      </c>
+      <c r="B100" s="6">
         <v>45</v>
       </c>
       <c r="C100" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>987</v>
-      </c>
-      <c r="B101" s="7">
+        <v>986</v>
+      </c>
+      <c r="B101" s="6">
         <v>40</v>
       </c>
       <c r="C101" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>988</v>
-      </c>
-      <c r="B102" s="7">
+        <v>987</v>
+      </c>
+      <c r="B102" s="6">
         <v>35</v>
       </c>
       <c r="C102" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>989</v>
-      </c>
-      <c r="B103" s="7">
+        <v>988</v>
+      </c>
+      <c r="B103" s="6">
         <v>32.5</v>
       </c>
       <c r="C103" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>990</v>
-      </c>
-      <c r="B104" s="7">
+        <v>989</v>
+      </c>
+      <c r="B104" s="6">
         <v>30</v>
       </c>
       <c r="C104" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>991</v>
-      </c>
-      <c r="B105" s="7">
+        <v>990</v>
+      </c>
+      <c r="B105" s="6">
         <v>30</v>
       </c>
       <c r="C105" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>992</v>
-      </c>
-      <c r="B106" s="7">
+        <v>991</v>
+      </c>
+      <c r="B106" s="6">
         <v>30</v>
       </c>
       <c r="C106" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>992</v>
+      </c>
+      <c r="B107" s="6">
+        <v>30</v>
+      </c>
+      <c r="C107" t="s">
         <v>993</v>
-      </c>
-      <c r="B107" s="7">
-        <v>30</v>
-      </c>
-      <c r="C107" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>995</v>
-      </c>
-      <c r="B108" s="7">
+        <v>994</v>
+      </c>
+      <c r="B108" s="6">
         <v>30</v>
       </c>
       <c r="C108" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>959</v>
-      </c>
-      <c r="B109" s="7">
+        <v>958</v>
+      </c>
+      <c r="B109" s="6">
         <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>931</v>
-      </c>
-      <c r="B110" s="7">
+        <v>930</v>
+      </c>
+      <c r="B110" s="6">
         <v>24</v>
       </c>
       <c r="C110" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>998</v>
-      </c>
-      <c r="B111" s="7">
+        <v>997</v>
+      </c>
+      <c r="B111" s="6">
         <v>21</v>
       </c>
       <c r="C111" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>999</v>
-      </c>
-      <c r="B112" s="7">
+        <v>998</v>
+      </c>
+      <c r="B112" s="6">
         <v>20</v>
       </c>
       <c r="C112" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B113" s="7">
+        <v>999</v>
+      </c>
+      <c r="B113" s="6">
         <v>20</v>
       </c>
       <c r="C113" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B114" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B114" s="6">
         <v>18</v>
       </c>
       <c r="C114" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B115" s="7">
+        <v>1001</v>
+      </c>
+      <c r="B115" s="6">
         <v>17.5</v>
       </c>
       <c r="C115" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>989</v>
-      </c>
-      <c r="B116" s="7">
+        <v>988</v>
+      </c>
+      <c r="B116" s="6">
         <v>16</v>
       </c>
       <c r="C116" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B117" s="7">
+        <v>1002</v>
+      </c>
+      <c r="B117" s="6">
         <v>15</v>
       </c>
       <c r="C117" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B118" s="7">
+        <v>1003</v>
+      </c>
+      <c r="B118" s="6">
         <v>15</v>
       </c>
       <c r="C118" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>978</v>
-      </c>
-      <c r="B119" s="7">
+        <v>977</v>
+      </c>
+      <c r="B119" s="6">
         <v>15</v>
       </c>
       <c r="C119" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B120" s="7">
+        <v>1005</v>
+      </c>
+      <c r="B120" s="6">
         <v>15</v>
       </c>
       <c r="C120" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B121" s="7">
+        <v>1006</v>
+      </c>
+      <c r="B121" s="6">
         <v>14</v>
       </c>
       <c r="C121" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B122" s="6">
+        <v>11</v>
+      </c>
+      <c r="C122" t="s">
         <v>1008</v>
-      </c>
-      <c r="B122" s="7">
-        <v>11</v>
-      </c>
-      <c r="C122" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>961</v>
-      </c>
-      <c r="B123" s="7">
+        <v>960</v>
+      </c>
+      <c r="B123" s="6">
         <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B124" s="7">
+        <v>1009</v>
+      </c>
+      <c r="B124" s="6">
         <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>959</v>
-      </c>
-      <c r="B125" s="7">
+        <v>958</v>
+      </c>
+      <c r="B125" s="6">
         <v>7</v>
       </c>
       <c r="C125" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B126" s="7">
+        <v>1007</v>
+      </c>
+      <c r="B126" s="6">
         <v>6</v>
       </c>
       <c r="C126" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B127" s="7">
+        <v>1012</v>
+      </c>
+      <c r="B127" s="6">
         <v>5</v>
       </c>
       <c r="C127" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B128" s="7">
+        <v>1013</v>
+      </c>
+      <c r="B128" s="6">
         <v>5</v>
       </c>
       <c r="C128" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>954</v>
-      </c>
-      <c r="B129" s="7">
+        <v>953</v>
+      </c>
+      <c r="B129" s="6">
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>998</v>
-      </c>
-      <c r="B130" s="7">
+        <v>997</v>
+      </c>
+      <c r="B130" s="6">
         <v>3</v>
       </c>
       <c r="C130" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B131" s="7">
+        <v>1014</v>
+      </c>
+      <c r="B131" s="6">
         <v>3</v>
       </c>
       <c r="C131" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B132" s="7">
+        <v>1015</v>
+      </c>
+      <c r="B132" s="6">
         <v>2.5</v>
       </c>
       <c r="C132" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B133" s="7">
+        <v>1016</v>
+      </c>
+      <c r="B133" s="6">
         <v>2</v>
       </c>
       <c r="C133" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>954</v>
-      </c>
-      <c r="B134" s="7">
+        <v>953</v>
+      </c>
+      <c r="B134" s="6">
         <v>2</v>
       </c>
       <c r="C134" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B135" s="7">
+        <v>1018</v>
+      </c>
+      <c r="B135" s="6">
         <v>2</v>
       </c>
       <c r="C135" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B136" s="7">
+        <v>1019</v>
+      </c>
+      <c r="B136" s="6">
         <v>2</v>
       </c>
       <c r="C136" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B137" s="7">
+        <v>1020</v>
+      </c>
+      <c r="B137" s="6">
         <v>2</v>
       </c>
       <c r="C137" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B138" s="6">
+        <v>2</v>
+      </c>
+      <c r="C138" t="s">
         <v>1022</v>
-      </c>
-      <c r="B138" s="7">
-        <v>2</v>
-      </c>
-      <c r="C138" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B139" s="7">
+        <v>1023</v>
+      </c>
+      <c r="B139" s="6">
         <v>1</v>
       </c>
       <c r="C139" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>1025</v>
-      </c>
-      <c r="B140" s="7">
+        <v>1024</v>
+      </c>
+      <c r="B140" s="6">
         <v>1</v>
       </c>
       <c r="C140" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>972</v>
-      </c>
-      <c r="B141" s="7">
+        <v>971</v>
+      </c>
+      <c r="B141" s="6">
         <v>1</v>
       </c>
       <c r="C141" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B142" s="7">
+        <v>1012</v>
+      </c>
+      <c r="B142" s="6">
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
   </sheetData>
@@ -9824,986 +10287,986 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>1030</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>1031</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1033</v>
-      </c>
-      <c r="B5" s="12">
+        <v>1032</v>
+      </c>
+      <c r="B5" s="11">
         <v>57497.5</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <f>B5/1000</f>
         <v>57.497500000000002</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <f>B5/700</f>
         <v>82.13928571428572</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1034</v>
-      </c>
-      <c r="B6" s="12">
+        <v>1033</v>
+      </c>
+      <c r="B6" s="11">
         <v>21048</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <f>B6/1000</f>
         <v>21.047999999999998</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <f>B6/700</f>
         <v>30.068571428571428</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B7" s="12">
+        <v>1034</v>
+      </c>
+      <c r="B7" s="11">
         <v>17360</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <f>B7/1000</f>
         <v>17.36</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <f>B7/700</f>
         <v>24.8</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B8" s="12">
+        <v>1035</v>
+      </c>
+      <c r="B8" s="11">
         <v>0</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="13">
         <f>B8/1000</f>
         <v>0</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <f>B8/700</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B9" s="13">
+      <c r="A9" s="10" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B9" s="12">
         <f>SUM(B5:B8)</f>
         <v>95905.5</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="14">
         <f>B9/1000</f>
         <v>95.905500000000004</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <f>B9/700</f>
         <v>137.00785714285715</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>1033</v>
+      <c r="A11" s="9" t="s">
+        <v>1032</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>880</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>882</v>
+      <c r="A12" s="15" t="s">
+        <v>879</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>886</v>
-      </c>
-      <c r="B13" s="7">
+        <v>885</v>
+      </c>
+      <c r="B13" s="6">
         <v>22740</v>
       </c>
       <c r="C13" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>888</v>
-      </c>
-      <c r="B14" s="7">
+        <v>887</v>
+      </c>
+      <c r="B14" s="6">
         <v>10950</v>
       </c>
       <c r="C14" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>894</v>
-      </c>
-      <c r="B15" s="7">
+        <v>893</v>
+      </c>
+      <c r="B15" s="6">
         <v>4395</v>
       </c>
       <c r="C15" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>897</v>
-      </c>
-      <c r="B16" s="7">
+        <v>896</v>
+      </c>
+      <c r="B16" s="6">
         <v>3660</v>
       </c>
       <c r="C16" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>898</v>
-      </c>
-      <c r="B17" s="7">
+        <v>897</v>
+      </c>
+      <c r="B17" s="6">
         <v>3200</v>
       </c>
       <c r="C17" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>900</v>
-      </c>
-      <c r="B18" s="7">
+        <v>899</v>
+      </c>
+      <c r="B18" s="6">
         <v>2765</v>
       </c>
       <c r="C18" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>905</v>
-      </c>
-      <c r="B19" s="7">
+        <v>904</v>
+      </c>
+      <c r="B19" s="6">
         <v>1895</v>
       </c>
       <c r="C19" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>908</v>
-      </c>
-      <c r="B20" s="7">
+        <v>907</v>
+      </c>
+      <c r="B20" s="6">
         <v>1215</v>
       </c>
       <c r="C20" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>910</v>
-      </c>
-      <c r="B21" s="7">
+        <v>909</v>
+      </c>
+      <c r="B21" s="6">
         <v>1010</v>
       </c>
       <c r="C21" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>912</v>
-      </c>
-      <c r="B22" s="7">
+        <v>911</v>
+      </c>
+      <c r="B22" s="6">
         <v>840</v>
       </c>
       <c r="C22" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>913</v>
-      </c>
-      <c r="B23" s="7">
+        <v>912</v>
+      </c>
+      <c r="B23" s="6">
         <v>780</v>
       </c>
       <c r="C23" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>915</v>
-      </c>
-      <c r="B24" s="7">
+        <v>914</v>
+      </c>
+      <c r="B24" s="6">
         <v>730</v>
       </c>
       <c r="C24" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>924</v>
-      </c>
-      <c r="B25" s="7">
+        <v>923</v>
+      </c>
+      <c r="B25" s="6">
         <v>495</v>
       </c>
       <c r="C25" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>926</v>
-      </c>
-      <c r="B26" s="7">
+        <v>925</v>
+      </c>
+      <c r="B26" s="6">
         <v>450</v>
       </c>
       <c r="C26" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>929</v>
-      </c>
-      <c r="B27" s="7">
+        <v>928</v>
+      </c>
+      <c r="B27" s="6">
         <v>345</v>
       </c>
       <c r="C27" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>934</v>
-      </c>
-      <c r="B28" s="7">
+        <v>933</v>
+      </c>
+      <c r="B28" s="6">
         <v>285</v>
       </c>
       <c r="C28" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>935</v>
-      </c>
-      <c r="B29" s="7">
+        <v>934</v>
+      </c>
+      <c r="B29" s="6">
         <v>265</v>
       </c>
       <c r="C29" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>939</v>
-      </c>
-      <c r="B30" s="7">
+        <v>938</v>
+      </c>
+      <c r="B30" s="6">
         <v>240</v>
       </c>
       <c r="C30" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>943</v>
-      </c>
-      <c r="B31" s="7">
+        <v>942</v>
+      </c>
+      <c r="B31" s="6">
         <v>210</v>
       </c>
       <c r="C31" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>946</v>
-      </c>
-      <c r="B32" s="7">
+        <v>945</v>
+      </c>
+      <c r="B32" s="6">
         <v>180</v>
       </c>
       <c r="C32" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>947</v>
-      </c>
-      <c r="B33" s="7">
+        <v>946</v>
+      </c>
+      <c r="B33" s="6">
         <v>180</v>
       </c>
       <c r="C33" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>948</v>
-      </c>
-      <c r="B34" s="7">
+        <v>947</v>
+      </c>
+      <c r="B34" s="6">
         <v>180</v>
       </c>
       <c r="C34" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>965</v>
-      </c>
-      <c r="B35" s="7">
+        <v>964</v>
+      </c>
+      <c r="B35" s="6">
         <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>968</v>
-      </c>
-      <c r="B36" s="7">
+        <v>967</v>
+      </c>
+      <c r="B36" s="6">
         <v>120</v>
       </c>
       <c r="C36" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>979</v>
-      </c>
-      <c r="B37" s="7">
+        <v>978</v>
+      </c>
+      <c r="B37" s="6">
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>980</v>
-      </c>
-      <c r="B38" s="7">
+        <v>979</v>
+      </c>
+      <c r="B38" s="6">
         <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>981</v>
-      </c>
-      <c r="B39" s="7">
+        <v>980</v>
+      </c>
+      <c r="B39" s="6">
         <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>989</v>
-      </c>
-      <c r="B40" s="7">
+        <v>988</v>
+      </c>
+      <c r="B40" s="6">
         <v>32.5</v>
       </c>
       <c r="C40" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B41" s="7">
+        <v>999</v>
+      </c>
+      <c r="B41" s="6">
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B42" s="7">
+        <v>1003</v>
+      </c>
+      <c r="B42" s="6">
         <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>989</v>
-      </c>
-      <c r="B43" s="7">
+        <v>988</v>
+      </c>
+      <c r="B43" s="6">
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="10" t="s">
-        <v>1034</v>
+      <c r="A45" s="9" t="s">
+        <v>1033</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
-        <v>880</v>
-      </c>
-      <c r="B46" s="16" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>882</v>
+      <c r="A46" s="15" t="s">
+        <v>879</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>895</v>
-      </c>
-      <c r="B47" s="7">
+        <v>894</v>
+      </c>
+      <c r="B47" s="6">
         <v>4110</v>
       </c>
       <c r="C47" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>896</v>
-      </c>
-      <c r="B48" s="7">
+        <v>895</v>
+      </c>
+      <c r="B48" s="6">
         <v>4080</v>
       </c>
       <c r="C48" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>899</v>
-      </c>
-      <c r="B49" s="7">
+        <v>898</v>
+      </c>
+      <c r="B49" s="6">
         <v>3165</v>
       </c>
       <c r="C49" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>902</v>
-      </c>
-      <c r="B50" s="7">
+        <v>901</v>
+      </c>
+      <c r="B50" s="6">
         <v>2185</v>
       </c>
       <c r="C50" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>904</v>
-      </c>
-      <c r="B51" s="7">
+        <v>903</v>
+      </c>
+      <c r="B51" s="6">
         <v>1925</v>
       </c>
       <c r="C51" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>919</v>
-      </c>
-      <c r="B52" s="7">
+        <v>918</v>
+      </c>
+      <c r="B52" s="6">
         <v>540</v>
       </c>
       <c r="C52" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>921</v>
-      </c>
-      <c r="B53" s="7">
+        <v>920</v>
+      </c>
+      <c r="B53" s="6">
         <v>525</v>
       </c>
       <c r="C53" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>922</v>
-      </c>
-      <c r="B54" s="7">
+        <v>921</v>
+      </c>
+      <c r="B54" s="6">
         <v>524</v>
       </c>
       <c r="C54" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>923</v>
-      </c>
-      <c r="B55" s="7">
+        <v>922</v>
+      </c>
+      <c r="B55" s="6">
         <v>495</v>
       </c>
       <c r="C55" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>925</v>
-      </c>
-      <c r="B56" s="7">
+        <v>924</v>
+      </c>
+      <c r="B56" s="6">
         <v>490</v>
       </c>
       <c r="C56" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>927</v>
-      </c>
-      <c r="B57" s="7">
+        <v>926</v>
+      </c>
+      <c r="B57" s="6">
         <v>450</v>
       </c>
       <c r="C57" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>930</v>
-      </c>
-      <c r="B58" s="7">
+        <v>929</v>
+      </c>
+      <c r="B58" s="6">
         <v>330</v>
       </c>
       <c r="C58" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>938</v>
-      </c>
-      <c r="B59" s="7">
+        <v>937</v>
+      </c>
+      <c r="B59" s="6">
         <v>245</v>
       </c>
       <c r="C59" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>941</v>
-      </c>
-      <c r="B60" s="7">
+        <v>940</v>
+      </c>
+      <c r="B60" s="6">
         <v>240</v>
       </c>
       <c r="C60" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>942</v>
-      </c>
-      <c r="B61" s="7">
+        <v>941</v>
+      </c>
+      <c r="B61" s="6">
         <v>210</v>
       </c>
       <c r="C61" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>944</v>
-      </c>
-      <c r="B62" s="7">
+        <v>943</v>
+      </c>
+      <c r="B62" s="6">
         <v>200</v>
       </c>
       <c r="C62" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>945</v>
-      </c>
-      <c r="B63" s="7">
+        <v>944</v>
+      </c>
+      <c r="B63" s="6">
         <v>194</v>
       </c>
       <c r="C63" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>949</v>
-      </c>
-      <c r="B64" s="7">
+        <v>948</v>
+      </c>
+      <c r="B64" s="6">
         <v>180</v>
       </c>
       <c r="C64" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>951</v>
-      </c>
-      <c r="B65" s="7">
+        <v>950</v>
+      </c>
+      <c r="B65" s="6">
         <v>170</v>
       </c>
       <c r="C65" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>953</v>
-      </c>
-      <c r="B66" s="7">
+        <v>952</v>
+      </c>
+      <c r="B66" s="6">
         <v>155</v>
       </c>
       <c r="C66" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>967</v>
-      </c>
-      <c r="B67" s="7">
+        <v>966</v>
+      </c>
+      <c r="B67" s="6">
         <v>120</v>
       </c>
       <c r="C67" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>969</v>
-      </c>
-      <c r="B68" s="7">
+        <v>968</v>
+      </c>
+      <c r="B68" s="6">
         <v>105</v>
       </c>
       <c r="C68" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>974</v>
-      </c>
-      <c r="B69" s="7">
+        <v>973</v>
+      </c>
+      <c r="B69" s="6">
         <v>90</v>
       </c>
       <c r="C69" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>975</v>
-      </c>
-      <c r="B70" s="7">
+        <v>974</v>
+      </c>
+      <c r="B70" s="6">
         <v>90</v>
       </c>
       <c r="C70" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>977</v>
-      </c>
-      <c r="B71" s="7">
+        <v>976</v>
+      </c>
+      <c r="B71" s="6">
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>987</v>
-      </c>
-      <c r="B72" s="7">
+        <v>986</v>
+      </c>
+      <c r="B72" s="6">
         <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>991</v>
-      </c>
-      <c r="B73" s="7">
+        <v>990</v>
+      </c>
+      <c r="B73" s="6">
         <v>30</v>
       </c>
       <c r="C73" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>992</v>
-      </c>
-      <c r="B74" s="7">
+        <v>991</v>
+      </c>
+      <c r="B74" s="6">
         <v>30</v>
       </c>
       <c r="C74" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>999</v>
-      </c>
-      <c r="B75" s="7">
+        <v>998</v>
+      </c>
+      <c r="B75" s="6">
         <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B76" s="7">
+        <v>1002</v>
+      </c>
+      <c r="B76" s="6">
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B77" s="7">
+        <v>1005</v>
+      </c>
+      <c r="B77" s="6">
         <v>15</v>
       </c>
       <c r="C77" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A79" s="10" t="s">
-        <v>1035</v>
+      <c r="A79" s="9" t="s">
+        <v>1034</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" s="16" t="s">
-        <v>880</v>
-      </c>
-      <c r="B80" s="16" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C80" s="16" t="s">
-        <v>882</v>
+      <c r="A80" s="15" t="s">
+        <v>879</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>887</v>
-      </c>
-      <c r="B81" s="7">
+        <v>886</v>
+      </c>
+      <c r="B81" s="6">
         <v>12510</v>
       </c>
       <c r="C81" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>901</v>
-      </c>
-      <c r="B82" s="7">
+        <v>900</v>
+      </c>
+      <c r="B82" s="6">
         <v>2265</v>
       </c>
       <c r="C82" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>907</v>
-      </c>
-      <c r="B83" s="7">
+        <v>906</v>
+      </c>
+      <c r="B83" s="6">
         <v>1300</v>
       </c>
       <c r="C83" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>911</v>
-      </c>
-      <c r="B84" s="7">
+        <v>910</v>
+      </c>
+      <c r="B84" s="6">
         <v>945</v>
       </c>
       <c r="C84" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>950</v>
-      </c>
-      <c r="B85" s="7">
+        <v>949</v>
+      </c>
+      <c r="B85" s="6">
         <v>175</v>
       </c>
       <c r="C85" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>966</v>
-      </c>
-      <c r="B86" s="7">
+        <v>965</v>
+      </c>
+      <c r="B86" s="6">
         <v>120</v>
       </c>
       <c r="C86" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>986</v>
-      </c>
-      <c r="B87" s="7">
+        <v>985</v>
+      </c>
+      <c r="B87" s="6">
         <v>45</v>
       </c>
       <c r="C87" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="10" t="s">
-        <v>1036</v>
+      <c r="A89" s="9" t="s">
+        <v>1035</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="16" t="s">
-        <v>880</v>
-      </c>
-      <c r="B90" s="16" t="s">
-        <v>1038</v>
-      </c>
-      <c r="C90" s="16" t="s">
-        <v>882</v>
+      <c r="A90" s="15" t="s">
+        <v>879</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>881</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>953</v>
+      </c>
+      <c r="B91" s="6">
+        <v>150</v>
+      </c>
+      <c r="C91" t="s">
         <v>954</v>
-      </c>
-      <c r="B91" s="7">
-        <v>150</v>
-      </c>
-      <c r="C91" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>990</v>
-      </c>
-      <c r="B92" s="7">
+        <v>989</v>
+      </c>
+      <c r="B92" s="6">
         <v>30</v>
       </c>
       <c r="C92" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B93" s="7">
+        <v>1000</v>
+      </c>
+      <c r="B93" s="6">
         <v>18</v>
       </c>
       <c r="C93" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>954</v>
-      </c>
-      <c r="B94" s="7">
+        <v>953</v>
+      </c>
+      <c r="B94" s="6">
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>954</v>
-      </c>
-      <c r="B95" s="7">
+        <v>953</v>
+      </c>
+      <c r="B95" s="6">
         <v>2</v>
       </c>
       <c r="C95" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
   </sheetData>

--- a/cocktail_source.xlsx
+++ b/cocktail_source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bainandcompany-my.sharepoint.com/personal/gregoire_baudry_bain_com/Documents/Documents/GitHub/Greg's Bar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{55666991-13C5-43F9-9A70-97D3BDF1EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B509AAA-35B8-4D19-BA96-4EBAC9316F9E}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{55666991-13C5-43F9-9A70-97D3BDF1EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFC334B9-9BBF-46B2-A231-1E967A94E028}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="1040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="1041">
   <si>
     <t>Abbey</t>
   </si>
@@ -3897,15 +3897,19 @@
 Celery Salt – 1 pinch
 Lime – 1 wedge</t>
   </si>
+  <si>
+    <t>ABV %</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.#"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0\%"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -4024,7 +4028,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4053,6 +4057,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4246,7 +4251,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
+  <wetp:taskpane dockstate="right" visibility="0" width="571" row="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -4268,7 +4273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F220"/>
+  <dimension ref="A1:G220"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4277,9 +4282,10 @@
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
     <col min="6" max="6" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>876</v>
       </c>
@@ -4298,8 +4304,11 @@
       <c r="F1" s="17" t="s">
         <v>1038</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G1" s="17" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -4318,8 +4327,11 @@
       <c r="F2" s="16">
         <v>21.4</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G2" s="18">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
@@ -4338,8 +4350,11 @@
       <c r="F3" s="16">
         <v>30.4</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G3" s="18">
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -4358,8 +4373,11 @@
       <c r="F4" s="16">
         <v>10.9</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G4" s="18">
+        <v>16.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
@@ -4378,8 +4396,11 @@
       <c r="F5" s="16">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G5" s="18">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -4398,8 +4419,11 @@
       <c r="F6" s="16">
         <v>27.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G6" s="18">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -4418,8 +4442,11 @@
       <c r="F7" s="16">
         <v>30</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G7" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
@@ -4438,8 +4465,11 @@
       <c r="F8" s="16">
         <v>16.600000000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G8" s="18">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -4458,8 +4488,11 @@
       <c r="F9" s="16">
         <v>29.4</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G9" s="18">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
@@ -4478,8 +4511,11 @@
       <c r="F10" s="16">
         <v>16.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G10" s="18">
+        <v>18.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
@@ -4498,8 +4534,11 @@
       <c r="F11" s="16">
         <v>36</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G11" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>31</v>
       </c>
@@ -4518,8 +4557,11 @@
       <c r="F12" s="16">
         <v>30</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G12" s="18">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>34</v>
       </c>
@@ -4538,8 +4580,11 @@
       <c r="F13" s="16">
         <v>18.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G13" s="18">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
@@ -4558,8 +4603,11 @@
       <c r="F14" s="16">
         <v>13.4</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G14" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>40</v>
       </c>
@@ -4578,8 +4626,11 @@
       <c r="F15" s="16">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G15" s="18">
+        <v>36.700000000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>43</v>
       </c>
@@ -4598,8 +4649,11 @@
       <c r="F16" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G16" s="18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>46</v>
       </c>
@@ -4618,8 +4672,11 @@
       <c r="F17" s="16">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G17" s="18">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>49</v>
       </c>
@@ -4638,8 +4695,11 @@
       <c r="F18" s="16">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G18" s="18">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>52</v>
       </c>
@@ -4658,8 +4718,11 @@
       <c r="F19" s="16">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="G19" s="18">
+        <v>8.8000000000000007</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>861</v>
       </c>
@@ -4678,8 +4741,11 @@
       <c r="F20" s="16">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G20" s="18">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>858</v>
       </c>
@@ -4698,8 +4764,11 @@
       <c r="F21" s="16">
         <v>26.4</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G21" s="18">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>850</v>
       </c>
@@ -4718,8 +4787,11 @@
       <c r="F22" s="16">
         <v>18.600000000000001</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G22" s="18">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>55</v>
       </c>
@@ -4738,8 +4810,11 @@
       <c r="F23" s="16">
         <v>15.6</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G23" s="18">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>854</v>
       </c>
@@ -4758,8 +4833,11 @@
       <c r="F24" s="16">
         <v>17</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G24" s="18">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>58</v>
       </c>
@@ -4778,8 +4856,11 @@
       <c r="F25" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G25" s="18">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>61</v>
       </c>
@@ -4798,8 +4879,11 @@
       <c r="F26" s="16">
         <v>24.5</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G26" s="18">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>64</v>
       </c>
@@ -4818,8 +4902,11 @@
       <c r="F27" s="16">
         <v>23.1</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G27" s="18">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>67</v>
       </c>
@@ -4838,8 +4925,11 @@
       <c r="F28" s="16">
         <v>30</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G28" s="18">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>70</v>
       </c>
@@ -4858,8 +4948,11 @@
       <c r="F29" s="16">
         <v>22.2</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G29" s="18">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>73</v>
       </c>
@@ -4878,8 +4971,11 @@
       <c r="F30" s="16">
         <v>23.8</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G30" s="18">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>76</v>
       </c>
@@ -4898,8 +4994,11 @@
       <c r="F31" s="16">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G31" s="18">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>79</v>
       </c>
@@ -4918,8 +5017,11 @@
       <c r="F32" s="16">
         <v>30</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G32" s="18">
+        <v>33.299999999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>82</v>
       </c>
@@ -4938,8 +5040,11 @@
       <c r="F33" s="16">
         <v>28.8</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="G33" s="18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>85</v>
       </c>
@@ -4958,8 +5063,11 @@
       <c r="F34" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G34" s="18">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>88</v>
       </c>
@@ -4978,8 +5086,11 @@
       <c r="F35" s="16">
         <v>20.3</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G35" s="18">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>91</v>
       </c>
@@ -4998,8 +5109,11 @@
       <c r="F36" s="16">
         <v>27.2</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G36" s="18">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>94</v>
       </c>
@@ -5018,8 +5132,11 @@
       <c r="F37" s="16">
         <v>12.6</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G37" s="18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>97</v>
       </c>
@@ -5038,8 +5155,11 @@
       <c r="F38" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G38" s="18">
+        <v>34.299999999999997</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>100</v>
       </c>
@@ -5058,8 +5178,11 @@
       <c r="F39" s="16">
         <v>30.3</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G39" s="18">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>103</v>
       </c>
@@ -5078,8 +5201,11 @@
       <c r="F40" s="16">
         <v>30.3</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G40" s="18">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>106</v>
       </c>
@@ -5098,8 +5224,11 @@
       <c r="F41" s="16">
         <v>31.4</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G41" s="18">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>109</v>
       </c>
@@ -5118,8 +5247,11 @@
       <c r="F42" s="16">
         <v>25.5</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G42" s="18">
+        <v>37.799999999999997</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>112</v>
       </c>
@@ -5138,8 +5270,11 @@
       <c r="F43" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G43" s="18">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>115</v>
       </c>
@@ -5158,8 +5293,11 @@
       <c r="F44" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G44" s="18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>118</v>
       </c>
@@ -5178,8 +5316,11 @@
       <c r="F45" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G45" s="18">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>121</v>
       </c>
@@ -5198,8 +5339,11 @@
       <c r="F46" s="16">
         <v>29.1</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G46" s="18">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>124</v>
       </c>
@@ -5218,8 +5362,11 @@
       <c r="F47" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G47" s="18">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>127</v>
       </c>
@@ -5238,8 +5385,11 @@
       <c r="F48" s="16">
         <v>15.8</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G48" s="18">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>130</v>
       </c>
@@ -5258,8 +5408,11 @@
       <c r="F49" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G49" s="18">
+        <v>26.9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>133</v>
       </c>
@@ -5278,8 +5431,11 @@
       <c r="F50" s="16">
         <v>33</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G50" s="18">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>136</v>
       </c>
@@ -5298,8 +5454,11 @@
       <c r="F51" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G51" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>139</v>
       </c>
@@ -5318,8 +5477,11 @@
       <c r="F52" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G52" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>142</v>
       </c>
@@ -5338,8 +5500,11 @@
       <c r="F53" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G53" s="18">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>145</v>
       </c>
@@ -5358,8 +5523,11 @@
       <c r="F54" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="G54" s="18">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>148</v>
       </c>
@@ -5378,8 +5546,11 @@
       <c r="F55" s="16">
         <v>31.2</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G55" s="18">
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>151</v>
       </c>
@@ -5398,8 +5569,11 @@
       <c r="F56" s="16">
         <v>15</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G56" s="18">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>154</v>
       </c>
@@ -5418,8 +5592,11 @@
       <c r="F57" s="16">
         <v>26.8</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G57" s="18">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>157</v>
       </c>
@@ -5438,8 +5615,11 @@
       <c r="F58" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G58" s="18">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>160</v>
       </c>
@@ -5458,8 +5638,11 @@
       <c r="F59" s="16">
         <v>22.8</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G59" s="18">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>163</v>
       </c>
@@ -5478,8 +5661,11 @@
       <c r="F60" s="16">
         <v>26.1</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G60" s="18">
+        <v>26.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>166</v>
       </c>
@@ -5498,8 +5684,11 @@
       <c r="F61" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G61" s="18">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>169</v>
       </c>
@@ -5518,8 +5707,11 @@
       <c r="F62" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G62" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>172</v>
       </c>
@@ -5538,8 +5730,11 @@
       <c r="F63" s="16">
         <v>27</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G63" s="18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>175</v>
       </c>
@@ -5558,8 +5753,11 @@
       <c r="F64" s="16">
         <v>16.8</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G64" s="18">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>178</v>
       </c>
@@ -5578,8 +5776,11 @@
       <c r="F65" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G65" s="18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>181</v>
       </c>
@@ -5598,8 +5799,11 @@
       <c r="F66" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G66" s="18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>184</v>
       </c>
@@ -5618,8 +5822,11 @@
       <c r="F67" s="16">
         <v>19.399999999999999</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G67" s="18">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>187</v>
       </c>
@@ -5638,8 +5845,11 @@
       <c r="F68" s="16">
         <v>30</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G68" s="18">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>190</v>
       </c>
@@ -5658,8 +5868,11 @@
       <c r="F69" s="16">
         <v>27</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G69" s="18">
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>193</v>
       </c>
@@ -5678,8 +5891,11 @@
       <c r="F70" s="16">
         <v>16.899999999999999</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G70" s="18">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>196</v>
       </c>
@@ -5698,8 +5914,11 @@
       <c r="F71" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G71" s="18">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>199</v>
       </c>
@@ -5718,8 +5937,11 @@
       <c r="F72" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G72" s="18">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>202</v>
       </c>
@@ -5738,8 +5960,11 @@
       <c r="F73" s="16">
         <v>16.399999999999999</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G73" s="18">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>205</v>
       </c>
@@ -5758,8 +5983,11 @@
       <c r="F74" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G74" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>208</v>
       </c>
@@ -5778,8 +6006,11 @@
       <c r="F75" s="16">
         <v>31.6</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G75" s="18">
+        <v>18.600000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>211</v>
       </c>
@@ -5798,8 +6029,11 @@
       <c r="F76" s="16">
         <v>18.899999999999999</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G76" s="18">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>215</v>
       </c>
@@ -5818,8 +6052,11 @@
       <c r="F77" s="16">
         <v>34</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G77" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>218</v>
       </c>
@@ -5838,8 +6075,11 @@
       <c r="F78" s="16">
         <v>15.3</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G78" s="18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>221</v>
       </c>
@@ -5858,8 +6098,11 @@
       <c r="F79" s="16">
         <v>19</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G79" s="18">
+        <v>22.4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>224</v>
       </c>
@@ -5878,8 +6121,11 @@
       <c r="F80" s="16">
         <v>35.4</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G80" s="18">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>227</v>
       </c>
@@ -5898,8 +6144,11 @@
       <c r="F81" s="16">
         <v>24.5</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G81" s="18">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>230</v>
       </c>
@@ -5918,8 +6167,11 @@
       <c r="F82" s="16">
         <v>20</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G82" s="18">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>233</v>
       </c>
@@ -5938,8 +6190,11 @@
       <c r="F83" s="16">
         <v>30</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G83" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>236</v>
       </c>
@@ -5958,8 +6213,11 @@
       <c r="F84" s="16">
         <v>30</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G84" s="18">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>239</v>
       </c>
@@ -5978,8 +6236,11 @@
       <c r="F85" s="16">
         <v>28.8</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G85" s="18">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>242</v>
       </c>
@@ -5998,8 +6259,11 @@
       <c r="F86" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G86" s="18">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>245</v>
       </c>
@@ -6018,8 +6282,11 @@
       <c r="F87" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G87" s="18">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>248</v>
       </c>
@@ -6038,8 +6305,11 @@
       <c r="F88" s="16">
         <v>14.3</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G88" s="18">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>251</v>
       </c>
@@ -6058,8 +6328,11 @@
       <c r="F89" s="16">
         <v>25.4</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G89" s="18">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>254</v>
       </c>
@@ -6078,8 +6351,11 @@
       <c r="F90" s="16">
         <v>18.2</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G90" s="18">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>257</v>
       </c>
@@ -6098,8 +6374,11 @@
       <c r="F91" s="16">
         <v>18.399999999999999</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G91" s="18">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>260</v>
       </c>
@@ -6118,8 +6397,11 @@
       <c r="F92" s="16">
         <v>19.2</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G92" s="18">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>263</v>
       </c>
@@ -6138,8 +6420,11 @@
       <c r="F93" s="16">
         <v>24.8</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G93" s="18">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>266</v>
       </c>
@@ -6158,8 +6443,11 @@
       <c r="F94" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G94" s="18">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>269</v>
       </c>
@@ -6178,8 +6466,11 @@
       <c r="F95" s="16">
         <v>19.8</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G95" s="18">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>636</v>
       </c>
@@ -6198,8 +6489,11 @@
       <c r="F96" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G96" s="18">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>272</v>
       </c>
@@ -6218,8 +6512,11 @@
       <c r="F97" s="16">
         <v>16</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G97" s="18">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>275</v>
       </c>
@@ -6238,8 +6535,11 @@
       <c r="F98" s="16">
         <v>14</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G98" s="18">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>278</v>
       </c>
@@ -6258,8 +6558,11 @@
       <c r="F99" s="16">
         <v>32.4</v>
       </c>
-    </row>
-    <row r="100" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G99" s="18">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>281</v>
       </c>
@@ -6278,8 +6581,11 @@
       <c r="F100" s="16">
         <v>32.4</v>
       </c>
-    </row>
-    <row r="101" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G100" s="18">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>284</v>
       </c>
@@ -6298,8 +6604,11 @@
       <c r="F101" s="16">
         <v>20</v>
       </c>
-    </row>
-    <row r="102" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G101" s="18">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>287</v>
       </c>
@@ -6318,8 +6627,11 @@
       <c r="F102" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G102" s="18">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>290</v>
       </c>
@@ -6338,8 +6650,11 @@
       <c r="F103" s="16">
         <v>18.399999999999999</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G103" s="18">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>293</v>
       </c>
@@ -6358,8 +6673,11 @@
       <c r="F104" s="16">
         <v>28.8</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G104" s="18">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>296</v>
       </c>
@@ -6378,8 +6696,11 @@
       <c r="F105" s="16">
         <v>22.5</v>
       </c>
-    </row>
-    <row r="106" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G105" s="18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>299</v>
       </c>
@@ -6398,8 +6719,11 @@
       <c r="F106" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="107" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G106" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>302</v>
       </c>
@@ -6418,8 +6742,11 @@
       <c r="F107" s="16">
         <v>15.2</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G107" s="18">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>305</v>
       </c>
@@ -6438,8 +6765,11 @@
       <c r="F108" s="16">
         <v>17.100000000000001</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G108" s="18">
+        <v>27.6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>308</v>
       </c>
@@ -6458,8 +6788,11 @@
       <c r="F109" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="110" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G109" s="18">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>311</v>
       </c>
@@ -6478,8 +6811,11 @@
       <c r="F110" s="16">
         <v>33.299999999999997</v>
       </c>
-    </row>
-    <row r="111" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G110" s="18">
+        <v>27.7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>314</v>
       </c>
@@ -6498,8 +6834,11 @@
       <c r="F111" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G111" s="18">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>317</v>
       </c>
@@ -6518,8 +6857,11 @@
       <c r="F112" s="16">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="113" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G112" s="18">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>870</v>
       </c>
@@ -6538,8 +6880,11 @@
       <c r="F113" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="114" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G113" s="18">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>320</v>
       </c>
@@ -6558,8 +6903,11 @@
       <c r="F114" s="16">
         <v>29.2</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G114" s="18">
+        <v>29.2</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>323</v>
       </c>
@@ -6578,8 +6926,11 @@
       <c r="F115" s="16">
         <v>32</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G115" s="18">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>326</v>
       </c>
@@ -6598,8 +6949,11 @@
       <c r="F116" s="16">
         <v>20.6</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G116" s="18">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>329</v>
       </c>
@@ -6618,8 +6972,11 @@
       <c r="F117" s="16">
         <v>26</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G117" s="18">
+        <v>23.6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>332</v>
       </c>
@@ -6638,8 +6995,11 @@
       <c r="F118" s="16">
         <v>15</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G118" s="18">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>335</v>
       </c>
@@ -6658,8 +7018,11 @@
       <c r="F119" s="16">
         <v>33</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G119" s="18">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>338</v>
       </c>
@@ -6678,8 +7041,11 @@
       <c r="F120" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G120" s="18">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>341</v>
       </c>
@@ -6698,8 +7064,11 @@
       <c r="F121" s="16">
         <v>21</v>
       </c>
-    </row>
-    <row r="122" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G121" s="18">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>344</v>
       </c>
@@ -6718,8 +7087,11 @@
       <c r="F122" s="16">
         <v>19.2</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G122" s="18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>347</v>
       </c>
@@ -6738,8 +7110,11 @@
       <c r="F123" s="16">
         <v>32</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G123" s="18">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>350</v>
       </c>
@@ -6758,8 +7133,11 @@
       <c r="F124" s="16">
         <v>25.4</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G124" s="18">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>353</v>
       </c>
@@ -6778,8 +7156,11 @@
       <c r="F125" s="16">
         <v>31.5</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G125" s="18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>356</v>
       </c>
@@ -6798,8 +7179,11 @@
       <c r="F126" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="G126" s="18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="120" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>359</v>
       </c>
@@ -6818,8 +7202,11 @@
       <c r="F127" s="16">
         <v>38</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G127" s="18">
+        <v>26.2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>362</v>
       </c>
@@ -6838,8 +7225,11 @@
       <c r="F128" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="129" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G128" s="18">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>365</v>
       </c>
@@ -6858,8 +7248,11 @@
       <c r="F129" s="16">
         <v>28.5</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G129" s="18">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>368</v>
       </c>
@@ -6878,8 +7271,11 @@
       <c r="F130" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G130" s="18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>371</v>
       </c>
@@ -6898,8 +7294,11 @@
       <c r="F131" s="16">
         <v>28.8</v>
       </c>
-    </row>
-    <row r="132" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G131" s="18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>374</v>
       </c>
@@ -6918,8 +7317,11 @@
       <c r="F132" s="16">
         <v>28.8</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G132" s="18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>377</v>
       </c>
@@ -6938,8 +7340,11 @@
       <c r="F133" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G133" s="18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>380</v>
       </c>
@@ -6958,8 +7363,11 @@
       <c r="F134" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="135" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G134" s="18">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>383</v>
       </c>
@@ -6978,8 +7386,11 @@
       <c r="F135" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G135" s="18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>386</v>
       </c>
@@ -6998,8 +7409,11 @@
       <c r="F136" s="16">
         <v>33.6</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G136" s="18">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>864</v>
       </c>
@@ -7018,8 +7432,11 @@
       <c r="F137" s="16">
         <v>23</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G137" s="18">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>389</v>
       </c>
@@ -7038,8 +7455,11 @@
       <c r="F138" s="16">
         <v>24.3</v>
       </c>
-    </row>
-    <row r="139" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="G138" s="18">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>392</v>
       </c>
@@ -7056,10 +7476,13 @@
         <v>393</v>
       </c>
       <c r="F139" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="G139" s="18">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>394</v>
       </c>
@@ -7078,8 +7501,11 @@
       <c r="F140" s="16">
         <v>24.6</v>
       </c>
-    </row>
-    <row r="141" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G140" s="18">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>397</v>
       </c>
@@ -7098,8 +7524,11 @@
       <c r="F141" s="16">
         <v>20.399999999999999</v>
       </c>
-    </row>
-    <row r="142" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G141" s="18">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>400</v>
       </c>
@@ -7118,8 +7547,11 @@
       <c r="F142" s="16">
         <v>12</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G142" s="18">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>403</v>
       </c>
@@ -7138,8 +7570,11 @@
       <c r="F143" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G143" s="18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>406</v>
       </c>
@@ -7158,8 +7593,11 @@
       <c r="F144" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="145" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G144" s="18">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>409</v>
       </c>
@@ -7178,8 +7616,11 @@
       <c r="F145" s="16">
         <v>35.1</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G145" s="18">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>412</v>
       </c>
@@ -7198,8 +7639,11 @@
       <c r="F146" s="16">
         <v>18.2</v>
       </c>
-    </row>
-    <row r="147" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G146" s="18">
+        <v>22.7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>415</v>
       </c>
@@ -7218,8 +7662,11 @@
       <c r="F147" s="16">
         <v>24.3</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G147" s="18">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>418</v>
       </c>
@@ -7238,8 +7685,11 @@
       <c r="F148" s="16">
         <v>15.9</v>
       </c>
-    </row>
-    <row r="149" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G148" s="18">
+        <v>17.7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>421</v>
       </c>
@@ -7258,8 +7708,11 @@
       <c r="F149" s="16">
         <v>24.3</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G149" s="18">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>424</v>
       </c>
@@ -7278,8 +7731,11 @@
       <c r="F150" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G150" s="18">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>427</v>
       </c>
@@ -7298,8 +7754,11 @@
       <c r="F151" s="16">
         <v>26.4</v>
       </c>
-    </row>
-    <row r="152" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G151" s="18">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>430</v>
       </c>
@@ -7318,8 +7777,11 @@
       <c r="F152" s="16">
         <v>12</v>
       </c>
-    </row>
-    <row r="153" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G152" s="18">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>433</v>
       </c>
@@ -7338,8 +7800,11 @@
       <c r="F153" s="16">
         <v>30</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G153" s="18">
+        <v>33.299999999999997</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>436</v>
       </c>
@@ -7358,8 +7823,11 @@
       <c r="F154" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G154" s="18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>439</v>
       </c>
@@ -7378,8 +7846,11 @@
       <c r="F155" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="156" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G155" s="18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>442</v>
       </c>
@@ -7398,8 +7869,11 @@
       <c r="F156" s="16">
         <v>27.2</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G156" s="18">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>445</v>
       </c>
@@ -7418,8 +7892,11 @@
       <c r="F157" s="16">
         <v>16.2</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G157" s="18">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>448</v>
       </c>
@@ -7438,8 +7915,11 @@
       <c r="F158" s="16">
         <v>20</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G158" s="18">
+        <v>23.5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>451</v>
       </c>
@@ -7458,8 +7938,11 @@
       <c r="F159" s="16">
         <v>5</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G159" s="18">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>454</v>
       </c>
@@ -7478,8 +7961,11 @@
       <c r="F160" s="16">
         <v>35.1</v>
       </c>
-    </row>
-    <row r="161" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G160" s="18">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>457</v>
       </c>
@@ -7498,8 +7984,11 @@
       <c r="F161" s="16">
         <v>15</v>
       </c>
-    </row>
-    <row r="162" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G161" s="18">
+        <v>7.7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>460</v>
       </c>
@@ -7518,8 +8007,11 @@
       <c r="F162" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="163" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G162" s="18">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>463</v>
       </c>
@@ -7538,8 +8030,11 @@
       <c r="F163" s="16">
         <v>25.9</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G163" s="18">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>466</v>
       </c>
@@ -7558,8 +8053,11 @@
       <c r="F164" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="165" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G164" s="18">
+        <v>33.299999999999997</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>469</v>
       </c>
@@ -7578,8 +8076,11 @@
       <c r="F165" s="16">
         <v>15.6</v>
       </c>
-    </row>
-    <row r="166" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G165" s="18">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>472</v>
       </c>
@@ -7598,8 +8099,11 @@
       <c r="F166" s="16">
         <v>16.100000000000001</v>
       </c>
-    </row>
-    <row r="167" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G166" s="18">
+        <v>18.899999999999999</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>475</v>
       </c>
@@ -7618,8 +8122,11 @@
       <c r="F167" s="16">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="168" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G167" s="18">
+        <v>10.8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>478</v>
       </c>
@@ -7638,8 +8145,11 @@
       <c r="F168" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G168" s="18">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>481</v>
       </c>
@@ -7658,8 +8168,11 @@
       <c r="F169" s="16">
         <v>21</v>
       </c>
-    </row>
-    <row r="170" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G169" s="18">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>484</v>
       </c>
@@ -7678,8 +8191,11 @@
       <c r="F170" s="16">
         <v>9</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G170" s="18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>487</v>
       </c>
@@ -7698,8 +8214,11 @@
       <c r="F171" s="16">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G171" s="18">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>490</v>
       </c>
@@ -7718,8 +8237,11 @@
       <c r="F172" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="173" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G172" s="18">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>493</v>
       </c>
@@ -7738,8 +8260,11 @@
       <c r="F173" s="16">
         <v>9</v>
       </c>
-    </row>
-    <row r="174" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G173" s="18">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>496</v>
       </c>
@@ -7758,8 +8283,11 @@
       <c r="F174" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G174" s="18">
+        <v>22.9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>499</v>
       </c>
@@ -7778,8 +8306,11 @@
       <c r="F175" s="16">
         <v>28.8</v>
       </c>
-    </row>
-    <row r="176" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G175" s="18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>502</v>
       </c>
@@ -7798,8 +8329,11 @@
       <c r="F176" s="16">
         <v>30.6</v>
       </c>
-    </row>
-    <row r="177" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G176" s="18">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>505</v>
       </c>
@@ -7818,8 +8352,11 @@
       <c r="F177" s="16">
         <v>32</v>
       </c>
-    </row>
-    <row r="178" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G177" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>508</v>
       </c>
@@ -7838,8 +8375,11 @@
       <c r="F178" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G178" s="18">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>511</v>
       </c>
@@ -7858,8 +8398,11 @@
       <c r="F179" s="16">
         <v>27.6</v>
       </c>
-    </row>
-    <row r="180" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G179" s="18">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>514</v>
       </c>
@@ -7878,8 +8421,11 @@
       <c r="F180" s="16">
         <v>21.8</v>
       </c>
-    </row>
-    <row r="181" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G180" s="18">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>517</v>
       </c>
@@ -7898,8 +8444,11 @@
       <c r="F181" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G181" s="18">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>520</v>
       </c>
@@ -7918,8 +8467,11 @@
       <c r="F182" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="183" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G182" s="18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>523</v>
       </c>
@@ -7938,8 +8490,11 @@
       <c r="F183" s="16">
         <v>32.4</v>
       </c>
-    </row>
-    <row r="184" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G183" s="18">
+        <v>19.600000000000001</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>526</v>
       </c>
@@ -7958,8 +8513,11 @@
       <c r="F184" s="16">
         <v>12</v>
       </c>
-    </row>
-    <row r="185" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G184" s="18">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>529</v>
       </c>
@@ -7978,8 +8536,11 @@
       <c r="F185" s="16">
         <v>33</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G185" s="18">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>532</v>
       </c>
@@ -7998,8 +8559,11 @@
       <c r="F186" s="16">
         <v>21.8</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G186" s="18">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>535</v>
       </c>
@@ -8018,8 +8582,11 @@
       <c r="F187" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="G187" s="18">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>538</v>
       </c>
@@ -8038,8 +8605,11 @@
       <c r="F188" s="16">
         <v>32</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G188" s="18">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>541</v>
       </c>
@@ -8058,8 +8628,11 @@
       <c r="F189" s="16">
         <v>16</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G189" s="18">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>544</v>
       </c>
@@ -8078,8 +8651,11 @@
       <c r="F190" s="16">
         <v>11.7</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G190" s="18">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>547</v>
       </c>
@@ -8098,8 +8674,11 @@
       <c r="F191" s="16">
         <v>25.7</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G191" s="18">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>550</v>
       </c>
@@ -8118,8 +8697,11 @@
       <c r="F192" s="16">
         <v>31.7</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G192" s="18">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>553</v>
       </c>
@@ -8138,8 +8720,11 @@
       <c r="F193" s="16">
         <v>11.6</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G193" s="18">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>556</v>
       </c>
@@ -8158,8 +8743,11 @@
       <c r="F194" s="16">
         <v>16.2</v>
       </c>
-    </row>
-    <row r="195" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G194" s="18">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>559</v>
       </c>
@@ -8178,8 +8766,11 @@
       <c r="F195" s="16">
         <v>21.3</v>
       </c>
-    </row>
-    <row r="196" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G195" s="18">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>562</v>
       </c>
@@ -8198,8 +8789,11 @@
       <c r="F196" s="16">
         <v>22.8</v>
       </c>
-    </row>
-    <row r="197" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G196" s="18">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>565</v>
       </c>
@@ -8218,8 +8812,11 @@
       <c r="F197" s="16">
         <v>13.5</v>
       </c>
-    </row>
-    <row r="198" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G197" s="18">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>568</v>
       </c>
@@ -8238,8 +8835,11 @@
       <c r="F198" s="16">
         <v>22.8</v>
       </c>
-    </row>
-    <row r="199" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G198" s="18">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>571</v>
       </c>
@@ -8258,8 +8858,11 @@
       <c r="F199" s="16">
         <v>36</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G199" s="18">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>574</v>
       </c>
@@ -8278,8 +8881,11 @@
       <c r="F200" s="16">
         <v>23</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G200" s="18">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>577</v>
       </c>
@@ -8298,8 +8904,11 @@
       <c r="F201" s="16">
         <v>36.1</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G201" s="18">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>580</v>
       </c>
@@ -8318,8 +8927,11 @@
       <c r="F202" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G202" s="18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>583</v>
       </c>
@@ -8338,8 +8950,11 @@
       <c r="F203" s="16">
         <v>28.5</v>
       </c>
-    </row>
-    <row r="204" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G203" s="18">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>586</v>
       </c>
@@ -8358,8 +8973,11 @@
       <c r="F204" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="205" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G204" s="18">
+        <v>35.799999999999997</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>589</v>
       </c>
@@ -8378,8 +8996,11 @@
       <c r="F205" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="206" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="G205" s="18">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>592</v>
       </c>
@@ -8398,8 +9019,11 @@
       <c r="F206" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G206" s="18">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>595</v>
       </c>
@@ -8418,8 +9042,11 @@
       <c r="F207" s="16">
         <v>21.8</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G207" s="18">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>598</v>
       </c>
@@ -8438,8 +9065,11 @@
       <c r="F208" s="16">
         <v>38.6</v>
       </c>
-    </row>
-    <row r="209" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="G208" s="18">
+        <v>36.799999999999997</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>601</v>
       </c>
@@ -8458,8 +9088,11 @@
       <c r="F209" s="16">
         <v>30.8</v>
       </c>
-    </row>
-    <row r="210" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G209" s="18">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>604</v>
       </c>
@@ -8478,8 +9111,11 @@
       <c r="F210" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="211" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G210" s="18">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>607</v>
       </c>
@@ -8498,8 +9134,11 @@
       <c r="F211" s="16">
         <v>33.6</v>
       </c>
-    </row>
-    <row r="212" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G211" s="18">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>610</v>
       </c>
@@ -8518,8 +9157,11 @@
       <c r="F212" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G212" s="18">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>613</v>
       </c>
@@ -8538,8 +9180,11 @@
       <c r="F213" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="214" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G213" s="18">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>616</v>
       </c>
@@ -8558,8 +9203,11 @@
       <c r="F214" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G214" s="18">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>619</v>
       </c>
@@ -8578,8 +9226,11 @@
       <c r="F215" s="16">
         <v>24</v>
       </c>
-    </row>
-    <row r="216" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="G215" s="18">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>625</v>
       </c>
@@ -8598,8 +9249,11 @@
       <c r="F216" s="16">
         <v>21.6</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G216" s="18">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>622</v>
       </c>
@@ -8618,8 +9272,11 @@
       <c r="F217" s="16">
         <v>21.9</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="G217" s="18">
+        <v>24.3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>628</v>
       </c>
@@ -8638,8 +9295,11 @@
       <c r="F218" s="16">
         <v>18</v>
       </c>
-    </row>
-    <row r="219" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G218" s="18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>630</v>
       </c>
@@ -8658,8 +9318,11 @@
       <c r="F219" s="16">
         <v>22.8</v>
       </c>
-    </row>
-    <row r="220" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="G219" s="18">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>633</v>
       </c>
@@ -8677,6 +9340,9 @@
       </c>
       <c r="F220" s="16">
         <v>28.9</v>
+      </c>
+      <c r="G220" s="18">
+        <v>32.1</v>
       </c>
     </row>
   </sheetData>
@@ -8684,6 +9350,7 @@
     <sortCondition ref="A2:A220"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/cocktail_source.xlsx
+++ b/cocktail_source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bainandcompany-my.sharepoint.com/personal/gregoire_baudry_bain_com/Documents/Documents/GitHub/Greg's Bar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{55666991-13C5-43F9-9A70-97D3BDF1EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFC334B9-9BBF-46B2-A231-1E967A94E028}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{55666991-13C5-43F9-9A70-97D3BDF1EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2DFFDEA-679F-4094-B2BF-766D95B9A464}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="1041">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="1037">
   <si>
     <t>Abbey</t>
   </si>
@@ -2332,18 +2332,6 @@
     <t>Spritz.jpg</t>
   </si>
   <si>
-    <t>St. Germain Cocktail</t>
-  </si>
-  <si>
-    <t>St. Germain – 45 ml
-Sparkling Wine – 60 ml
-Club Soda – 60 ml
-Lemon Peel – 1</t>
-  </si>
-  <si>
-    <t>St_Germain_Cocktail.jpg</t>
-  </si>
-  <si>
     <t>Sweet Basil #2</t>
   </si>
   <si>
@@ -3224,9 +3212,6 @@
   </si>
   <si>
     <t>An Italian wine-based cocktail commonly served as an aperitif in Northeast Italy. Prosecco, Aperol, and soda water combine in this light, refreshing, bittersweet drink now popular worldwide.</t>
-  </si>
-  <si>
-    <t>A refreshingly fizzy, flowery cocktail that highlights the delicate elderflower flavors of St. Germain liqueur. Sparkling wine and club soda add effervescence to this elegant, simple drink.</t>
   </si>
   <si>
     <t>A cocktail for basil lovers from Todd Thrasher of Restaurant Eve in Alexandria, Virginia. Lillet Blanc, gin, and basil syrup combine for a fragrant, herbaceous, and refreshing drink.</t>
@@ -4273,7 +4258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G220"/>
+  <dimension ref="A1:G219"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4287,25 +4272,25 @@
   <sheetData>
     <row r="1" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>874</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>878</v>
-      </c>
       <c r="F1" s="17" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="G1" s="17" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -4313,7 +4298,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -4336,7 +4321,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
@@ -4382,7 +4367,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
@@ -4405,7 +4390,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>14</v>
@@ -4428,7 +4413,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
@@ -4451,7 +4436,7 @@
         <v>19</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>20</v>
@@ -4474,7 +4459,7 @@
         <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>23</v>
@@ -4497,7 +4482,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>26</v>
@@ -4520,7 +4505,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>29</v>
@@ -4543,7 +4528,7 @@
         <v>31</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>32</v>
@@ -4566,7 +4551,7 @@
         <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>35</v>
@@ -4589,7 +4574,7 @@
         <v>37</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>38</v>
@@ -4612,7 +4597,7 @@
         <v>40</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>41</v>
@@ -4635,7 +4620,7 @@
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>44</v>
@@ -4658,7 +4643,7 @@
         <v>46</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>47</v>
@@ -4681,7 +4666,7 @@
         <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>50</v>
@@ -4704,7 +4689,7 @@
         <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>53</v>
@@ -4724,19 +4709,19 @@
     </row>
     <row r="20" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B20" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="F20" s="16">
         <v>25</v>
@@ -4747,19 +4732,19 @@
     </row>
     <row r="21" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="D21" s="3">
         <v>0</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="F21" s="16">
         <v>26.4</v>
@@ -4770,19 +4755,19 @@
     </row>
     <row r="22" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="D22" s="3">
         <v>0</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="F22" s="16">
         <v>18.600000000000001</v>
@@ -4796,7 +4781,7 @@
         <v>55</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>56</v>
@@ -4816,19 +4801,19 @@
     </row>
     <row r="24" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="D24" s="3">
         <v>0</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="F24" s="16">
         <v>17</v>
@@ -4842,7 +4827,7 @@
         <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>59</v>
@@ -4865,7 +4850,7 @@
         <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>62</v>
@@ -4888,7 +4873,7 @@
         <v>64</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>65</v>
@@ -4911,7 +4896,7 @@
         <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>68</v>
@@ -4934,7 +4919,7 @@
         <v>70</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>71</v>
@@ -4957,7 +4942,7 @@
         <v>73</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>74</v>
@@ -4980,7 +4965,7 @@
         <v>76</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>77</v>
@@ -5003,7 +4988,7 @@
         <v>79</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>80</v>
@@ -5026,7 +5011,7 @@
         <v>82</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>83</v>
@@ -5049,7 +5034,7 @@
         <v>85</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>86</v>
@@ -5072,7 +5057,7 @@
         <v>88</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>89</v>
@@ -5095,7 +5080,7 @@
         <v>91</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>92</v>
@@ -5118,7 +5103,7 @@
         <v>94</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>95</v>
@@ -5141,7 +5126,7 @@
         <v>97</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>98</v>
@@ -5164,7 +5149,7 @@
         <v>100</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>101</v>
@@ -5187,7 +5172,7 @@
         <v>103</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>104</v>
@@ -5210,7 +5195,7 @@
         <v>106</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>107</v>
@@ -5233,7 +5218,7 @@
         <v>109</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>110</v>
@@ -5256,7 +5241,7 @@
         <v>112</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>113</v>
@@ -5279,7 +5264,7 @@
         <v>115</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>116</v>
@@ -5302,7 +5287,7 @@
         <v>118</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>119</v>
@@ -5325,7 +5310,7 @@
         <v>121</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>122</v>
@@ -5348,7 +5333,7 @@
         <v>124</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>125</v>
@@ -5371,7 +5356,7 @@
         <v>127</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>128</v>
@@ -5394,7 +5379,7 @@
         <v>130</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>131</v>
@@ -5417,7 +5402,7 @@
         <v>133</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>134</v>
@@ -5440,7 +5425,7 @@
         <v>136</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>137</v>
@@ -5463,7 +5448,7 @@
         <v>139</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>140</v>
@@ -5486,7 +5471,7 @@
         <v>142</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>143</v>
@@ -5509,7 +5494,7 @@
         <v>145</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>146</v>
@@ -5532,7 +5517,7 @@
         <v>148</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>149</v>
@@ -5555,7 +5540,7 @@
         <v>151</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>152</v>
@@ -5578,7 +5563,7 @@
         <v>154</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>155</v>
@@ -5601,7 +5586,7 @@
         <v>157</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>158</v>
@@ -5624,7 +5609,7 @@
         <v>160</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>161</v>
@@ -5647,7 +5632,7 @@
         <v>163</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>164</v>
@@ -5670,7 +5655,7 @@
         <v>166</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>167</v>
@@ -5693,7 +5678,7 @@
         <v>169</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>170</v>
@@ -5716,7 +5701,7 @@
         <v>172</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>173</v>
@@ -5739,7 +5724,7 @@
         <v>175</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>176</v>
@@ -5762,7 +5747,7 @@
         <v>178</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>179</v>
@@ -5785,7 +5770,7 @@
         <v>181</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>182</v>
@@ -5808,7 +5793,7 @@
         <v>184</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>185</v>
@@ -5831,7 +5816,7 @@
         <v>187</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>188</v>
@@ -5854,7 +5839,7 @@
         <v>190</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>191</v>
@@ -5877,7 +5862,7 @@
         <v>193</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>194</v>
@@ -5900,7 +5885,7 @@
         <v>196</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>197</v>
@@ -5923,7 +5908,7 @@
         <v>199</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>200</v>
@@ -5946,7 +5931,7 @@
         <v>202</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>203</v>
@@ -5969,7 +5954,7 @@
         <v>205</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>206</v>
@@ -5992,7 +5977,7 @@
         <v>208</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>209</v>
@@ -6038,7 +6023,7 @@
         <v>215</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>216</v>
@@ -6061,7 +6046,7 @@
         <v>218</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>219</v>
@@ -6084,7 +6069,7 @@
         <v>221</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>222</v>
@@ -6107,7 +6092,7 @@
         <v>224</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>225</v>
@@ -6130,7 +6115,7 @@
         <v>227</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>228</v>
@@ -6153,7 +6138,7 @@
         <v>230</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>231</v>
@@ -6176,7 +6161,7 @@
         <v>233</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>234</v>
@@ -6199,7 +6184,7 @@
         <v>236</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>237</v>
@@ -6222,7 +6207,7 @@
         <v>239</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>240</v>
@@ -6245,7 +6230,7 @@
         <v>242</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>243</v>
@@ -6268,7 +6253,7 @@
         <v>245</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>246</v>
@@ -6291,7 +6276,7 @@
         <v>248</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>249</v>
@@ -6314,7 +6299,7 @@
         <v>251</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>252</v>
@@ -6337,7 +6322,7 @@
         <v>254</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>255</v>
@@ -6360,7 +6345,7 @@
         <v>257</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>258</v>
@@ -6383,7 +6368,7 @@
         <v>260</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>261</v>
@@ -6406,7 +6391,7 @@
         <v>263</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>264</v>
@@ -6429,7 +6414,7 @@
         <v>266</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>267</v>
@@ -6452,7 +6437,7 @@
         <v>269</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>270</v>
@@ -6472,19 +6457,19 @@
     </row>
     <row r="96" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="D96" s="3">
         <v>1</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="F96" s="16">
         <v>24</v>
@@ -6498,7 +6483,7 @@
         <v>272</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>273</v>
@@ -6521,7 +6506,7 @@
         <v>275</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>276</v>
@@ -6544,7 +6529,7 @@
         <v>278</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>279</v>
@@ -6567,7 +6552,7 @@
         <v>281</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>282</v>
@@ -6590,7 +6575,7 @@
         <v>284</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>285</v>
@@ -6613,7 +6598,7 @@
         <v>287</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>288</v>
@@ -6636,7 +6621,7 @@
         <v>290</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>291</v>
@@ -6659,7 +6644,7 @@
         <v>293</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>294</v>
@@ -6682,7 +6667,7 @@
         <v>296</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>297</v>
@@ -6705,7 +6690,7 @@
         <v>299</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>300</v>
@@ -6728,7 +6713,7 @@
         <v>302</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>303</v>
@@ -6751,7 +6736,7 @@
         <v>305</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>306</v>
@@ -6774,7 +6759,7 @@
         <v>308</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>309</v>
@@ -6797,7 +6782,7 @@
         <v>311</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>312</v>
@@ -6820,7 +6805,7 @@
         <v>314</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>315</v>
@@ -6843,7 +6828,7 @@
         <v>317</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>318</v>
@@ -6863,19 +6848,19 @@
     </row>
     <row r="113" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="D113" s="3">
         <v>0</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="F113" s="16">
         <v>24</v>
@@ -6889,7 +6874,7 @@
         <v>320</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>321</v>
@@ -6912,7 +6897,7 @@
         <v>323</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>324</v>
@@ -6935,7 +6920,7 @@
         <v>326</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>327</v>
@@ -6958,7 +6943,7 @@
         <v>329</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>330</v>
@@ -6981,7 +6966,7 @@
         <v>332</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>333</v>
@@ -7004,7 +6989,7 @@
         <v>335</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>336</v>
@@ -7027,7 +7012,7 @@
         <v>338</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>339</v>
@@ -7050,7 +7035,7 @@
         <v>341</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>342</v>
@@ -7073,7 +7058,7 @@
         <v>344</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>345</v>
@@ -7096,7 +7081,7 @@
         <v>347</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>348</v>
@@ -7119,7 +7104,7 @@
         <v>350</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>351</v>
@@ -7142,7 +7127,7 @@
         <v>353</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>354</v>
@@ -7165,7 +7150,7 @@
         <v>356</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>357</v>
@@ -7188,7 +7173,7 @@
         <v>359</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>360</v>
@@ -7211,7 +7196,7 @@
         <v>362</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>363</v>
@@ -7234,7 +7219,7 @@
         <v>365</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>366</v>
@@ -7257,7 +7242,7 @@
         <v>368</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>369</v>
@@ -7280,7 +7265,7 @@
         <v>371</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>372</v>
@@ -7303,7 +7288,7 @@
         <v>374</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>375</v>
@@ -7326,7 +7311,7 @@
         <v>377</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>378</v>
@@ -7349,7 +7334,7 @@
         <v>380</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>381</v>
@@ -7372,7 +7357,7 @@
         <v>383</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>384</v>
@@ -7395,7 +7380,7 @@
         <v>386</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>387</v>
@@ -7415,19 +7400,19 @@
     </row>
     <row r="137" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="D137" s="3">
         <v>0</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="F137" s="16">
         <v>23</v>
@@ -7441,7 +7426,7 @@
         <v>389</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>390</v>
@@ -7464,10 +7449,10 @@
         <v>392</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="D139" s="3">
         <v>0</v>
@@ -7487,7 +7472,7 @@
         <v>394</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>395</v>
@@ -7510,7 +7495,7 @@
         <v>397</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>398</v>
@@ -7533,7 +7518,7 @@
         <v>400</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>401</v>
@@ -7556,7 +7541,7 @@
         <v>403</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>404</v>
@@ -7579,7 +7564,7 @@
         <v>406</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>407</v>
@@ -7602,7 +7587,7 @@
         <v>409</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>410</v>
@@ -7625,7 +7610,7 @@
         <v>412</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>413</v>
@@ -7648,7 +7633,7 @@
         <v>415</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>416</v>
@@ -7671,7 +7656,7 @@
         <v>418</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>419</v>
@@ -7694,7 +7679,7 @@
         <v>421</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>422</v>
@@ -7717,7 +7702,7 @@
         <v>424</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>425</v>
@@ -7740,7 +7725,7 @@
         <v>427</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>428</v>
@@ -7763,7 +7748,7 @@
         <v>430</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>431</v>
@@ -7786,7 +7771,7 @@
         <v>433</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>434</v>
@@ -7809,7 +7794,7 @@
         <v>436</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>437</v>
@@ -7832,7 +7817,7 @@
         <v>439</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>440</v>
@@ -7855,7 +7840,7 @@
         <v>442</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>443</v>
@@ -7878,7 +7863,7 @@
         <v>445</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>446</v>
@@ -7901,7 +7886,7 @@
         <v>448</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>449</v>
@@ -7924,7 +7909,7 @@
         <v>451</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>452</v>
@@ -7947,7 +7932,7 @@
         <v>454</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>455</v>
@@ -7970,7 +7955,7 @@
         <v>457</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>458</v>
@@ -7993,7 +7978,7 @@
         <v>460</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>461</v>
@@ -8016,7 +8001,7 @@
         <v>463</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>464</v>
@@ -8039,7 +8024,7 @@
         <v>466</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>467</v>
@@ -8062,7 +8047,7 @@
         <v>469</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>470</v>
@@ -8085,7 +8070,7 @@
         <v>472</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>473</v>
@@ -8108,7 +8093,7 @@
         <v>475</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>476</v>
@@ -8131,7 +8116,7 @@
         <v>478</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>479</v>
@@ -8154,7 +8139,7 @@
         <v>481</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>482</v>
@@ -8177,7 +8162,7 @@
         <v>484</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>485</v>
@@ -8200,7 +8185,7 @@
         <v>487</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>488</v>
@@ -8223,7 +8208,7 @@
         <v>490</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>491</v>
@@ -8246,7 +8231,7 @@
         <v>493</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>494</v>
@@ -8269,7 +8254,7 @@
         <v>496</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>497</v>
@@ -8292,7 +8277,7 @@
         <v>499</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>500</v>
@@ -8315,7 +8300,7 @@
         <v>502</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>503</v>
@@ -8338,7 +8323,7 @@
         <v>505</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>506</v>
@@ -8361,7 +8346,7 @@
         <v>508</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>509</v>
@@ -8384,7 +8369,7 @@
         <v>511</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>512</v>
@@ -8407,7 +8392,7 @@
         <v>514</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>515</v>
@@ -8430,7 +8415,7 @@
         <v>517</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>518</v>
@@ -8453,7 +8438,7 @@
         <v>520</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>521</v>
@@ -8476,7 +8461,7 @@
         <v>523</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C183" s="2" t="s">
         <v>524</v>
@@ -8499,7 +8484,7 @@
         <v>526</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C184" s="2" t="s">
         <v>527</v>
@@ -8522,7 +8507,7 @@
         <v>529</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>530</v>
@@ -8545,7 +8530,7 @@
         <v>532</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>533</v>
@@ -8568,7 +8553,7 @@
         <v>535</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>536</v>
@@ -8591,7 +8576,7 @@
         <v>538</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>539</v>
@@ -8614,7 +8599,7 @@
         <v>541</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>542</v>
@@ -8637,7 +8622,7 @@
         <v>544</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>545</v>
@@ -8660,7 +8645,7 @@
         <v>547</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>548</v>
@@ -8683,7 +8668,7 @@
         <v>550</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="C192" s="2" t="s">
         <v>551</v>
@@ -8706,7 +8691,7 @@
         <v>553</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="C193" s="2" t="s">
         <v>554</v>
@@ -8729,91 +8714,91 @@
         <v>556</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C194" s="2" t="s">
         <v>557</v>
       </c>
       <c r="D194" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>558</v>
       </c>
       <c r="F194" s="16">
-        <v>16.2</v>
+        <v>21.3</v>
       </c>
       <c r="G194" s="18">
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>559</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C195" s="2" t="s">
         <v>560</v>
       </c>
       <c r="D195" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>561</v>
       </c>
       <c r="F195" s="16">
-        <v>21.3</v>
+        <v>22.8</v>
       </c>
       <c r="G195" s="18">
-        <v>15.8</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>562</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C196" s="2" t="s">
         <v>563</v>
       </c>
       <c r="D196" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>564</v>
       </c>
       <c r="F196" s="16">
-        <v>22.8</v>
+        <v>13.5</v>
       </c>
       <c r="G196" s="18">
-        <v>36.5</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>565</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>566</v>
       </c>
       <c r="D197" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>567</v>
       </c>
       <c r="F197" s="16">
-        <v>13.5</v>
+        <v>22.8</v>
       </c>
       <c r="G197" s="18">
-        <v>11.3</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -8821,30 +8806,30 @@
         <v>568</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>569</v>
       </c>
       <c r="D198" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>570</v>
       </c>
       <c r="F198" s="16">
-        <v>22.8</v>
+        <v>36</v>
       </c>
       <c r="G198" s="18">
-        <v>28.5</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>571</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>572</v>
@@ -8856,10 +8841,10 @@
         <v>573</v>
       </c>
       <c r="F199" s="16">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G199" s="18">
-        <v>40</v>
+        <v>18.399999999999999</v>
       </c>
     </row>
     <row r="200" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -8867,22 +8852,22 @@
         <v>574</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C200" s="2" t="s">
         <v>575</v>
       </c>
       <c r="D200" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>576</v>
       </c>
       <c r="F200" s="16">
-        <v>23</v>
+        <v>36.1</v>
       </c>
       <c r="G200" s="18">
-        <v>18.399999999999999</v>
+        <v>33.700000000000003</v>
       </c>
     </row>
     <row r="201" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -8890,22 +8875,22 @@
         <v>577</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>578</v>
       </c>
       <c r="D201" s="3">
-        <v>2</v>
+        <v>81</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>579</v>
       </c>
       <c r="F201" s="16">
-        <v>36.1</v>
+        <v>18</v>
       </c>
       <c r="G201" s="18">
-        <v>33.700000000000003</v>
+        <v>9</v>
       </c>
     </row>
     <row r="202" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -8913,30 +8898,30 @@
         <v>580</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C202" s="2" t="s">
         <v>581</v>
       </c>
       <c r="D202" s="3">
-        <v>81</v>
+        <v>1</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>582</v>
       </c>
       <c r="F202" s="16">
-        <v>18</v>
+        <v>28.5</v>
       </c>
       <c r="G202" s="18">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>583</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C203" s="2" t="s">
         <v>584</v>
@@ -8948,10 +8933,10 @@
         <v>585</v>
       </c>
       <c r="F203" s="16">
-        <v>28.5</v>
+        <v>24</v>
       </c>
       <c r="G203" s="18">
-        <v>22.8</v>
+        <v>35.799999999999997</v>
       </c>
     </row>
     <row r="204" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -8959,7 +8944,7 @@
         <v>586</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="C204" s="2" t="s">
         <v>587</v>
@@ -8971,56 +8956,56 @@
         <v>588</v>
       </c>
       <c r="F204" s="16">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G204" s="18">
-        <v>35.799999999999997</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="90" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>589</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C205" s="2" t="s">
         <v>590</v>
       </c>
       <c r="D205" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>591</v>
       </c>
       <c r="F205" s="16">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G205" s="18">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>592</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C206" s="2" t="s">
         <v>593</v>
       </c>
       <c r="D206" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>594</v>
       </c>
       <c r="F206" s="16">
-        <v>24</v>
+        <v>21.8</v>
       </c>
       <c r="G206" s="18">
-        <v>26.7</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="60" x14ac:dyDescent="0.25">
@@ -9028,30 +9013,30 @@
         <v>595</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>596</v>
       </c>
       <c r="D207" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>597</v>
       </c>
       <c r="F207" s="16">
-        <v>21.8</v>
+        <v>38.6</v>
       </c>
       <c r="G207" s="18">
-        <v>24.2</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>36.799999999999997</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="105" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>598</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>599</v>
@@ -9063,18 +9048,18 @@
         <v>600</v>
       </c>
       <c r="F208" s="16">
-        <v>38.6</v>
+        <v>30.8</v>
       </c>
       <c r="G208" s="18">
-        <v>36.799999999999997</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" ht="105" x14ac:dyDescent="0.25">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>601</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>602</v>
@@ -9086,56 +9071,56 @@
         <v>603</v>
       </c>
       <c r="F209" s="16">
-        <v>30.8</v>
+        <v>24</v>
       </c>
       <c r="G209" s="18">
-        <v>32.4</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>604</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>605</v>
       </c>
       <c r="D210" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>606</v>
       </c>
       <c r="F210" s="16">
-        <v>24</v>
+        <v>33.6</v>
       </c>
       <c r="G210" s="18">
-        <v>21.8</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>607</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>608</v>
       </c>
       <c r="D211" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>609</v>
       </c>
       <c r="F211" s="16">
-        <v>33.6</v>
+        <v>24</v>
       </c>
       <c r="G211" s="18">
-        <v>35.4</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="212" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -9143,59 +9128,59 @@
         <v>610</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>611</v>
       </c>
       <c r="D212" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>612</v>
       </c>
       <c r="F212" s="16">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G212" s="18">
-        <v>21.4</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>613</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>614</v>
       </c>
       <c r="D213" s="3">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>615</v>
       </c>
       <c r="F213" s="16">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G213" s="18">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>616</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C214" s="2" t="s">
         <v>617</v>
       </c>
       <c r="D214" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>618</v>
@@ -9204,99 +9189,99 @@
         <v>24</v>
       </c>
       <c r="G214" s="18">
-        <v>25.3</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" ht="60" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="D215" s="3">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="F215" s="16">
-        <v>24</v>
+        <v>21.6</v>
       </c>
       <c r="G215" s="18">
         <v>24</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="D216" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="F216" s="16">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="G216" s="18">
-        <v>24</v>
+        <v>24.3</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>623</v>
+        <v>182</v>
       </c>
       <c r="D217" s="3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F217" s="16">
-        <v>21.9</v>
+        <v>18</v>
       </c>
       <c r="G217" s="18">
-        <v>24.3</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="C218" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>847</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>182</v>
-      </c>
       <c r="D218" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>629</v>
       </c>
       <c r="F218" s="16">
-        <v>18</v>
+        <v>22.8</v>
       </c>
       <c r="G218" s="18">
-        <v>20</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="219" spans="1:7" ht="75" x14ac:dyDescent="0.25">
@@ -9304,7 +9289,7 @@
         <v>630</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>631</v>
@@ -9316,38 +9301,15 @@
         <v>632</v>
       </c>
       <c r="F219" s="16">
-        <v>22.8</v>
+        <v>28.9</v>
       </c>
       <c r="G219" s="18">
-        <v>26.8</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A220" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="D220" s="3">
-        <v>2</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="F220" s="16">
-        <v>28.9</v>
-      </c>
-      <c r="G220" s="18">
         <v>32.1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F220">
-    <sortCondition ref="A2:A220"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F219">
+    <sortCondition ref="A2:A219"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9367,1567 +9329,1567 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B2" s="6">
         <v>48600</v>
       </c>
       <c r="C2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="B3" s="6">
         <v>27380</v>
       </c>
       <c r="C3" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B4" s="6">
         <v>22740</v>
       </c>
       <c r="C4" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="B5" s="6">
         <v>12510</v>
       </c>
       <c r="C5" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="B6" s="6">
         <v>10950</v>
       </c>
       <c r="C6" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B7" s="6">
         <v>10830</v>
       </c>
       <c r="C7" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B8" s="6">
         <v>9631</v>
       </c>
       <c r="C8" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="B9" s="6">
         <v>8380</v>
       </c>
       <c r="C9" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="B10" s="6">
         <v>5568</v>
       </c>
       <c r="C10" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="B11" s="6">
         <v>5400</v>
       </c>
       <c r="C11" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B12" s="6">
         <v>4395</v>
       </c>
       <c r="C12" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="B13" s="6">
         <v>4110</v>
       </c>
       <c r="C13" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="B14" s="6">
         <v>4080</v>
       </c>
       <c r="C14" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B15" s="6">
         <v>3660</v>
       </c>
       <c r="C15" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="B16" s="6">
         <v>3200</v>
       </c>
       <c r="C16" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="B17" s="6">
         <v>3165</v>
       </c>
       <c r="C17" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="B18" s="6">
         <v>2765</v>
       </c>
       <c r="C18" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B19" s="6">
         <v>2265</v>
       </c>
       <c r="C19" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B20" s="6">
         <v>2185</v>
       </c>
       <c r="C20" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B21" s="6">
         <v>2070</v>
       </c>
       <c r="C21" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B22" s="6">
         <v>1925</v>
       </c>
       <c r="C22" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B23" s="6">
         <v>1895</v>
       </c>
       <c r="C23" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B24" s="6">
         <v>1370</v>
       </c>
       <c r="C24" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B25" s="6">
         <v>1300</v>
       </c>
       <c r="C25" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B26" s="6">
         <v>1215</v>
       </c>
       <c r="C26" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="B27" s="6">
         <v>1020</v>
       </c>
       <c r="C27" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="B28" s="6">
         <v>1010</v>
       </c>
       <c r="C28" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B29" s="6">
         <v>945</v>
       </c>
       <c r="C29" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="B30" s="6">
         <v>840</v>
       </c>
       <c r="C30" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B31" s="6">
         <v>780</v>
       </c>
       <c r="C31" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B32" s="6">
         <v>770</v>
       </c>
       <c r="C32" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B33" s="6">
         <v>730</v>
       </c>
       <c r="C33" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B34" s="6">
         <v>630</v>
       </c>
       <c r="C34" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="B35" s="6">
         <v>630</v>
       </c>
       <c r="C35" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B36" s="6">
         <v>580</v>
       </c>
       <c r="C36" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B37" s="6">
         <v>540</v>
       </c>
       <c r="C37" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="B38" s="6">
         <v>525</v>
       </c>
       <c r="C38" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B39" s="6">
         <v>525</v>
       </c>
       <c r="C39" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B40" s="6">
         <v>524</v>
       </c>
       <c r="C40" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B41" s="6">
         <v>495</v>
       </c>
       <c r="C41" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B42" s="6">
         <v>495</v>
       </c>
       <c r="C42" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B43" s="6">
         <v>490</v>
       </c>
       <c r="C43" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B44" s="6">
         <v>450</v>
       </c>
       <c r="C44" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B45" s="6">
         <v>450</v>
       </c>
       <c r="C45" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="B46" s="6">
         <v>360</v>
       </c>
       <c r="C46" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B47" s="6">
         <v>345</v>
       </c>
       <c r="C47" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B48" s="6">
         <v>330</v>
       </c>
       <c r="C48" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="B49" s="6">
         <v>300</v>
       </c>
       <c r="C49" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="B50" s="6">
         <v>300</v>
       </c>
       <c r="C50" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B51" s="6">
         <v>285</v>
       </c>
       <c r="C51" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="B52" s="6">
         <v>265</v>
       </c>
       <c r="C52" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="B53" s="6">
         <v>260</v>
       </c>
       <c r="C53" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="B54" s="6">
         <v>245</v>
       </c>
       <c r="C54" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B55" s="6">
         <v>240</v>
       </c>
       <c r="C55" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="B56" s="6">
         <v>240</v>
       </c>
       <c r="C56" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="B57" s="6">
         <v>240</v>
       </c>
       <c r="C57" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B58" s="6">
         <v>210</v>
       </c>
       <c r="C58" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B59" s="6">
         <v>210</v>
       </c>
       <c r="C59" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B60" s="6">
         <v>200</v>
       </c>
       <c r="C60" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B61" s="6">
         <v>194</v>
       </c>
       <c r="C61" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B62" s="6">
         <v>180</v>
       </c>
       <c r="C62" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="B63" s="6">
         <v>180</v>
       </c>
       <c r="C63" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B64" s="6">
         <v>180</v>
       </c>
       <c r="C64" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="B65" s="6">
         <v>180</v>
       </c>
       <c r="C65" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B66" s="6">
         <v>175</v>
       </c>
       <c r="C66" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B67" s="6">
         <v>170</v>
       </c>
       <c r="C67" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="B68" s="6">
         <v>160</v>
       </c>
       <c r="C68" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="B69" s="6">
         <v>155</v>
       </c>
       <c r="C69" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B70" s="6">
         <v>150</v>
       </c>
       <c r="C70" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B71" s="6">
         <v>150</v>
       </c>
       <c r="C71" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="B72" s="6">
         <v>145</v>
       </c>
       <c r="C72" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="B73" s="6">
         <v>135</v>
       </c>
       <c r="C73" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B74" s="6">
         <v>132</v>
       </c>
       <c r="C74" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
     </row>
     <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="B75" s="6">
         <v>131</v>
       </c>
       <c r="C75" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B76" s="6">
         <v>120</v>
       </c>
       <c r="C76" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="B77" s="6">
         <v>120</v>
       </c>
       <c r="C77" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B78" s="6">
         <v>120</v>
       </c>
       <c r="C78" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B79" s="6">
         <v>120</v>
       </c>
       <c r="C79" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B80" s="6">
         <v>120</v>
       </c>
       <c r="C80" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B81" s="6">
         <v>120</v>
       </c>
       <c r="C81" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="B82" s="6">
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B83" s="6">
         <v>100</v>
       </c>
       <c r="C83" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="B84" s="6">
         <v>100</v>
       </c>
       <c r="C84" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="B85" s="6">
         <v>95</v>
       </c>
       <c r="C85" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
     </row>
     <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="B86" s="6">
         <v>93</v>
       </c>
       <c r="C86" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B87" s="6">
         <v>90</v>
       </c>
       <c r="C87" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="B88" s="6">
         <v>90</v>
       </c>
       <c r="C88" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="B89" s="6">
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="B90" s="6">
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B91" s="6">
         <v>64</v>
       </c>
       <c r="C91" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B92" s="6">
         <v>60</v>
       </c>
       <c r="C92" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="B93" s="6">
         <v>60</v>
       </c>
       <c r="C93" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="B94" s="6">
         <v>60</v>
       </c>
       <c r="C94" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B95" s="6">
         <v>60</v>
       </c>
       <c r="C95" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B96" s="6">
         <v>50</v>
       </c>
       <c r="C96" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B97" s="6">
         <v>50</v>
       </c>
       <c r="C97" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="B98" s="6">
         <v>49</v>
       </c>
       <c r="C98" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="B99" s="6">
         <v>45</v>
       </c>
       <c r="C99" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B100" s="6">
         <v>45</v>
       </c>
       <c r="C100" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="B101" s="6">
         <v>40</v>
       </c>
       <c r="C101" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="B102" s="6">
         <v>35</v>
       </c>
       <c r="C102" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B103" s="6">
         <v>32.5</v>
       </c>
       <c r="C103" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B104" s="6">
         <v>30</v>
       </c>
       <c r="C104" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="B105" s="6">
         <v>30</v>
       </c>
       <c r="C105" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="B106" s="6">
         <v>30</v>
       </c>
       <c r="C106" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="B107" s="6">
         <v>30</v>
       </c>
       <c r="C107" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="B108" s="6">
         <v>30</v>
       </c>
       <c r="C108" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B109" s="6">
         <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
     </row>
     <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="B110" s="6">
         <v>24</v>
       </c>
       <c r="C110" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
     </row>
     <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B111" s="6">
         <v>21</v>
       </c>
       <c r="C111" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B112" s="6">
         <v>20</v>
       </c>
       <c r="C112" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B113" s="6">
         <v>20</v>
       </c>
       <c r="C113" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="B114" s="6">
         <v>18</v>
       </c>
       <c r="C114" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B115" s="6">
         <v>17.5</v>
       </c>
       <c r="C115" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B116" s="6">
         <v>16</v>
       </c>
       <c r="C116" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="B117" s="6">
         <v>15</v>
       </c>
       <c r="C117" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="B118" s="6">
         <v>15</v>
       </c>
       <c r="C118" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B119" s="6">
         <v>15</v>
       </c>
       <c r="C119" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B120" s="6">
         <v>15</v>
       </c>
       <c r="C120" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="B121" s="6">
         <v>14</v>
       </c>
       <c r="C121" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B122" s="6">
         <v>11</v>
       </c>
       <c r="C122" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="B123" s="6">
         <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="B124" s="6">
         <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B125" s="6">
         <v>7</v>
       </c>
       <c r="C125" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B126" s="6">
         <v>6</v>
       </c>
       <c r="C126" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="B127" s="6">
         <v>5</v>
       </c>
       <c r="C127" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="B128" s="6">
         <v>5</v>
       </c>
       <c r="C128" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B129" s="6">
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
     </row>
     <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B130" s="6">
         <v>3</v>
       </c>
       <c r="C130" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="B131" s="6">
         <v>3</v>
       </c>
       <c r="C131" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="B132" s="6">
         <v>2.5</v>
       </c>
       <c r="C132" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="B133" s="6">
         <v>2</v>
       </c>
       <c r="C133" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B134" s="6">
         <v>2</v>
       </c>
       <c r="C134" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="B135" s="6">
         <v>2</v>
       </c>
       <c r="C135" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="B136" s="6">
         <v>2</v>
       </c>
       <c r="C136" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B137" s="6">
         <v>2</v>
       </c>
       <c r="C137" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="B138" s="6">
         <v>2</v>
       </c>
       <c r="C138" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="B139" s="6">
         <v>1</v>
       </c>
       <c r="C139" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="B140" s="6">
         <v>1</v>
       </c>
       <c r="C140" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="B141" s="6">
         <v>1</v>
       </c>
       <c r="C141" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="B142" s="6">
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
     </row>
   </sheetData>
@@ -10955,31 +10917,31 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="B5" s="11">
         <v>57497.5</v>
@@ -10995,7 +10957,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B6" s="11">
         <v>21048</v>
@@ -11011,7 +10973,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="B7" s="11">
         <v>17360</v>
@@ -11027,7 +10989,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="B8" s="11">
         <v>0</v>
@@ -11043,7 +11005,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="B9" s="12">
         <f>SUM(B5:B8)</f>
@@ -11060,880 +11022,880 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B13" s="6">
         <v>22740</v>
       </c>
       <c r="C13" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="B14" s="6">
         <v>10950</v>
       </c>
       <c r="C14" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B15" s="6">
         <v>4395</v>
       </c>
       <c r="C15" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B16" s="6">
         <v>3660</v>
       </c>
       <c r="C16" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="B17" s="6">
         <v>3200</v>
       </c>
       <c r="C17" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="B18" s="6">
         <v>2765</v>
       </c>
       <c r="C18" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B19" s="6">
         <v>1895</v>
       </c>
       <c r="C19" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B20" s="6">
         <v>1215</v>
       </c>
       <c r="C20" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="B21" s="6">
         <v>1010</v>
       </c>
       <c r="C21" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="B22" s="6">
         <v>840</v>
       </c>
       <c r="C22" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B23" s="6">
         <v>780</v>
       </c>
       <c r="C23" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="B24" s="6">
         <v>730</v>
       </c>
       <c r="C24" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B25" s="6">
         <v>495</v>
       </c>
       <c r="C25" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="B26" s="6">
         <v>450</v>
       </c>
       <c r="C26" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B27" s="6">
         <v>345</v>
       </c>
       <c r="C27" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B28" s="6">
         <v>285</v>
       </c>
       <c r="C28" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="B29" s="6">
         <v>265</v>
       </c>
       <c r="C29" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B30" s="6">
         <v>240</v>
       </c>
       <c r="C30" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B31" s="6">
         <v>210</v>
       </c>
       <c r="C31" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="B32" s="6">
         <v>180</v>
       </c>
       <c r="C32" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="B33" s="6">
         <v>180</v>
       </c>
       <c r="C33" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B34" s="6">
         <v>180</v>
       </c>
       <c r="C34" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B35" s="6">
         <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B36" s="6">
         <v>120</v>
       </c>
       <c r="C36" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B37" s="6">
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="B38" s="6">
         <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B39" s="6">
         <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B40" s="6">
         <v>32.5</v>
       </c>
       <c r="C40" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B41" s="6">
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="B42" s="6">
         <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B43" s="6">
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="B47" s="6">
         <v>4110</v>
       </c>
       <c r="C47" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="B48" s="6">
         <v>4080</v>
       </c>
       <c r="C48" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="B49" s="6">
         <v>3165</v>
       </c>
       <c r="C49" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B50" s="6">
         <v>2185</v>
       </c>
       <c r="C50" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B51" s="6">
         <v>1925</v>
       </c>
       <c r="C51" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B52" s="6">
         <v>540</v>
       </c>
       <c r="C52" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B53" s="6">
         <v>525</v>
       </c>
       <c r="C53" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B54" s="6">
         <v>524</v>
       </c>
       <c r="C54" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B55" s="6">
         <v>495</v>
       </c>
       <c r="C55" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B56" s="6">
         <v>490</v>
       </c>
       <c r="C56" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B57" s="6">
         <v>450</v>
       </c>
       <c r="C57" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B58" s="6">
         <v>330</v>
       </c>
       <c r="C58" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="B59" s="6">
         <v>245</v>
       </c>
       <c r="C59" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="B60" s="6">
         <v>240</v>
       </c>
       <c r="C60" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="B61" s="6">
         <v>210</v>
       </c>
       <c r="C61" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B62" s="6">
         <v>200</v>
       </c>
       <c r="C62" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B63" s="6">
         <v>194</v>
       </c>
       <c r="C63" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="B64" s="6">
         <v>180</v>
       </c>
       <c r="C64" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B65" s="6">
         <v>170</v>
       </c>
       <c r="C65" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="B66" s="6">
         <v>155</v>
       </c>
       <c r="C66" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B67" s="6">
         <v>120</v>
       </c>
       <c r="C67" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="B68" s="6">
         <v>105</v>
       </c>
       <c r="C68" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B69" s="6">
         <v>90</v>
       </c>
       <c r="C69" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="B70" s="6">
         <v>90</v>
       </c>
       <c r="C70" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="B71" s="6">
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="B72" s="6">
         <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="B73" s="6">
         <v>30</v>
       </c>
       <c r="C73" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="B74" s="6">
         <v>30</v>
       </c>
       <c r="C74" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B75" s="6">
         <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="B76" s="6">
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B77" s="6">
         <v>15</v>
       </c>
       <c r="C77" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="9" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="B81" s="6">
         <v>12510</v>
       </c>
       <c r="C81" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B82" s="6">
         <v>2265</v>
       </c>
       <c r="C82" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B83" s="6">
         <v>1300</v>
       </c>
       <c r="C83" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B84" s="6">
         <v>945</v>
       </c>
       <c r="C84" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B85" s="6">
         <v>175</v>
       </c>
       <c r="C85" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B86" s="6">
         <v>120</v>
       </c>
       <c r="C86" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B87" s="6">
         <v>45</v>
       </c>
       <c r="C87" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="9" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="15" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B91" s="6">
         <v>150</v>
       </c>
       <c r="C91" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B92" s="6">
         <v>30</v>
       </c>
       <c r="C92" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="B93" s="6">
         <v>18</v>
       </c>
       <c r="C93" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B94" s="6">
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="B95" s="6">
         <v>2</v>
       </c>
       <c r="C95" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
     </row>
   </sheetData>

--- a/cocktail_source.xlsx
+++ b/cocktail_source.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bainandcompany-my.sharepoint.com/personal/gregoire_baudry_bain_com/Documents/Documents/GitHub/Greg's Bar/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\06GBA\OneDrive - Bain\Documents\GitHub\Greg's Bar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{55666991-13C5-43F9-9A70-97D3BDF1EC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFC948E1-4BD3-4094-A9FC-32D6DDE58D32}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187AF605-8261-4BA5-8C1A-4BB3A5BE4362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,8 +37,112 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Gregoire Baudry</author>
+  </authors>
+  <commentList>
+    <comment ref="A103" authorId="0" shapeId="0" xr:uid="{45CA97C4-2C64-4FD9-BB4A-6A3AEAF89453}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Gregoire Baudry:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Sic — matches the typo "Lilmoncello" in Cocktails!C205 (Limoncello). ABV assumed 30% for standard bottled limoncello; verify against actual bottle.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E106" authorId="0" shapeId="0" xr:uid="{0A94048E-73BD-45C1-9171-0BE0A6434956}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Gregoire Baudry:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Low confidence: specialty/regional product, exact bottle ABV not independently verified. Please confirm and update.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A108" authorId="0" shapeId="0" xr:uid="{9F33738B-DA6A-45EA-9C31-FA95C98662C8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Gregoire Baudry:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Alias for "St. Germain" without the period, as spelled in some recipes (e.g. The Elderflower Collins). Same 20% ABV.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1392" uniqueCount="1089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="1112">
   <si>
     <t>Abbey</t>
   </si>
@@ -1653,9 +1757,6 @@
 Orange Juice – 120 ml</t>
   </si>
   <si>
-    <t>Sea Breeze</t>
-  </si>
-  <si>
     <t>Vodka – 60 ml
 Cranberry Juice – 45 ml
 Grapefruit Juice – 45 ml
@@ -4068,16 +4169,98 @@
   <si>
     <t>Spritz St Germain (Hugo)</t>
   </si>
+  <si>
+    <t>Spritz Limoncello</t>
+  </si>
+  <si>
+    <t>A Spritz version with Limoncello, a liqueur made from the zest of lemons.</t>
+  </si>
+  <si>
+    <t>Lilmoncello – 40 ml
+Sparkling Wine – 60 ml
+Club Soda – 20 ml</t>
+  </si>
+  <si>
+    <t>images/cocktails/spritzlimoncello.jpg</t>
+  </si>
+  <si>
+    <t>Spritz Sarti Rosa</t>
+  </si>
+  <si>
+    <t>A Spritz version with Sarti Rosa, an aperitivo crafted with blood orange, mango and passion fruit.</t>
+  </si>
+  <si>
+    <t>Sarti Rosa – 40 ml
+Sparkling Wine – 60 ml
+Club Soda – 20 ml 
+Lime juice – 5 ml</t>
+  </si>
+  <si>
+    <t>images/cocktails/spritzsartirosa.jpg</t>
+  </si>
+  <si>
+    <t>ABV %</t>
+  </si>
+  <si>
+    <t>Note: ABV % values are standard/typical bottle strengths used to recompute each cocktail's Alcohol Content (ml) and ABV. Verify against your actual bottles where precision matters.</t>
+  </si>
+  <si>
+    <t>Spritz-only liqueurs (used in Cocktails!F/G formulas, not tracked above)</t>
+  </si>
+  <si>
+    <t>Averna</t>
+  </si>
+  <si>
+    <t>Cynar</t>
+  </si>
+  <si>
+    <t>Italicus</t>
+  </si>
+  <si>
+    <t>Sarti Rosa</t>
+  </si>
+  <si>
+    <t>Select</t>
+  </si>
+  <si>
+    <t>Spritz des Dunes</t>
+  </si>
+  <si>
+    <t>Lilmoncello</t>
+  </si>
+  <si>
+    <t>The Elderflower Collins</t>
+  </si>
+  <si>
+    <t>A Tom Collins variation using Vodka as a spirit and St Germain for the sweet touch. Very refreshing cooler.</t>
+  </si>
+  <si>
+    <t>Vodka – 50 ml
+Lemon Juice – 30 ml
+St Germain – 20 ml
+Club Soda – 150 ml
+Lemon – 2 wheels</t>
+  </si>
+  <si>
+    <t>images/cocktails/elderflowercollins.jpg</t>
+  </si>
+  <si>
+    <t>St Germain</t>
+  </si>
+  <si>
+    <t>The Sea Breeze</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.#"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="170" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4150,6 +4333,48 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -4311,7 +4536,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4366,6 +4591,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4381,6 +4625,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4559,7 +4807,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="571" row="1">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -4595,25 +4843,25 @@
   <sheetData>
     <row r="1" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>645</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>648</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>646</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>649</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>647</v>
-      </c>
       <c r="E1" s="14" t="s">
+        <v>809</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>808</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>810</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>809</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>811</v>
       </c>
       <c r="H1" s="15"/>
       <c r="I1" s="15"/>
@@ -4640,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C2" s="18" t="s">
         <v>1</v>
@@ -4649,7 +4897,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F2" s="21">
         <v>21.4</v>
@@ -4682,7 +4930,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C3" s="22" t="s">
         <v>3</v>
@@ -4691,7 +4939,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F3" s="25">
         <v>30.4</v>
@@ -4733,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F4" s="21">
         <v>10.9</v>
@@ -4766,7 +5014,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C5" s="22" t="s">
         <v>8</v>
@@ -4775,7 +5023,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F5" s="25">
         <v>42</v>
@@ -4808,7 +5056,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>10</v>
@@ -4817,7 +5065,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F6" s="21">
         <v>27.5</v>
@@ -4850,7 +5098,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C7" s="22" t="s">
         <v>12</v>
@@ -4859,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="F7" s="25">
         <v>30</v>
@@ -4892,7 +5140,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>14</v>
@@ -4901,7 +5149,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F8" s="21">
         <v>16.600000000000001</v>
@@ -4934,7 +5182,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C9" s="22" t="s">
         <v>16</v>
@@ -4943,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="F9" s="25">
         <v>29.4</v>
@@ -4976,7 +5224,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>18</v>
@@ -4985,7 +5233,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F10" s="21">
         <v>16.8</v>
@@ -5018,7 +5266,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C11" s="22" t="s">
         <v>20</v>
@@ -5027,7 +5275,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F11" s="25">
         <v>36</v>
@@ -5060,7 +5308,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>22</v>
@@ -5069,7 +5317,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F12" s="21">
         <v>30</v>
@@ -5102,7 +5350,7 @@
         <v>23</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>24</v>
@@ -5111,7 +5359,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F13" s="25">
         <v>18.5</v>
@@ -5144,7 +5392,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>26</v>
@@ -5153,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F14" s="21">
         <v>13.4</v>
@@ -5186,16 +5434,16 @@
         <v>27</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C15" s="22" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F15" s="25">
         <v>33</v>
@@ -5228,7 +5476,7 @@
         <v>29</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C16" s="18" t="s">
         <v>30</v>
@@ -5237,7 +5485,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F16" s="21">
         <v>24</v>
@@ -5270,7 +5518,7 @@
         <v>31</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C17" s="22" t="s">
         <v>32</v>
@@ -5279,7 +5527,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="F17" s="25">
         <v>20</v>
@@ -5312,7 +5560,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C18" s="18" t="s">
         <v>34</v>
@@ -5321,7 +5569,7 @@
         <v>5</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="F18" s="21">
         <v>15</v>
@@ -5354,7 +5602,7 @@
         <v>35</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C19" s="22" t="s">
         <v>36</v>
@@ -5363,7 +5611,7 @@
         <v>78</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="F19" s="25">
         <v>15</v>
@@ -5393,19 +5641,19 @@
     </row>
     <row r="20" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D20" s="19">
         <v>0</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F20" s="21">
         <v>25</v>
@@ -5435,19 +5683,19 @@
     </row>
     <row r="21" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D21" s="23">
         <v>2</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F21" s="25">
         <v>26.4</v>
@@ -5477,19 +5725,19 @@
     </row>
     <row r="22" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="16" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D22" s="19">
         <v>0</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F22" s="21">
         <v>18.600000000000001</v>
@@ -5522,7 +5770,7 @@
         <v>37</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C23" s="22" t="s">
         <v>38</v>
@@ -5531,7 +5779,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F23" s="25">
         <v>15.6</v>
@@ -5561,19 +5809,19 @@
     </row>
     <row r="24" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D24" s="19">
         <v>0</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F24" s="21">
         <v>17</v>
@@ -5606,7 +5854,7 @@
         <v>39</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C25" s="22" t="s">
         <v>40</v>
@@ -5615,7 +5863,7 @@
         <v>3</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F25" s="25">
         <v>24</v>
@@ -5648,7 +5896,7 @@
         <v>41</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C26" s="18" t="s">
         <v>42</v>
@@ -5657,7 +5905,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F26" s="21">
         <v>24.5</v>
@@ -5690,7 +5938,7 @@
         <v>43</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C27" s="22" t="s">
         <v>44</v>
@@ -5699,7 +5947,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="F27" s="25">
         <v>23.1</v>
@@ -5732,7 +5980,7 @@
         <v>45</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C28" s="18" t="s">
         <v>46</v>
@@ -5741,7 +5989,7 @@
         <v>4</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="F28" s="21">
         <v>30</v>
@@ -5774,7 +6022,7 @@
         <v>47</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C29" s="22" t="s">
         <v>48</v>
@@ -5783,7 +6031,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F29" s="25">
         <v>22.2</v>
@@ -5816,7 +6064,7 @@
         <v>49</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C30" s="18" t="s">
         <v>50</v>
@@ -5825,7 +6073,7 @@
         <v>8</v>
       </c>
       <c r="E30" s="20" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F30" s="21">
         <v>23.8</v>
@@ -5858,7 +6106,7 @@
         <v>51</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C31" s="22" t="s">
         <v>52</v>
@@ -5867,7 +6115,7 @@
         <v>2</v>
       </c>
       <c r="E31" s="24" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F31" s="25">
         <v>5</v>
@@ -5900,7 +6148,7 @@
         <v>53</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C32" s="18" t="s">
         <v>54</v>
@@ -5909,7 +6157,7 @@
         <v>1</v>
       </c>
       <c r="E32" s="20" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="F32" s="21">
         <v>30</v>
@@ -5942,7 +6190,7 @@
         <v>55</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C33" s="22" t="s">
         <v>56</v>
@@ -5951,7 +6199,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="24" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F33" s="25">
         <v>28.8</v>
@@ -5984,7 +6232,7 @@
         <v>57</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C34" s="18" t="s">
         <v>58</v>
@@ -5993,7 +6241,7 @@
         <v>7</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F34" s="21">
         <v>18</v>
@@ -6026,7 +6274,7 @@
         <v>59</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C35" s="22" t="s">
         <v>60</v>
@@ -6035,7 +6283,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F35" s="25">
         <v>20.3</v>
@@ -6068,7 +6316,7 @@
         <v>61</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C36" s="18" t="s">
         <v>62</v>
@@ -6077,7 +6325,7 @@
         <v>2</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F36" s="21">
         <v>27.2</v>
@@ -6110,7 +6358,7 @@
         <v>63</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C37" s="22" t="s">
         <v>64</v>
@@ -6119,7 +6367,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="24" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F37" s="25">
         <v>12.6</v>
@@ -6152,7 +6400,7 @@
         <v>65</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C38" s="18" t="s">
         <v>66</v>
@@ -6161,7 +6409,7 @@
         <v>1</v>
       </c>
       <c r="E38" s="20" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F38" s="21">
         <v>24</v>
@@ -6194,7 +6442,7 @@
         <v>67</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C39" s="22" t="s">
         <v>68</v>
@@ -6203,7 +6451,7 @@
         <v>1</v>
       </c>
       <c r="E39" s="24" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F39" s="25">
         <v>30.3</v>
@@ -6236,7 +6484,7 @@
         <v>69</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C40" s="18" t="s">
         <v>70</v>
@@ -6245,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="20" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F40" s="21">
         <v>30.3</v>
@@ -6278,7 +6526,7 @@
         <v>71</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C41" s="22" t="s">
         <v>72</v>
@@ -6287,7 +6535,7 @@
         <v>1</v>
       </c>
       <c r="E41" s="24" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F41" s="25">
         <v>31.4</v>
@@ -6320,7 +6568,7 @@
         <v>73</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C42" s="18" t="s">
         <v>74</v>
@@ -6329,7 +6577,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="20" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F42" s="21">
         <v>25.5</v>
@@ -6362,7 +6610,7 @@
         <v>75</v>
       </c>
       <c r="B43" s="22" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C43" s="22" t="s">
         <v>76</v>
@@ -6371,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="E43" s="24" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F43" s="25">
         <v>24</v>
@@ -6404,7 +6652,7 @@
         <v>77</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C44" s="18" t="s">
         <v>78</v>
@@ -6413,7 +6661,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="20" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F44" s="21">
         <v>18</v>
@@ -6446,7 +6694,7 @@
         <v>79</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C45" s="22" t="s">
         <v>80</v>
@@ -6455,7 +6703,7 @@
         <v>2</v>
       </c>
       <c r="E45" s="24" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F45" s="25">
         <v>24</v>
@@ -6488,7 +6736,7 @@
         <v>81</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C46" s="18" t="s">
         <v>82</v>
@@ -6497,7 +6745,7 @@
         <v>1</v>
       </c>
       <c r="E46" s="20" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F46" s="21">
         <v>29.1</v>
@@ -6530,7 +6778,7 @@
         <v>83</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C47" s="22" t="s">
         <v>84</v>
@@ -6539,7 +6787,7 @@
         <v>2</v>
       </c>
       <c r="E47" s="24" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F47" s="25">
         <v>24</v>
@@ -6572,7 +6820,7 @@
         <v>85</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C48" s="18" t="s">
         <v>86</v>
@@ -6581,7 +6829,7 @@
         <v>2</v>
       </c>
       <c r="E48" s="20" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F48" s="21">
         <v>15.8</v>
@@ -6614,7 +6862,7 @@
         <v>87</v>
       </c>
       <c r="B49" s="22" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C49" s="22" t="s">
         <v>88</v>
@@ -6623,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="E49" s="24" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F49" s="25">
         <v>18</v>
@@ -6656,7 +6904,7 @@
         <v>89</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C50" s="18" t="s">
         <v>90</v>
@@ -6665,7 +6913,7 @@
         <v>3</v>
       </c>
       <c r="E50" s="20" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F50" s="21">
         <v>33</v>
@@ -6698,7 +6946,7 @@
         <v>91</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C51" s="22" t="s">
         <v>92</v>
@@ -6707,7 +6955,7 @@
         <v>14</v>
       </c>
       <c r="E51" s="24" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F51" s="25">
         <v>24</v>
@@ -6740,7 +6988,7 @@
         <v>93</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C52" s="18" t="s">
         <v>94</v>
@@ -6749,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="20" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F52" s="21">
         <v>24</v>
@@ -6782,7 +7030,7 @@
         <v>95</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C53" s="22" t="s">
         <v>96</v>
@@ -6791,7 +7039,7 @@
         <v>2</v>
       </c>
       <c r="E53" s="24" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F53" s="25">
         <v>24</v>
@@ -6824,7 +7072,7 @@
         <v>97</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C54" s="18" t="s">
         <v>98</v>
@@ -6833,7 +7081,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="20" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F54" s="21">
         <v>24</v>
@@ -6866,7 +7114,7 @@
         <v>99</v>
       </c>
       <c r="B55" s="22" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C55" s="22" t="s">
         <v>100</v>
@@ -6875,7 +7123,7 @@
         <v>0</v>
       </c>
       <c r="E55" s="24" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F55" s="25">
         <v>31.2</v>
@@ -6908,7 +7156,7 @@
         <v>101</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C56" s="18" t="s">
         <v>102</v>
@@ -6917,7 +7165,7 @@
         <v>1</v>
       </c>
       <c r="E56" s="20" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F56" s="21">
         <v>15</v>
@@ -6950,7 +7198,7 @@
         <v>103</v>
       </c>
       <c r="B57" s="22" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C57" s="22" t="s">
         <v>104</v>
@@ -6959,7 +7207,7 @@
         <v>3</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F57" s="25">
         <v>26.8</v>
@@ -6992,7 +7240,7 @@
         <v>105</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C58" s="18" t="s">
         <v>106</v>
@@ -7001,7 +7249,7 @@
         <v>5</v>
       </c>
       <c r="E58" s="20" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F58" s="21">
         <v>24</v>
@@ -7034,7 +7282,7 @@
         <v>107</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C59" s="22" t="s">
         <v>108</v>
@@ -7043,7 +7291,7 @@
         <v>0</v>
       </c>
       <c r="E59" s="24" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F59" s="25">
         <v>22.8</v>
@@ -7076,7 +7324,7 @@
         <v>109</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C60" s="18" t="s">
         <v>110</v>
@@ -7085,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="20" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F60" s="21">
         <v>26.1</v>
@@ -7118,7 +7366,7 @@
         <v>111</v>
       </c>
       <c r="B61" s="22" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C61" s="22" t="s">
         <v>112</v>
@@ -7127,7 +7375,7 @@
         <v>1</v>
       </c>
       <c r="E61" s="24" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="F61" s="25">
         <v>24</v>
@@ -7160,7 +7408,7 @@
         <v>113</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C62" s="18" t="s">
         <v>114</v>
@@ -7169,7 +7417,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="20" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F62" s="21">
         <v>18</v>
@@ -7202,7 +7450,7 @@
         <v>115</v>
       </c>
       <c r="B63" s="22" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C63" s="22" t="s">
         <v>116</v>
@@ -7211,7 +7459,7 @@
         <v>0</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F63" s="25">
         <v>27</v>
@@ -7244,7 +7492,7 @@
         <v>117</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C64" s="18" t="s">
         <v>118</v>
@@ -7253,7 +7501,7 @@
         <v>3</v>
       </c>
       <c r="E64" s="20" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F64" s="21">
         <v>16.8</v>
@@ -7286,7 +7534,7 @@
         <v>119</v>
       </c>
       <c r="B65" s="22" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C65" s="22" t="s">
         <v>120</v>
@@ -7295,7 +7543,7 @@
         <v>1</v>
       </c>
       <c r="E65" s="24" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F65" s="25">
         <v>24</v>
@@ -7328,7 +7576,7 @@
         <v>121</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C66" s="18" t="s">
         <v>122</v>
@@ -7337,7 +7585,7 @@
         <v>1</v>
       </c>
       <c r="E66" s="20" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F66" s="21">
         <v>18</v>
@@ -7370,7 +7618,7 @@
         <v>123</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C67" s="22" t="s">
         <v>124</v>
@@ -7379,7 +7627,7 @@
         <v>4</v>
       </c>
       <c r="E67" s="24" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F67" s="25">
         <v>19.399999999999999</v>
@@ -7412,7 +7660,7 @@
         <v>125</v>
       </c>
       <c r="B68" s="18" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C68" s="18" t="s">
         <v>126</v>
@@ -7421,7 +7669,7 @@
         <v>8</v>
       </c>
       <c r="E68" s="20" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F68" s="21">
         <v>30</v>
@@ -7454,7 +7702,7 @@
         <v>127</v>
       </c>
       <c r="B69" s="22" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C69" s="22" t="s">
         <v>128</v>
@@ -7463,7 +7711,7 @@
         <v>3</v>
       </c>
       <c r="E69" s="24" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F69" s="25">
         <v>27</v>
@@ -7496,7 +7744,7 @@
         <v>129</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C70" s="18" t="s">
         <v>130</v>
@@ -7505,7 +7753,7 @@
         <v>2</v>
       </c>
       <c r="E70" s="20" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F70" s="21">
         <v>16.899999999999999</v>
@@ -7538,7 +7786,7 @@
         <v>131</v>
       </c>
       <c r="B71" s="22" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C71" s="22" t="s">
         <v>132</v>
@@ -7547,7 +7795,7 @@
         <v>9</v>
       </c>
       <c r="E71" s="24" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F71" s="25">
         <v>24</v>
@@ -7580,7 +7828,7 @@
         <v>133</v>
       </c>
       <c r="B72" s="18" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C72" s="18" t="s">
         <v>134</v>
@@ -7589,7 +7837,7 @@
         <v>0</v>
       </c>
       <c r="E72" s="20" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F72" s="21">
         <v>24</v>
@@ -7622,16 +7870,16 @@
         <v>135</v>
       </c>
       <c r="B73" s="22" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C73" s="22" t="s">
         <v>136</v>
       </c>
       <c r="D73" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" s="24" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F73" s="25">
         <v>16.399999999999999</v>
@@ -7664,7 +7912,7 @@
         <v>137</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C74" s="18" t="s">
         <v>138</v>
@@ -7673,7 +7921,7 @@
         <v>21</v>
       </c>
       <c r="E74" s="20" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F74" s="21">
         <v>18</v>
@@ -7706,7 +7954,7 @@
         <v>139</v>
       </c>
       <c r="B75" s="22" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C75" s="22" t="s">
         <v>140</v>
@@ -7715,7 +7963,7 @@
         <v>1</v>
       </c>
       <c r="E75" s="24" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F75" s="25">
         <v>31.6</v>
@@ -7757,7 +8005,7 @@
         <v>2</v>
       </c>
       <c r="E76" s="20" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F76" s="21">
         <v>18.899999999999999</v>
@@ -7790,7 +8038,7 @@
         <v>144</v>
       </c>
       <c r="B77" s="22" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C77" s="22" t="s">
         <v>145</v>
@@ -7799,7 +8047,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="24" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F77" s="25">
         <v>34</v>
@@ -7832,7 +8080,7 @@
         <v>146</v>
       </c>
       <c r="B78" s="18" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C78" s="18" t="s">
         <v>147</v>
@@ -7841,7 +8089,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="20" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F78" s="21">
         <v>15.3</v>
@@ -7874,7 +8122,7 @@
         <v>148</v>
       </c>
       <c r="B79" s="22" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C79" s="22" t="s">
         <v>149</v>
@@ -7883,7 +8131,7 @@
         <v>2</v>
       </c>
       <c r="E79" s="24" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F79" s="25">
         <v>19</v>
@@ -7916,7 +8164,7 @@
         <v>150</v>
       </c>
       <c r="B80" s="18" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C80" s="18" t="s">
         <v>151</v>
@@ -7925,7 +8173,7 @@
         <v>1</v>
       </c>
       <c r="E80" s="20" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F80" s="21">
         <v>35.4</v>
@@ -7958,7 +8206,7 @@
         <v>152</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C81" s="22" t="s">
         <v>153</v>
@@ -7967,7 +8215,7 @@
         <v>1</v>
       </c>
       <c r="E81" s="24" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F81" s="25">
         <v>24.5</v>
@@ -8000,7 +8248,7 @@
         <v>154</v>
       </c>
       <c r="B82" s="18" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C82" s="18" t="s">
         <v>155</v>
@@ -8009,7 +8257,7 @@
         <v>2</v>
       </c>
       <c r="E82" s="20" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F82" s="21">
         <v>20</v>
@@ -8042,7 +8290,7 @@
         <v>156</v>
       </c>
       <c r="B83" s="22" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C83" s="22" t="s">
         <v>157</v>
@@ -8051,7 +8299,7 @@
         <v>2</v>
       </c>
       <c r="E83" s="24" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F83" s="25">
         <v>30</v>
@@ -8084,7 +8332,7 @@
         <v>158</v>
       </c>
       <c r="B84" s="18" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C84" s="18" t="s">
         <v>159</v>
@@ -8093,7 +8341,7 @@
         <v>3</v>
       </c>
       <c r="E84" s="20" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F84" s="21">
         <v>30</v>
@@ -8126,7 +8374,7 @@
         <v>160</v>
       </c>
       <c r="B85" s="22" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C85" s="22" t="s">
         <v>161</v>
@@ -8135,7 +8383,7 @@
         <v>3</v>
       </c>
       <c r="E85" s="24" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F85" s="25">
         <v>28.8</v>
@@ -8168,16 +8416,16 @@
         <v>162</v>
       </c>
       <c r="B86" s="18" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C86" s="18" t="s">
         <v>163</v>
       </c>
       <c r="D86" s="19">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E86" s="20" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F86" s="21">
         <v>24</v>
@@ -8210,7 +8458,7 @@
         <v>164</v>
       </c>
       <c r="B87" s="22" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C87" s="22" t="s">
         <v>165</v>
@@ -8219,7 +8467,7 @@
         <v>3</v>
       </c>
       <c r="E87" s="24" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F87" s="25">
         <v>24</v>
@@ -8252,7 +8500,7 @@
         <v>166</v>
       </c>
       <c r="B88" s="18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C88" s="18" t="s">
         <v>167</v>
@@ -8261,7 +8509,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="20" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="F88" s="21">
         <v>14.3</v>
@@ -8294,7 +8542,7 @@
         <v>168</v>
       </c>
       <c r="B89" s="22" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C89" s="22" t="s">
         <v>169</v>
@@ -8303,7 +8551,7 @@
         <v>1</v>
       </c>
       <c r="E89" s="24" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F89" s="25">
         <v>25.4</v>
@@ -8336,7 +8584,7 @@
         <v>170</v>
       </c>
       <c r="B90" s="18" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C90" s="18" t="s">
         <v>171</v>
@@ -8345,7 +8593,7 @@
         <v>2</v>
       </c>
       <c r="E90" s="20" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F90" s="21">
         <v>18.2</v>
@@ -8378,7 +8626,7 @@
         <v>172</v>
       </c>
       <c r="B91" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C91" s="22" t="s">
         <v>173</v>
@@ -8387,7 +8635,7 @@
         <v>5</v>
       </c>
       <c r="E91" s="24" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F91" s="25">
         <v>18.399999999999999</v>
@@ -8420,7 +8668,7 @@
         <v>174</v>
       </c>
       <c r="B92" s="18" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C92" s="18" t="s">
         <v>175</v>
@@ -8429,7 +8677,7 @@
         <v>29</v>
       </c>
       <c r="E92" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F92" s="21">
         <v>19.2</v>
@@ -8462,7 +8710,7 @@
         <v>176</v>
       </c>
       <c r="B93" s="22" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C93" s="22" t="s">
         <v>177</v>
@@ -8471,7 +8719,7 @@
         <v>2</v>
       </c>
       <c r="E93" s="24" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F93" s="25">
         <v>24.8</v>
@@ -8504,7 +8752,7 @@
         <v>178</v>
       </c>
       <c r="B94" s="18" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C94" s="18" t="s">
         <v>179</v>
@@ -8513,7 +8761,7 @@
         <v>7</v>
       </c>
       <c r="E94" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="F94" s="21">
         <v>24</v>
@@ -8546,7 +8794,7 @@
         <v>180</v>
       </c>
       <c r="B95" s="22" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C95" s="22" t="s">
         <v>181</v>
@@ -8555,7 +8803,7 @@
         <v>31</v>
       </c>
       <c r="E95" s="24" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F95" s="25">
         <v>19.8</v>
@@ -8585,19 +8833,19 @@
     </row>
     <row r="96" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>510</v>
+      </c>
+      <c r="C96" s="18" t="s">
         <v>421</v>
-      </c>
-      <c r="B96" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="C96" s="18" t="s">
-        <v>422</v>
       </c>
       <c r="D96" s="19">
         <v>1</v>
       </c>
       <c r="E96" s="20" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F96" s="21">
         <v>24</v>
@@ -8630,7 +8878,7 @@
         <v>182</v>
       </c>
       <c r="B97" s="22" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C97" s="22" t="s">
         <v>183</v>
@@ -8639,7 +8887,7 @@
         <v>27</v>
       </c>
       <c r="E97" s="24" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F97" s="25">
         <v>16</v>
@@ -8672,7 +8920,7 @@
         <v>184</v>
       </c>
       <c r="B98" s="18" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C98" s="18" t="s">
         <v>185</v>
@@ -8681,7 +8929,7 @@
         <v>9</v>
       </c>
       <c r="E98" s="20" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F98" s="21">
         <v>14</v>
@@ -8714,7 +8962,7 @@
         <v>186</v>
       </c>
       <c r="B99" s="22" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C99" s="22" t="s">
         <v>187</v>
@@ -8723,7 +8971,7 @@
         <v>1</v>
       </c>
       <c r="E99" s="24" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F99" s="25">
         <v>32.4</v>
@@ -8756,7 +9004,7 @@
         <v>188</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C100" s="18" t="s">
         <v>189</v>
@@ -8765,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="20" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F100" s="21">
         <v>32.4</v>
@@ -8798,7 +9046,7 @@
         <v>190</v>
       </c>
       <c r="B101" s="22" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C101" s="22" t="s">
         <v>191</v>
@@ -8807,7 +9055,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="24" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F101" s="25">
         <v>20</v>
@@ -8840,7 +9088,7 @@
         <v>192</v>
       </c>
       <c r="B102" s="18" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C102" s="18" t="s">
         <v>193</v>
@@ -8849,7 +9097,7 @@
         <v>4</v>
       </c>
       <c r="E102" s="20" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F102" s="21">
         <v>24</v>
@@ -8882,7 +9130,7 @@
         <v>194</v>
       </c>
       <c r="B103" s="22" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C103" s="22" t="s">
         <v>195</v>
@@ -8891,7 +9139,7 @@
         <v>2</v>
       </c>
       <c r="E103" s="24" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F103" s="25">
         <v>18.399999999999999</v>
@@ -8924,7 +9172,7 @@
         <v>196</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C104" s="18" t="s">
         <v>197</v>
@@ -8933,7 +9181,7 @@
         <v>23</v>
       </c>
       <c r="E104" s="20" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F104" s="21">
         <v>28.8</v>
@@ -8966,16 +9214,16 @@
         <v>198</v>
       </c>
       <c r="B105" s="22" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C105" s="22" t="s">
         <v>199</v>
       </c>
       <c r="D105" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" s="24" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F105" s="25">
         <v>22.5</v>
@@ -9008,7 +9256,7 @@
         <v>200</v>
       </c>
       <c r="B106" s="18" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C106" s="18" t="s">
         <v>201</v>
@@ -9017,7 +9265,7 @@
         <v>0</v>
       </c>
       <c r="E106" s="20" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F106" s="21">
         <v>24</v>
@@ -9050,7 +9298,7 @@
         <v>203</v>
       </c>
       <c r="B107" s="18" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C107" s="18" t="s">
         <v>204</v>
@@ -9059,7 +9307,7 @@
         <v>1</v>
       </c>
       <c r="E107" s="20" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F107" s="21">
         <v>17.100000000000001</v>
@@ -9092,7 +9340,7 @@
         <v>205</v>
       </c>
       <c r="B108" s="22" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C108" s="22" t="s">
         <v>206</v>
@@ -9101,7 +9349,7 @@
         <v>0</v>
       </c>
       <c r="E108" s="24" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F108" s="25">
         <v>24</v>
@@ -9134,7 +9382,7 @@
         <v>207</v>
       </c>
       <c r="B109" s="18" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C109" s="18" t="s">
         <v>208</v>
@@ -9143,7 +9391,7 @@
         <v>1</v>
       </c>
       <c r="E109" s="20" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F109" s="21">
         <v>33.299999999999997</v>
@@ -9176,7 +9424,7 @@
         <v>209</v>
       </c>
       <c r="B110" s="22" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C110" s="22" t="s">
         <v>210</v>
@@ -9185,7 +9433,7 @@
         <v>1</v>
       </c>
       <c r="E110" s="24" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F110" s="25">
         <v>24</v>
@@ -9218,7 +9466,7 @@
         <v>211</v>
       </c>
       <c r="B111" s="18" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C111" s="18" t="s">
         <v>212</v>
@@ -9227,7 +9475,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="20" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="F111" s="21">
         <v>19.5</v>
@@ -9257,19 +9505,19 @@
     </row>
     <row r="112" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="17" t="s">
+        <v>642</v>
+      </c>
+      <c r="B112" s="22" t="s">
         <v>643</v>
       </c>
-      <c r="B112" s="22" t="s">
+      <c r="C112" s="22" t="s">
         <v>644</v>
-      </c>
-      <c r="C112" s="22" t="s">
-        <v>645</v>
       </c>
       <c r="D112" s="23">
         <v>2</v>
       </c>
       <c r="E112" s="24" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F112" s="25">
         <v>24</v>
@@ -9302,7 +9550,7 @@
         <v>213</v>
       </c>
       <c r="B113" s="18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C113" s="18" t="s">
         <v>214</v>
@@ -9311,7 +9559,7 @@
         <v>3</v>
       </c>
       <c r="E113" s="20" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F113" s="21">
         <v>29.2</v>
@@ -9344,7 +9592,7 @@
         <v>215</v>
       </c>
       <c r="B114" s="22" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C114" s="22" t="s">
         <v>216</v>
@@ -9353,7 +9601,7 @@
         <v>2</v>
       </c>
       <c r="E114" s="24" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F114" s="25">
         <v>32</v>
@@ -9386,7 +9634,7 @@
         <v>217</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C115" s="18" t="s">
         <v>218</v>
@@ -9395,7 +9643,7 @@
         <v>4</v>
       </c>
       <c r="E115" s="20" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F115" s="21">
         <v>20.6</v>
@@ -9428,16 +9676,16 @@
         <v>219</v>
       </c>
       <c r="B116" s="22" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C116" s="22" t="s">
         <v>220</v>
       </c>
       <c r="D116" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E116" s="24" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F116" s="25">
         <v>26</v>
@@ -9470,7 +9718,7 @@
         <v>221</v>
       </c>
       <c r="B117" s="18" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C117" s="18" t="s">
         <v>222</v>
@@ -9479,7 +9727,7 @@
         <v>2</v>
       </c>
       <c r="E117" s="20" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F117" s="21">
         <v>15</v>
@@ -9512,7 +9760,7 @@
         <v>223</v>
       </c>
       <c r="B118" s="22" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C118" s="22" t="s">
         <v>224</v>
@@ -9521,7 +9769,7 @@
         <v>8</v>
       </c>
       <c r="E118" s="24" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="F118" s="25">
         <v>33</v>
@@ -9554,7 +9802,7 @@
         <v>225</v>
       </c>
       <c r="B119" s="18" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C119" s="18" t="s">
         <v>226</v>
@@ -9563,7 +9811,7 @@
         <v>2</v>
       </c>
       <c r="E119" s="20" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F119" s="21">
         <v>24</v>
@@ -9596,7 +9844,7 @@
         <v>227</v>
       </c>
       <c r="B120" s="22" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C120" s="22" t="s">
         <v>228</v>
@@ -9605,7 +9853,7 @@
         <v>1</v>
       </c>
       <c r="E120" s="24" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F120" s="25">
         <v>21</v>
@@ -9638,7 +9886,7 @@
         <v>229</v>
       </c>
       <c r="B121" s="18" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C121" s="18" t="s">
         <v>230</v>
@@ -9647,7 +9895,7 @@
         <v>4</v>
       </c>
       <c r="E121" s="20" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F121" s="21">
         <v>19.2</v>
@@ -9680,16 +9928,16 @@
         <v>231</v>
       </c>
       <c r="B122" s="22" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C122" s="22" t="s">
         <v>232</v>
       </c>
       <c r="D122" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E122" s="24" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F122" s="25">
         <v>32</v>
@@ -9722,7 +9970,7 @@
         <v>233</v>
       </c>
       <c r="B123" s="18" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C123" s="18" t="s">
         <v>234</v>
@@ -9731,7 +9979,7 @@
         <v>1</v>
       </c>
       <c r="E123" s="20" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F123" s="21">
         <v>25.4</v>
@@ -9764,7 +10012,7 @@
         <v>235</v>
       </c>
       <c r="B124" s="22" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C124" s="22" t="s">
         <v>236</v>
@@ -9773,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="E124" s="24" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F124" s="25">
         <v>31.5</v>
@@ -9806,7 +10054,7 @@
         <v>237</v>
       </c>
       <c r="B125" s="18" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C125" s="18" t="s">
         <v>238</v>
@@ -9815,7 +10063,7 @@
         <v>1</v>
       </c>
       <c r="E125" s="20" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="F125" s="21">
         <v>18</v>
@@ -9848,7 +10096,7 @@
         <v>239</v>
       </c>
       <c r="B126" s="22" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C126" s="22" t="s">
         <v>240</v>
@@ -9857,7 +10105,7 @@
         <v>3</v>
       </c>
       <c r="E126" s="24" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F126" s="25">
         <v>38</v>
@@ -9890,7 +10138,7 @@
         <v>241</v>
       </c>
       <c r="B127" s="18" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C127" s="18" t="s">
         <v>242</v>
@@ -9899,7 +10147,7 @@
         <v>0</v>
       </c>
       <c r="E127" s="20" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F127" s="21">
         <v>24</v>
@@ -9932,7 +10180,7 @@
         <v>243</v>
       </c>
       <c r="B128" s="22" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C128" s="22" t="s">
         <v>244</v>
@@ -9941,7 +10189,7 @@
         <v>25</v>
       </c>
       <c r="E128" s="24" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="F128" s="25">
         <v>28.5</v>
@@ -9974,7 +10222,7 @@
         <v>245</v>
       </c>
       <c r="B129" s="18" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C129" s="18" t="s">
         <v>246</v>
@@ -9983,7 +10231,7 @@
         <v>39</v>
       </c>
       <c r="E129" s="20" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F129" s="21">
         <v>18</v>
@@ -10016,7 +10264,7 @@
         <v>247</v>
       </c>
       <c r="B130" s="22" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C130" s="22" t="s">
         <v>248</v>
@@ -10025,7 +10273,7 @@
         <v>1</v>
       </c>
       <c r="E130" s="24" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="F130" s="25">
         <v>28.8</v>
@@ -10058,7 +10306,7 @@
         <v>249</v>
       </c>
       <c r="B131" s="18" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C131" s="18" t="s">
         <v>250</v>
@@ -10067,7 +10315,7 @@
         <v>2</v>
       </c>
       <c r="E131" s="20" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F131" s="21">
         <v>28.8</v>
@@ -10100,7 +10348,7 @@
         <v>251</v>
       </c>
       <c r="B132" s="22" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C132" s="22" t="s">
         <v>252</v>
@@ -10109,7 +10357,7 @@
         <v>1</v>
       </c>
       <c r="E132" s="24" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F132" s="25">
         <v>24</v>
@@ -10142,7 +10390,7 @@
         <v>253</v>
       </c>
       <c r="B133" s="18" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C133" s="18" t="s">
         <v>254</v>
@@ -10151,7 +10399,7 @@
         <v>6</v>
       </c>
       <c r="E133" s="20" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F133" s="21">
         <v>18</v>
@@ -10184,16 +10432,16 @@
         <v>255</v>
       </c>
       <c r="B134" s="22" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="C134" s="22" t="s">
         <v>256</v>
       </c>
       <c r="D134" s="23">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E134" s="24" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F134" s="25">
         <v>24</v>
@@ -10226,7 +10474,7 @@
         <v>257</v>
       </c>
       <c r="B135" s="18" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C135" s="18" t="s">
         <v>258</v>
@@ -10235,7 +10483,7 @@
         <v>2</v>
       </c>
       <c r="E135" s="20" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F135" s="21">
         <v>33.6</v>
@@ -10265,19 +10513,19 @@
     </row>
     <row r="136" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="17" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B136" s="22" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C136" s="22" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="D136" s="23">
         <v>0</v>
       </c>
       <c r="E136" s="24" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F136" s="25">
         <v>23</v>
@@ -10310,7 +10558,7 @@
         <v>259</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C137" s="18" t="s">
         <v>260</v>
@@ -10319,7 +10567,7 @@
         <v>4</v>
       </c>
       <c r="E137" s="20" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="F137" s="21">
         <v>24.3</v>
@@ -10352,16 +10600,16 @@
         <v>261</v>
       </c>
       <c r="B138" s="22" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C138" s="22" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D138" s="23">
         <v>0</v>
       </c>
       <c r="E138" s="24" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F138" s="25">
         <v>18</v>
@@ -10394,7 +10642,7 @@
         <v>262</v>
       </c>
       <c r="B139" s="18" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C139" s="18" t="s">
         <v>263</v>
@@ -10403,7 +10651,7 @@
         <v>1</v>
       </c>
       <c r="E139" s="20" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F139" s="21">
         <v>24.6</v>
@@ -10436,7 +10684,7 @@
         <v>264</v>
       </c>
       <c r="B140" s="22" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C140" s="22" t="s">
         <v>265</v>
@@ -10445,7 +10693,7 @@
         <v>1</v>
       </c>
       <c r="E140" s="24" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="F140" s="25">
         <v>20.399999999999999</v>
@@ -10478,7 +10726,7 @@
         <v>266</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C141" s="18" t="s">
         <v>267</v>
@@ -10487,7 +10735,7 @@
         <v>0</v>
       </c>
       <c r="E141" s="20" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="F141" s="21">
         <v>12</v>
@@ -10520,7 +10768,7 @@
         <v>268</v>
       </c>
       <c r="B142" s="22" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C142" s="22" t="s">
         <v>269</v>
@@ -10529,7 +10777,7 @@
         <v>11</v>
       </c>
       <c r="E142" s="24" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="F142" s="25">
         <v>24</v>
@@ -10559,19 +10807,19 @@
     </row>
     <row r="143" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="17" t="s">
+        <v>959</v>
+      </c>
+      <c r="B143" s="22" t="s">
         <v>960</v>
       </c>
-      <c r="B143" s="22" t="s">
+      <c r="C143" s="22" t="s">
         <v>961</v>
-      </c>
-      <c r="C143" s="22" t="s">
-        <v>962</v>
       </c>
       <c r="D143" s="23">
         <v>3</v>
       </c>
       <c r="E143" s="24" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="F143" s="25">
         <v>0</v>
@@ -10604,16 +10852,16 @@
         <v>270</v>
       </c>
       <c r="B144" s="18" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C144" s="18" t="s">
         <v>271</v>
       </c>
       <c r="D144" s="19">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E144" s="20" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F144" s="21">
         <v>24</v>
@@ -10646,7 +10894,7 @@
         <v>272</v>
       </c>
       <c r="B145" s="22" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C145" s="22" t="s">
         <v>273</v>
@@ -10655,7 +10903,7 @@
         <v>0</v>
       </c>
       <c r="E145" s="24" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F145" s="25">
         <v>35.1</v>
@@ -10688,7 +10936,7 @@
         <v>274</v>
       </c>
       <c r="B146" s="18" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C146" s="18" t="s">
         <v>275</v>
@@ -10697,7 +10945,7 @@
         <v>5</v>
       </c>
       <c r="E146" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F146" s="21">
         <v>18.2</v>
@@ -10730,7 +10978,7 @@
         <v>276</v>
       </c>
       <c r="B147" s="22" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C147" s="22" t="s">
         <v>277</v>
@@ -10739,7 +10987,7 @@
         <v>33</v>
       </c>
       <c r="E147" s="24" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F147" s="25">
         <v>24.3</v>
@@ -10772,7 +11020,7 @@
         <v>278</v>
       </c>
       <c r="B148" s="18" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C148" s="18" t="s">
         <v>279</v>
@@ -10781,7 +11029,7 @@
         <v>6</v>
       </c>
       <c r="E148" s="20" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F148" s="21">
         <v>15.9</v>
@@ -10814,7 +11062,7 @@
         <v>280</v>
       </c>
       <c r="B149" s="22" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C149" s="22" t="s">
         <v>281</v>
@@ -10823,7 +11071,7 @@
         <v>1</v>
       </c>
       <c r="E149" s="24" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F149" s="25">
         <v>24.3</v>
@@ -10856,7 +11104,7 @@
         <v>282</v>
       </c>
       <c r="B150" s="18" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C150" s="18" t="s">
         <v>283</v>
@@ -10865,7 +11113,7 @@
         <v>1</v>
       </c>
       <c r="E150" s="20" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F150" s="21">
         <v>18</v>
@@ -10898,7 +11146,7 @@
         <v>284</v>
       </c>
       <c r="B151" s="22" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C151" s="22" t="s">
         <v>285</v>
@@ -10907,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="E151" s="24" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F151" s="25">
         <v>26.4</v>
@@ -10940,7 +11188,7 @@
         <v>286</v>
       </c>
       <c r="B152" s="18" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C152" s="18" t="s">
         <v>287</v>
@@ -10949,7 +11197,7 @@
         <v>14</v>
       </c>
       <c r="E152" s="20" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F152" s="21">
         <v>12</v>
@@ -10982,7 +11230,7 @@
         <v>288</v>
       </c>
       <c r="B153" s="22" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C153" s="22" t="s">
         <v>289</v>
@@ -10991,7 +11239,7 @@
         <v>1</v>
       </c>
       <c r="E153" s="24" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F153" s="25">
         <v>30</v>
@@ -11024,7 +11272,7 @@
         <v>290</v>
       </c>
       <c r="B154" s="18" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C154" s="18" t="s">
         <v>291</v>
@@ -11033,7 +11281,7 @@
         <v>10</v>
       </c>
       <c r="E154" s="20" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F154" s="21">
         <v>18</v>
@@ -11066,7 +11314,7 @@
         <v>292</v>
       </c>
       <c r="B155" s="22" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C155" s="22" t="s">
         <v>293</v>
@@ -11075,7 +11323,7 @@
         <v>12</v>
       </c>
       <c r="E155" s="24" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="F155" s="25">
         <v>24</v>
@@ -11108,7 +11356,7 @@
         <v>294</v>
       </c>
       <c r="B156" s="18" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C156" s="18" t="s">
         <v>295</v>
@@ -11117,7 +11365,7 @@
         <v>4</v>
       </c>
       <c r="E156" s="20" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="F156" s="21">
         <v>27.2</v>
@@ -11147,19 +11395,19 @@
     </row>
     <row r="157" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="17" t="s">
+        <v>976</v>
+      </c>
+      <c r="B157" s="22" t="s">
         <v>977</v>
       </c>
-      <c r="B157" s="22" t="s">
+      <c r="C157" s="22" t="s">
         <v>978</v>
-      </c>
-      <c r="C157" s="22" t="s">
-        <v>979</v>
       </c>
       <c r="D157" s="23">
         <v>0</v>
       </c>
       <c r="E157" s="24" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="F157" s="25">
         <v>0</v>
@@ -11189,19 +11437,19 @@
     </row>
     <row r="158" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="17" t="s">
+        <v>980</v>
+      </c>
+      <c r="B158" s="22" t="s">
         <v>981</v>
       </c>
-      <c r="B158" s="22" t="s">
+      <c r="C158" s="22" t="s">
         <v>982</v>
-      </c>
-      <c r="C158" s="22" t="s">
-        <v>983</v>
       </c>
       <c r="D158" s="23">
         <v>3</v>
       </c>
       <c r="E158" s="24" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F158" s="25">
         <v>0</v>
@@ -11231,19 +11479,19 @@
     </row>
     <row r="159" spans="1:26" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="17" t="s">
+        <v>984</v>
+      </c>
+      <c r="B159" s="22" t="s">
         <v>985</v>
       </c>
-      <c r="B159" s="22" t="s">
+      <c r="C159" s="22" t="s">
         <v>986</v>
-      </c>
-      <c r="C159" s="22" t="s">
-        <v>987</v>
       </c>
       <c r="D159" s="23">
         <v>1</v>
       </c>
       <c r="E159" s="24" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F159" s="25">
         <v>0</v>
@@ -11273,19 +11521,19 @@
     </row>
     <row r="160" spans="1:26" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="17" t="s">
+        <v>988</v>
+      </c>
+      <c r="B160" s="22" t="s">
         <v>989</v>
       </c>
-      <c r="B160" s="22" t="s">
+      <c r="C160" s="22" t="s">
         <v>990</v>
       </c>
-      <c r="C160" s="22" t="s">
-        <v>991</v>
-      </c>
       <c r="D160" s="23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E160" s="24" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F160" s="25">
         <v>0</v>
@@ -11318,7 +11566,7 @@
         <v>296</v>
       </c>
       <c r="B161" s="22" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C161" s="22" t="s">
         <v>297</v>
@@ -11327,7 +11575,7 @@
         <v>1</v>
       </c>
       <c r="E161" s="24" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F161" s="25">
         <v>16.2</v>
@@ -11360,7 +11608,7 @@
         <v>298</v>
       </c>
       <c r="B162" s="18" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C162" s="18" t="s">
         <v>299</v>
@@ -11369,7 +11617,7 @@
         <v>5</v>
       </c>
       <c r="E162" s="20" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F162" s="21">
         <v>20</v>
@@ -11402,7 +11650,7 @@
         <v>300</v>
       </c>
       <c r="B163" s="22" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C163" s="22" t="s">
         <v>301</v>
@@ -11411,7 +11659,7 @@
         <v>1</v>
       </c>
       <c r="E163" s="24" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F163" s="25">
         <v>5</v>
@@ -11444,7 +11692,7 @@
         <v>302</v>
       </c>
       <c r="B164" s="18" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C164" s="18" t="s">
         <v>303</v>
@@ -11453,7 +11701,7 @@
         <v>5</v>
       </c>
       <c r="E164" s="20" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F164" s="21">
         <v>35.1</v>
@@ -11486,7 +11734,7 @@
         <v>304</v>
       </c>
       <c r="B165" s="22" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C165" s="22" t="s">
         <v>305</v>
@@ -11495,7 +11743,7 @@
         <v>3</v>
       </c>
       <c r="E165" s="24" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="F165" s="25">
         <v>15</v>
@@ -11528,7 +11776,7 @@
         <v>306</v>
       </c>
       <c r="B166" s="18" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C166" s="18" t="s">
         <v>307</v>
@@ -11537,7 +11785,7 @@
         <v>15</v>
       </c>
       <c r="E166" s="20" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F166" s="21">
         <v>24</v>
@@ -11570,7 +11818,7 @@
         <v>308</v>
       </c>
       <c r="B167" s="22" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C167" s="22" t="s">
         <v>309</v>
@@ -11579,7 +11827,7 @@
         <v>5</v>
       </c>
       <c r="E167" s="24" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F167" s="25">
         <v>25.9</v>
@@ -11612,7 +11860,7 @@
         <v>310</v>
       </c>
       <c r="B168" s="18" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C168" s="18" t="s">
         <v>311</v>
@@ -11621,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="E168" s="20" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F168" s="21">
         <v>24</v>
@@ -11654,7 +11902,7 @@
         <v>312</v>
       </c>
       <c r="B169" s="22" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C169" s="22" t="s">
         <v>313</v>
@@ -11663,7 +11911,7 @@
         <v>2</v>
       </c>
       <c r="E169" s="24" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="F169" s="25">
         <v>15.6</v>
@@ -11696,7 +11944,7 @@
         <v>314</v>
       </c>
       <c r="B170" s="18" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C170" s="18" t="s">
         <v>315</v>
@@ -11705,7 +11953,7 @@
         <v>12</v>
       </c>
       <c r="E170" s="20" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F170" s="21">
         <v>16.100000000000001</v>
@@ -11738,7 +11986,7 @@
         <v>316</v>
       </c>
       <c r="B171" s="22" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C171" s="22" t="s">
         <v>317</v>
@@ -11747,7 +11995,7 @@
         <v>0</v>
       </c>
       <c r="E171" s="24" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F171" s="25">
         <v>19.5</v>
@@ -11780,7 +12028,7 @@
         <v>318</v>
       </c>
       <c r="B172" s="18" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C172" s="18" t="s">
         <v>319</v>
@@ -11789,7 +12037,7 @@
         <v>10</v>
       </c>
       <c r="E172" s="20" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F172" s="21">
         <v>24</v>
@@ -11822,7 +12070,7 @@
         <v>320</v>
       </c>
       <c r="B173" s="22" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C173" s="22" t="s">
         <v>321</v>
@@ -11831,7 +12079,7 @@
         <v>7</v>
       </c>
       <c r="E173" s="24" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F173" s="25">
         <v>21</v>
@@ -11864,7 +12112,7 @@
         <v>322</v>
       </c>
       <c r="B174" s="18" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C174" s="18" t="s">
         <v>323</v>
@@ -11873,7 +12121,7 @@
         <v>0</v>
       </c>
       <c r="E174" s="20" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F174" s="21">
         <v>9</v>
@@ -11906,7 +12154,7 @@
         <v>324</v>
       </c>
       <c r="B175" s="22" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C175" s="22" t="s">
         <v>325</v>
@@ -11915,7 +12163,7 @@
         <v>2</v>
       </c>
       <c r="E175" s="24" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F175" s="25">
         <v>19.5</v>
@@ -11948,7 +12196,7 @@
         <v>326</v>
       </c>
       <c r="B176" s="18" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C176" s="18" t="s">
         <v>327</v>
@@ -11957,7 +12205,7 @@
         <v>2</v>
       </c>
       <c r="E176" s="20" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F176" s="21">
         <v>24</v>
@@ -11990,7 +12238,7 @@
         <v>328</v>
       </c>
       <c r="B177" s="22" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C177" s="22" t="s">
         <v>329</v>
@@ -11999,7 +12247,7 @@
         <v>1</v>
       </c>
       <c r="E177" s="24" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F177" s="25">
         <v>9</v>
@@ -12032,7 +12280,7 @@
         <v>330</v>
       </c>
       <c r="B178" s="18" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C178" s="18" t="s">
         <v>331</v>
@@ -12041,7 +12289,7 @@
         <v>2</v>
       </c>
       <c r="E178" s="20" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="F178" s="21">
         <v>24</v>
@@ -12074,7 +12322,7 @@
         <v>332</v>
       </c>
       <c r="B179" s="22" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C179" s="22" t="s">
         <v>333</v>
@@ -12083,7 +12331,7 @@
         <v>0</v>
       </c>
       <c r="E179" s="24" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="F179" s="25">
         <v>28.8</v>
@@ -12116,7 +12364,7 @@
         <v>334</v>
       </c>
       <c r="B180" s="18" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C180" s="18" t="s">
         <v>335</v>
@@ -12125,7 +12373,7 @@
         <v>0</v>
       </c>
       <c r="E180" s="20" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F180" s="21">
         <v>30.6</v>
@@ -12158,7 +12406,7 @@
         <v>336</v>
       </c>
       <c r="B181" s="22" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C181" s="22" t="s">
         <v>337</v>
@@ -12167,7 +12415,7 @@
         <v>2</v>
       </c>
       <c r="E181" s="24" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="F181" s="25">
         <v>32</v>
@@ -12200,7 +12448,7 @@
         <v>338</v>
       </c>
       <c r="B182" s="18" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C182" s="18" t="s">
         <v>339</v>
@@ -12209,7 +12457,7 @@
         <v>1</v>
       </c>
       <c r="E182" s="20" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F182" s="21">
         <v>24</v>
@@ -12242,7 +12490,7 @@
         <v>340</v>
       </c>
       <c r="B183" s="22" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C183" s="22" t="s">
         <v>341</v>
@@ -12251,7 +12499,7 @@
         <v>0</v>
       </c>
       <c r="E183" s="24" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F183" s="25">
         <v>27.6</v>
@@ -12284,7 +12532,7 @@
         <v>342</v>
       </c>
       <c r="B184" s="18" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C184" s="18" t="s">
         <v>343</v>
@@ -12293,7 +12541,7 @@
         <v>0</v>
       </c>
       <c r="E184" s="20" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F184" s="21">
         <v>21.8</v>
@@ -12326,7 +12574,7 @@
         <v>344</v>
       </c>
       <c r="B185" s="22" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C185" s="22" t="s">
         <v>345</v>
@@ -12335,7 +12583,7 @@
         <v>0</v>
       </c>
       <c r="E185" s="24" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F185" s="25">
         <v>18</v>
@@ -12364,26 +12612,26 @@
       <c r="Z185" s="15"/>
     </row>
     <row r="186" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="16" t="s">
-        <v>346</v>
-      </c>
-      <c r="B186" s="18" t="s">
-        <v>595</v>
+      <c r="A186" s="17" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B186" s="22" t="s">
+        <v>1056</v>
       </c>
       <c r="C186" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="D186" s="19">
+        <v>1057</v>
+      </c>
+      <c r="D186" s="23">
         <v>0</v>
       </c>
       <c r="E186" s="20" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F186" s="21">
-        <v>24</v>
-      </c>
-      <c r="G186" s="21">
-        <v>0.16</v>
+        <v>1058</v>
+      </c>
+      <c r="F186" s="25">
+        <v>0</v>
+      </c>
+      <c r="G186" s="25">
+        <v>0</v>
       </c>
       <c r="H186" s="15"/>
       <c r="I186" s="15"/>
@@ -12405,21 +12653,21 @@
       <c r="Y186" s="15"/>
       <c r="Z186" s="15"/>
     </row>
-    <row r="187" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="17" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B187" s="22" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="D187" s="23">
         <v>0</v>
       </c>
       <c r="E187" s="20" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="F187" s="25">
         <v>0</v>
@@ -12447,27 +12695,27 @@
       <c r="Y187" s="15"/>
       <c r="Z187" s="15"/>
     </row>
-    <row r="188" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="17" t="s">
-        <v>1060</v>
+        <v>347</v>
       </c>
       <c r="B188" s="22" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C188" s="18" t="s">
-        <v>1062</v>
+        <v>595</v>
+      </c>
+      <c r="C188" s="22" t="s">
+        <v>348</v>
       </c>
       <c r="D188" s="23">
         <v>0</v>
       </c>
-      <c r="E188" s="20" t="s">
-        <v>1063</v>
+      <c r="E188" s="24" t="s">
+        <v>1017</v>
       </c>
       <c r="F188" s="25">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="G188" s="25">
-        <v>0</v>
+        <v>0.19600000000000001</v>
       </c>
       <c r="H188" s="15"/>
       <c r="I188" s="15"/>
@@ -12489,27 +12737,27 @@
       <c r="Y188" s="15"/>
       <c r="Z188" s="15"/>
     </row>
-    <row r="189" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="17" t="s">
-        <v>348</v>
-      </c>
-      <c r="B189" s="22" t="s">
+    <row r="189" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="B189" s="18" t="s">
         <v>596</v>
       </c>
-      <c r="C189" s="22" t="s">
-        <v>349</v>
-      </c>
-      <c r="D189" s="23">
-        <v>0</v>
-      </c>
-      <c r="E189" s="24" t="s">
+      <c r="C189" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="D189" s="19">
+        <v>2</v>
+      </c>
+      <c r="E189" s="20" t="s">
         <v>1018</v>
       </c>
-      <c r="F189" s="25">
-        <v>32.4</v>
-      </c>
-      <c r="G189" s="25">
-        <v>0.19600000000000001</v>
+      <c r="F189" s="21">
+        <v>12</v>
+      </c>
+      <c r="G189" s="21">
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="H189" s="15"/>
       <c r="I189" s="15"/>
@@ -12531,27 +12779,27 @@
       <c r="Y189" s="15"/>
       <c r="Z189" s="15"/>
     </row>
-    <row r="190" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="16" t="s">
-        <v>350</v>
-      </c>
-      <c r="B190" s="18" t="s">
+    <row r="190" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="B190" s="22" t="s">
         <v>597</v>
       </c>
-      <c r="C190" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="D190" s="19">
+      <c r="C190" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D190" s="23">
         <v>2</v>
       </c>
-      <c r="E190" s="20" t="s">
+      <c r="E190" s="24" t="s">
         <v>1019</v>
       </c>
-      <c r="F190" s="21">
-        <v>12</v>
-      </c>
-      <c r="G190" s="21">
-        <v>3.5999999999999997E-2</v>
+      <c r="F190" s="25">
+        <v>33</v>
+      </c>
+      <c r="G190" s="25">
+        <v>0.3</v>
       </c>
       <c r="H190" s="15"/>
       <c r="I190" s="15"/>
@@ -12574,26 +12822,26 @@
       <c r="Z190" s="15"/>
     </row>
     <row r="191" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="17" t="s">
-        <v>352</v>
-      </c>
-      <c r="B191" s="22" t="s">
+      <c r="A191" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="B191" s="18" t="s">
         <v>598</v>
       </c>
-      <c r="C191" s="22" t="s">
-        <v>353</v>
-      </c>
-      <c r="D191" s="23">
-        <v>2</v>
-      </c>
-      <c r="E191" s="24" t="s">
+      <c r="C191" s="18" t="s">
+        <v>354</v>
+      </c>
+      <c r="D191" s="19">
+        <v>1</v>
+      </c>
+      <c r="E191" s="20" t="s">
         <v>1020</v>
       </c>
-      <c r="F191" s="25">
-        <v>33</v>
-      </c>
-      <c r="G191" s="25">
-        <v>0.3</v>
+      <c r="F191" s="21">
+        <v>21.8</v>
+      </c>
+      <c r="G191" s="21">
+        <v>0.20799999999999999</v>
       </c>
       <c r="H191" s="15"/>
       <c r="I191" s="15"/>
@@ -12616,26 +12864,26 @@
       <c r="Z191" s="15"/>
     </row>
     <row r="192" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="16" t="s">
-        <v>354</v>
-      </c>
-      <c r="B192" s="18" t="s">
+      <c r="A192" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="B192" s="22" t="s">
         <v>599</v>
       </c>
-      <c r="C192" s="18" t="s">
-        <v>355</v>
-      </c>
-      <c r="D192" s="19">
-        <v>1</v>
-      </c>
-      <c r="E192" s="20" t="s">
+      <c r="C192" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="D192" s="23">
+        <v>61</v>
+      </c>
+      <c r="E192" s="24" t="s">
         <v>1021</v>
       </c>
-      <c r="F192" s="21">
-        <v>21.8</v>
-      </c>
-      <c r="G192" s="21">
-        <v>0.20799999999999999</v>
+      <c r="F192" s="25">
+        <v>24</v>
+      </c>
+      <c r="G192" s="25">
+        <v>0.14499999999999999</v>
       </c>
       <c r="H192" s="15"/>
       <c r="I192" s="15"/>
@@ -12657,27 +12905,27 @@
       <c r="Y192" s="15"/>
       <c r="Z192" s="15"/>
     </row>
-    <row r="193" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="B193" s="22" t="s">
+    <row r="193" spans="1:26" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="B193" s="18" t="s">
         <v>600</v>
       </c>
-      <c r="C193" s="22" t="s">
-        <v>357</v>
-      </c>
-      <c r="D193" s="23">
-        <v>61</v>
-      </c>
-      <c r="E193" s="24" t="s">
+      <c r="C193" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="D193" s="19">
+        <v>2</v>
+      </c>
+      <c r="E193" s="20" t="s">
         <v>1022</v>
       </c>
-      <c r="F193" s="25">
-        <v>24</v>
-      </c>
-      <c r="G193" s="25">
-        <v>0.14499999999999999</v>
+      <c r="F193" s="21">
+        <v>32</v>
+      </c>
+      <c r="G193" s="21">
+        <v>0.25600000000000001</v>
       </c>
       <c r="H193" s="15"/>
       <c r="I193" s="15"/>
@@ -12699,27 +12947,27 @@
       <c r="Y193" s="15"/>
       <c r="Z193" s="15"/>
     </row>
-    <row r="194" spans="1:26" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="16" t="s">
-        <v>358</v>
-      </c>
-      <c r="B194" s="18" t="s">
+    <row r="194" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="B194" s="22" t="s">
         <v>601</v>
       </c>
-      <c r="C194" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="D194" s="19">
-        <v>2</v>
-      </c>
-      <c r="E194" s="20" t="s">
+      <c r="C194" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="D194" s="23">
+        <v>54</v>
+      </c>
+      <c r="E194" s="24" t="s">
         <v>1023</v>
       </c>
-      <c r="F194" s="21">
-        <v>32</v>
-      </c>
-      <c r="G194" s="21">
-        <v>0.25600000000000001</v>
+      <c r="F194" s="25">
+        <v>16</v>
+      </c>
+      <c r="G194" s="25">
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="H194" s="15"/>
       <c r="I194" s="15"/>
@@ -12741,27 +12989,27 @@
       <c r="Y194" s="15"/>
       <c r="Z194" s="15"/>
     </row>
-    <row r="195" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="17" t="s">
-        <v>360</v>
-      </c>
-      <c r="B195" s="22" t="s">
+    <row r="195" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="B195" s="18" t="s">
         <v>602</v>
       </c>
-      <c r="C195" s="22" t="s">
-        <v>361</v>
-      </c>
-      <c r="D195" s="23">
-        <v>54</v>
-      </c>
-      <c r="E195" s="24" t="s">
+      <c r="C195" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="D195" s="19">
+        <v>50</v>
+      </c>
+      <c r="E195" s="20" t="s">
         <v>1024</v>
       </c>
-      <c r="F195" s="25">
-        <v>16</v>
-      </c>
-      <c r="G195" s="25">
-        <v>8.4000000000000005E-2</v>
+      <c r="F195" s="21">
+        <v>11.7</v>
+      </c>
+      <c r="G195" s="21">
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="H195" s="15"/>
       <c r="I195" s="15"/>
@@ -12783,27 +13031,27 @@
       <c r="Y195" s="15"/>
       <c r="Z195" s="15"/>
     </row>
-    <row r="196" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="16" t="s">
-        <v>362</v>
-      </c>
-      <c r="B196" s="18" t="s">
+    <row r="196" spans="1:26" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="B196" s="22" t="s">
         <v>603</v>
       </c>
-      <c r="C196" s="18" t="s">
-        <v>363</v>
-      </c>
-      <c r="D196" s="19">
-        <v>49</v>
-      </c>
-      <c r="E196" s="20" t="s">
+      <c r="C196" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="D196" s="23">
+        <v>0</v>
+      </c>
+      <c r="E196" s="24" t="s">
         <v>1025</v>
       </c>
-      <c r="F196" s="21">
-        <v>11.7</v>
-      </c>
-      <c r="G196" s="21">
-        <v>7.1999999999999995E-2</v>
+      <c r="F196" s="25">
+        <v>25.7</v>
+      </c>
+      <c r="G196" s="25">
+        <v>0.30599999999999999</v>
       </c>
       <c r="H196" s="15"/>
       <c r="I196" s="15"/>
@@ -12825,27 +13073,27 @@
       <c r="Y196" s="15"/>
       <c r="Z196" s="15"/>
     </row>
-    <row r="197" spans="1:26" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="B197" s="22" t="s">
+    <row r="197" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="B197" s="18" t="s">
         <v>604</v>
       </c>
-      <c r="C197" s="22" t="s">
-        <v>365</v>
-      </c>
-      <c r="D197" s="23">
-        <v>0</v>
-      </c>
-      <c r="E197" s="24" t="s">
+      <c r="C197" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="D197" s="19">
+        <v>1</v>
+      </c>
+      <c r="E197" s="20" t="s">
         <v>1026</v>
       </c>
-      <c r="F197" s="25">
-        <v>25.7</v>
-      </c>
-      <c r="G197" s="25">
-        <v>0.30599999999999999</v>
+      <c r="F197" s="21">
+        <v>31.7</v>
+      </c>
+      <c r="G197" s="21">
+        <v>0.31900000000000001</v>
       </c>
       <c r="H197" s="15"/>
       <c r="I197" s="15"/>
@@ -12867,27 +13115,27 @@
       <c r="Y197" s="15"/>
       <c r="Z197" s="15"/>
     </row>
-    <row r="198" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="B198" s="18" t="s">
+    <row r="198" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="B198" s="22" t="s">
         <v>605</v>
       </c>
-      <c r="C198" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="D198" s="19">
-        <v>1</v>
-      </c>
-      <c r="E198" s="20" t="s">
+      <c r="C198" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="D198" s="23">
+        <v>115</v>
+      </c>
+      <c r="E198" s="24" t="s">
         <v>1027</v>
       </c>
-      <c r="F198" s="21">
-        <v>31.7</v>
-      </c>
-      <c r="G198" s="21">
-        <v>0.31900000000000001</v>
+      <c r="F198" s="25">
+        <v>11.6</v>
+      </c>
+      <c r="G198" s="25">
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="H198" s="15"/>
       <c r="I198" s="15"/>
@@ -12911,25 +13159,27 @@
     </row>
     <row r="199" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="17" t="s">
-        <v>368</v>
+        <v>1063</v>
       </c>
       <c r="B199" s="22" t="s">
-        <v>606</v>
+        <v>1064</v>
       </c>
       <c r="C199" s="22" t="s">
-        <v>369</v>
+        <v>1065</v>
       </c>
       <c r="D199" s="23">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="E199" s="24" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F199" s="25">
-        <v>11.6</v>
-      </c>
-      <c r="G199" s="25">
-        <v>9.7000000000000003E-2</v>
+        <v>1066</v>
+      </c>
+      <c r="F199" s="30" cm="1">
+        <f t="array" ref="F199">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C199,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
+        <v>18.8</v>
+      </c>
+      <c r="G199" s="30" cm="1">
+        <f t="array" ref="G199">ROUND(F199/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C199,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
+        <v>0.157</v>
       </c>
       <c r="H199" s="15"/>
       <c r="I199" s="15"/>
@@ -12953,25 +13203,27 @@
     </row>
     <row r="200" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="17" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="B200" s="22" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D200" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E200" s="24" t="s">
-        <v>1067</v>
-      </c>
-      <c r="F200" s="25">
-        <v>11.6</v>
-      </c>
-      <c r="G200" s="25">
-        <v>9.7000000000000003E-2</v>
+        <v>1070</v>
+      </c>
+      <c r="F200" s="30" cm="1">
+        <f t="array" ref="F200">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C200,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
+        <v>17.2</v>
+      </c>
+      <c r="G200" s="30" cm="1">
+        <f t="array" ref="G200">ROUND(F200/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C200,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
+        <v>0.14299999999999999</v>
       </c>
       <c r="H200" s="15"/>
       <c r="I200" s="15"/>
@@ -12995,25 +13247,27 @@
     </row>
     <row r="201" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="17" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B201" s="22" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="C201" s="22" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="D201" s="23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E201" s="24" t="s">
-        <v>1071</v>
-      </c>
-      <c r="F201" s="25">
-        <v>11.6</v>
-      </c>
-      <c r="G201" s="25">
-        <v>9.7000000000000003E-2</v>
+        <v>1074</v>
+      </c>
+      <c r="F201" s="30" cm="1">
+        <f t="array" ref="F201">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C201,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
+        <v>13.8</v>
+      </c>
+      <c r="G201" s="30" cm="1">
+        <f t="array" ref="G201">ROUND(F201/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C201,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
+        <v>0.115</v>
       </c>
       <c r="H201" s="15"/>
       <c r="I201" s="15"/>
@@ -13037,25 +13291,27 @@
     </row>
     <row r="202" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="17" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="B202" s="22" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="C202" s="22" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="D202" s="23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E202" s="24" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F202" s="25">
-        <v>11.6</v>
-      </c>
-      <c r="G202" s="25">
-        <v>9.7000000000000003E-2</v>
+        <v>1078</v>
+      </c>
+      <c r="F202" s="30" cm="1">
+        <f t="array" ref="F202">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C202,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
+        <v>15.2</v>
+      </c>
+      <c r="G202" s="30" cm="1">
+        <f t="array" ref="G202">ROUND(F202/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C202,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
+        <v>0.127</v>
       </c>
       <c r="H202" s="15"/>
       <c r="I202" s="15"/>
@@ -13079,25 +13335,27 @@
     </row>
     <row r="203" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="17" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="B203" s="22" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="C203" s="22" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="D203" s="23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E203" s="24" t="s">
-        <v>1079</v>
-      </c>
-      <c r="F203" s="25">
-        <v>11.6</v>
-      </c>
-      <c r="G203" s="25">
-        <v>9.7000000000000003E-2</v>
+        <v>1082</v>
+      </c>
+      <c r="F203" s="30" cm="1">
+        <f t="array" ref="F203">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C203,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
+        <v>15.2</v>
+      </c>
+      <c r="G203" s="30" cm="1">
+        <f t="array" ref="G203">ROUND(F203/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C203,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
+        <v>0.127</v>
       </c>
       <c r="H203" s="15"/>
       <c r="I203" s="15"/>
@@ -13121,25 +13379,27 @@
     </row>
     <row r="204" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="17" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="B204" s="22" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="C204" s="22" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="D204" s="23">
         <v>0</v>
       </c>
       <c r="E204" s="24" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F204" s="25">
-        <v>11.6</v>
-      </c>
-      <c r="G204" s="25">
-        <v>9.7000000000000003E-2</v>
+        <v>1091</v>
+      </c>
+      <c r="F204" s="30" cm="1">
+        <f t="array" ref="F204">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C204,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
+        <v>19.2</v>
+      </c>
+      <c r="G204" s="30" cm="1">
+        <f t="array" ref="G204">ROUND(F204/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C204,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
+        <v>0.16</v>
       </c>
       <c r="H204" s="15"/>
       <c r="I204" s="15"/>
@@ -13161,27 +13421,29 @@
       <c r="Y204" s="15"/>
       <c r="Z204" s="15"/>
     </row>
-    <row r="205" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="17" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="B205" s="22" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="C205" s="22" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="D205" s="23">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E205" s="24" t="s">
-        <v>1087</v>
-      </c>
-      <c r="F205" s="25">
-        <v>11.6</v>
-      </c>
-      <c r="G205" s="25">
-        <v>9.7000000000000003E-2</v>
+        <v>1095</v>
+      </c>
+      <c r="F205" s="30" cm="1">
+        <f t="array" ref="F205">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C205,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
+        <v>12.8</v>
+      </c>
+      <c r="G205" s="30" cm="1">
+        <f t="array" ref="G205">ROUND(F205/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C205,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
+        <v>0.10199999999999999</v>
       </c>
       <c r="H205" s="15"/>
       <c r="I205" s="15"/>
@@ -13205,25 +13467,27 @@
     </row>
     <row r="206" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="17" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="B206" s="22" t="s">
-        <v>522</v>
+        <v>1084</v>
       </c>
       <c r="C206" s="22" t="s">
-        <v>202</v>
+        <v>1085</v>
       </c>
       <c r="D206" s="23">
         <v>6</v>
       </c>
       <c r="E206" s="24" t="s">
-        <v>921</v>
-      </c>
-      <c r="F206" s="25">
-        <v>15.2</v>
-      </c>
-      <c r="G206" s="25">
-        <v>0.127</v>
+        <v>1086</v>
+      </c>
+      <c r="F206" s="30" cm="1">
+        <f t="array" ref="F206">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C206,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
+        <v>14.2</v>
+      </c>
+      <c r="G206" s="30" cm="1">
+        <f t="array" ref="G206">ROUND(F206/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C206,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
+        <v>0.11799999999999999</v>
       </c>
       <c r="H206" s="15"/>
       <c r="I206" s="15"/>
@@ -13245,27 +13509,27 @@
       <c r="Y206" s="15"/>
       <c r="Z206" s="15"/>
     </row>
-    <row r="207" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="17" t="s">
-        <v>370</v>
+        <v>1087</v>
       </c>
       <c r="B207" s="22" t="s">
-        <v>607</v>
+        <v>521</v>
       </c>
       <c r="C207" s="22" t="s">
-        <v>371</v>
+        <v>202</v>
       </c>
       <c r="D207" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E207" s="24" t="s">
-        <v>1029</v>
+        <v>920</v>
       </c>
       <c r="F207" s="25">
-        <v>21.3</v>
+        <v>15.2</v>
       </c>
       <c r="G207" s="25">
-        <v>0.158</v>
+        <v>0.127</v>
       </c>
       <c r="H207" s="15"/>
       <c r="I207" s="15"/>
@@ -13287,27 +13551,27 @@
       <c r="Y207" s="15"/>
       <c r="Z207" s="15"/>
     </row>
-    <row r="208" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="16" t="s">
-        <v>372</v>
-      </c>
-      <c r="B208" s="18" t="s">
-        <v>608</v>
-      </c>
-      <c r="C208" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D208" s="19">
-        <v>0</v>
-      </c>
-      <c r="E208" s="20" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F208" s="21">
-        <v>22.8</v>
-      </c>
-      <c r="G208" s="21">
-        <v>0.36499999999999999</v>
+    <row r="208" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A208" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="B208" s="22" t="s">
+        <v>606</v>
+      </c>
+      <c r="C208" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="D208" s="23">
+        <v>5</v>
+      </c>
+      <c r="E208" s="24" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F208" s="25">
+        <v>21.3</v>
+      </c>
+      <c r="G208" s="25">
+        <v>0.158</v>
       </c>
       <c r="H208" s="15"/>
       <c r="I208" s="15"/>
@@ -13329,27 +13593,27 @@
       <c r="Y208" s="15"/>
       <c r="Z208" s="15"/>
     </row>
-    <row r="209" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="17" t="s">
-        <v>374</v>
-      </c>
-      <c r="B209" s="22" t="s">
-        <v>609</v>
-      </c>
-      <c r="C209" s="22" t="s">
-        <v>375</v>
-      </c>
-      <c r="D209" s="23">
-        <v>2</v>
-      </c>
-      <c r="E209" s="24" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F209" s="25">
-        <v>13.5</v>
-      </c>
-      <c r="G209" s="25">
-        <v>0.113</v>
+    <row r="209" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="B209" s="18" t="s">
+        <v>607</v>
+      </c>
+      <c r="C209" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="D209" s="19">
+        <v>0</v>
+      </c>
+      <c r="E209" s="20" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F209" s="21">
+        <v>22.8</v>
+      </c>
+      <c r="G209" s="21">
+        <v>0.36499999999999999</v>
       </c>
       <c r="H209" s="15"/>
       <c r="I209" s="15"/>
@@ -13371,27 +13635,27 @@
       <c r="Y209" s="15"/>
       <c r="Z209" s="15"/>
     </row>
-    <row r="210" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="16" t="s">
-        <v>376</v>
-      </c>
-      <c r="B210" s="18" t="s">
-        <v>610</v>
-      </c>
-      <c r="C210" s="18" t="s">
-        <v>377</v>
-      </c>
-      <c r="D210" s="19">
-        <v>4</v>
-      </c>
-      <c r="E210" s="20" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F210" s="21">
-        <v>22.8</v>
-      </c>
-      <c r="G210" s="21">
-        <v>0.28499999999999998</v>
+    <row r="210" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="B210" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="C210" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="D210" s="23">
+        <v>2</v>
+      </c>
+      <c r="E210" s="24" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F210" s="25">
+        <v>13.5</v>
+      </c>
+      <c r="G210" s="25">
+        <v>0.113</v>
       </c>
       <c r="H210" s="15"/>
       <c r="I210" s="15"/>
@@ -13414,26 +13678,26 @@
       <c r="Z210" s="15"/>
     </row>
     <row r="211" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="B211" s="22" t="s">
-        <v>611</v>
-      </c>
-      <c r="C211" s="22" t="s">
-        <v>379</v>
-      </c>
-      <c r="D211" s="23">
-        <v>1</v>
-      </c>
-      <c r="E211" s="24" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F211" s="25">
-        <v>36</v>
-      </c>
-      <c r="G211" s="25">
-        <v>0.4</v>
+      <c r="A211" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="B211" s="18" t="s">
+        <v>609</v>
+      </c>
+      <c r="C211" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="D211" s="19">
+        <v>4</v>
+      </c>
+      <c r="E211" s="20" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F211" s="21">
+        <v>22.8</v>
+      </c>
+      <c r="G211" s="21">
+        <v>0.28499999999999998</v>
       </c>
       <c r="H211" s="15"/>
       <c r="I211" s="15"/>
@@ -13456,26 +13720,28 @@
       <c r="Z211" s="15"/>
     </row>
     <row r="212" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="16" t="s">
-        <v>380</v>
-      </c>
-      <c r="B212" s="18" t="s">
-        <v>612</v>
-      </c>
-      <c r="C212" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="D212" s="19">
-        <v>1</v>
-      </c>
-      <c r="E212" s="20" t="s">
-        <v>1034</v>
-      </c>
-      <c r="F212" s="21">
-        <v>23</v>
-      </c>
-      <c r="G212" s="21">
-        <v>0.184</v>
+      <c r="A212" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B212" s="22" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C212" s="22" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D212" s="23">
+        <v>2</v>
+      </c>
+      <c r="E212" s="34" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F212" s="25" cm="1">
+        <f t="array" ref="F212">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C212,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.rest,_xlfn.TEXTAFTER(_xlpm.lines," – "),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlpm.rest," ")),_xlpm.unit,TRIM(_xlfn.TEXTAFTER(_xlpm.rest," ")),_xlpm.isml,--(_xlpm.unit="ml"),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$108,'Alcohol by Category'!$E$99:$E$108),0)),_xlpm.amt*_xlpm.abv*_xlpm.isml)),1)</f>
+        <v>24</v>
+      </c>
+      <c r="G212" s="25" cm="1">
+        <f t="array" ref="G212">ROUND(F212/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C212,,CHAR(10)),_xlpm.rest,_xlfn.TEXTAFTER(_xlpm.lines," – "),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlpm.rest," ")),_xlpm.unit,TRIM(_xlfn.TEXTAFTER(_xlpm.rest," ")),_xlpm.isml,--(_xlpm.unit="ml"),_xlpm.amt*_xlpm.isml)),3)</f>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H212" s="15"/>
       <c r="I212" s="15"/>
@@ -13497,27 +13763,27 @@
       <c r="Y212" s="15"/>
       <c r="Z212" s="15"/>
     </row>
-    <row r="213" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="17" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B213" s="22" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D213" s="23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E213" s="24" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="F213" s="25">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="G213" s="25">
-        <v>0.33700000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="H213" s="15"/>
       <c r="I213" s="15"/>
@@ -13541,25 +13807,25 @@
     </row>
     <row r="214" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="16" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B214" s="18" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C214" s="18" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D214" s="19">
-        <v>81</v>
+        <v>2</v>
       </c>
       <c r="E214" s="20" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="F214" s="21">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G214" s="21">
-        <v>0.09</v>
+        <v>0.184</v>
       </c>
       <c r="H214" s="15"/>
       <c r="I214" s="15"/>
@@ -13581,27 +13847,27 @@
       <c r="Y214" s="15"/>
       <c r="Z214" s="15"/>
     </row>
-    <row r="215" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="17" t="s">
-        <v>386</v>
-      </c>
-      <c r="B215" s="22" t="s">
-        <v>615</v>
-      </c>
-      <c r="C215" s="22" t="s">
-        <v>387</v>
-      </c>
-      <c r="D215" s="23">
+    <row r="215" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A215" s="16" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B215" s="18" t="s">
+        <v>594</v>
+      </c>
+      <c r="C215" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="D215" s="19">
         <v>1</v>
       </c>
-      <c r="E215" s="24" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F215" s="25">
-        <v>28.5</v>
-      </c>
-      <c r="G215" s="25">
-        <v>0.22800000000000001</v>
+      <c r="E215" s="20" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F215" s="21">
+        <v>24</v>
+      </c>
+      <c r="G215" s="21">
+        <v>0.16</v>
       </c>
       <c r="H215" s="15"/>
       <c r="I215" s="15"/>
@@ -13623,27 +13889,27 @@
       <c r="Y215" s="15"/>
       <c r="Z215" s="15"/>
     </row>
-    <row r="216" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="16" t="s">
-        <v>388</v>
-      </c>
-      <c r="B216" s="18" t="s">
-        <v>616</v>
-      </c>
-      <c r="C216" s="18" t="s">
-        <v>389</v>
-      </c>
-      <c r="D216" s="19">
-        <v>1</v>
-      </c>
-      <c r="E216" s="20" t="s">
-        <v>1038</v>
-      </c>
-      <c r="F216" s="21">
-        <v>24</v>
-      </c>
-      <c r="G216" s="21">
-        <v>0.35799999999999998</v>
+    <row r="216" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="B216" s="22" t="s">
+        <v>612</v>
+      </c>
+      <c r="C216" s="22" t="s">
+        <v>382</v>
+      </c>
+      <c r="D216" s="23">
+        <v>2</v>
+      </c>
+      <c r="E216" s="24" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F216" s="25">
+        <v>36.1</v>
+      </c>
+      <c r="G216" s="25">
+        <v>0.33700000000000002</v>
       </c>
       <c r="H216" s="15"/>
       <c r="I216" s="15"/>
@@ -13665,27 +13931,27 @@
       <c r="Y216" s="15"/>
       <c r="Z216" s="15"/>
     </row>
-    <row r="217" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="17" t="s">
-        <v>390</v>
-      </c>
-      <c r="B217" s="22" t="s">
-        <v>617</v>
-      </c>
-      <c r="C217" s="22" t="s">
-        <v>391</v>
-      </c>
-      <c r="D217" s="23">
-        <v>1</v>
-      </c>
-      <c r="E217" s="24" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F217" s="25">
+    <row r="217" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="B217" s="18" t="s">
+        <v>613</v>
+      </c>
+      <c r="C217" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="D217" s="19">
+        <v>81</v>
+      </c>
+      <c r="E217" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F217" s="21">
         <v>18</v>
       </c>
-      <c r="G217" s="25">
-        <v>9.1999999999999998E-2</v>
+      <c r="G217" s="21">
+        <v>0.09</v>
       </c>
       <c r="H217" s="15"/>
       <c r="I217" s="15"/>
@@ -13707,27 +13973,27 @@
       <c r="Y217" s="15"/>
       <c r="Z217" s="15"/>
     </row>
-    <row r="218" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="16" t="s">
-        <v>392</v>
-      </c>
-      <c r="B218" s="18" t="s">
-        <v>618</v>
-      </c>
-      <c r="C218" s="18" t="s">
-        <v>393</v>
-      </c>
-      <c r="D218" s="19">
-        <v>7</v>
-      </c>
-      <c r="E218" s="20" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F218" s="21">
-        <v>24</v>
-      </c>
-      <c r="G218" s="21">
-        <v>0.26700000000000002</v>
+    <row r="218" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="B218" s="22" t="s">
+        <v>614</v>
+      </c>
+      <c r="C218" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="D218" s="23">
+        <v>1</v>
+      </c>
+      <c r="E218" s="24" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F218" s="25">
+        <v>28.5</v>
+      </c>
+      <c r="G218" s="25">
+        <v>0.22800000000000001</v>
       </c>
       <c r="H218" s="15"/>
       <c r="I218" s="15"/>
@@ -13750,26 +14016,26 @@
       <c r="Z218" s="15"/>
     </row>
     <row r="219" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="17" t="s">
-        <v>394</v>
-      </c>
-      <c r="B219" s="22" t="s">
-        <v>619</v>
-      </c>
-      <c r="C219" s="22" t="s">
-        <v>395</v>
-      </c>
-      <c r="D219" s="23">
+      <c r="A219" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="B219" s="18" t="s">
+        <v>615</v>
+      </c>
+      <c r="C219" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="D219" s="19">
         <v>1</v>
       </c>
-      <c r="E219" s="24" t="s">
-        <v>1041</v>
-      </c>
-      <c r="F219" s="25">
-        <v>21.8</v>
-      </c>
-      <c r="G219" s="25">
-        <v>0.24199999999999999</v>
+      <c r="E219" s="20" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F219" s="21">
+        <v>24</v>
+      </c>
+      <c r="G219" s="21">
+        <v>0.35799999999999998</v>
       </c>
       <c r="H219" s="15"/>
       <c r="I219" s="15"/>
@@ -13792,26 +14058,26 @@
       <c r="Z219" s="15"/>
     </row>
     <row r="220" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="16" t="s">
-        <v>396</v>
-      </c>
-      <c r="B220" s="18" t="s">
-        <v>620</v>
-      </c>
-      <c r="C220" s="18" t="s">
-        <v>397</v>
-      </c>
-      <c r="D220" s="19">
-        <v>2</v>
-      </c>
-      <c r="E220" s="20" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F220" s="21">
-        <v>38.6</v>
-      </c>
-      <c r="G220" s="21">
-        <v>0.36799999999999999</v>
+      <c r="A220" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="B220" s="22" t="s">
+        <v>616</v>
+      </c>
+      <c r="C220" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="D220" s="23">
+        <v>1</v>
+      </c>
+      <c r="E220" s="24" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F220" s="25">
+        <v>18</v>
+      </c>
+      <c r="G220" s="25">
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="H220" s="15"/>
       <c r="I220" s="15"/>
@@ -13833,27 +14099,27 @@
       <c r="Y220" s="15"/>
       <c r="Z220" s="15"/>
     </row>
-    <row r="221" spans="1:26" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="17" t="s">
-        <v>398</v>
-      </c>
-      <c r="B221" s="22" t="s">
-        <v>621</v>
-      </c>
-      <c r="C221" s="22" t="s">
-        <v>399</v>
-      </c>
-      <c r="D221" s="23">
-        <v>2</v>
-      </c>
-      <c r="E221" s="24" t="s">
-        <v>1043</v>
-      </c>
-      <c r="F221" s="25">
-        <v>30.8</v>
-      </c>
-      <c r="G221" s="25">
-        <v>0.32400000000000001</v>
+    <row r="221" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="B221" s="18" t="s">
+        <v>617</v>
+      </c>
+      <c r="C221" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="D221" s="19">
+        <v>7</v>
+      </c>
+      <c r="E221" s="20" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F221" s="21">
+        <v>24</v>
+      </c>
+      <c r="G221" s="21">
+        <v>0.26700000000000002</v>
       </c>
       <c r="H221" s="15"/>
       <c r="I221" s="15"/>
@@ -13876,26 +14142,26 @@
       <c r="Z221" s="15"/>
     </row>
     <row r="222" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="16" t="s">
-        <v>400</v>
-      </c>
-      <c r="B222" s="18" t="s">
-        <v>622</v>
-      </c>
-      <c r="C222" s="18" t="s">
-        <v>401</v>
-      </c>
-      <c r="D222" s="19">
-        <v>2</v>
-      </c>
-      <c r="E222" s="20" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F222" s="21">
-        <v>24</v>
-      </c>
-      <c r="G222" s="21">
-        <v>0.218</v>
+      <c r="A222" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="B222" s="22" t="s">
+        <v>618</v>
+      </c>
+      <c r="C222" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="D222" s="23">
+        <v>1</v>
+      </c>
+      <c r="E222" s="24" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F222" s="25">
+        <v>21.8</v>
+      </c>
+      <c r="G222" s="25">
+        <v>0.24199999999999999</v>
       </c>
       <c r="H222" s="15"/>
       <c r="I222" s="15"/>
@@ -13917,27 +14183,27 @@
       <c r="Y222" s="15"/>
       <c r="Z222" s="15"/>
     </row>
-    <row r="223" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="17" t="s">
-        <v>402</v>
-      </c>
-      <c r="B223" s="22" t="s">
-        <v>623</v>
-      </c>
-      <c r="C223" s="22" t="s">
-        <v>403</v>
-      </c>
-      <c r="D223" s="23">
-        <v>0</v>
-      </c>
-      <c r="E223" s="24" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F223" s="25">
-        <v>33.6</v>
-      </c>
-      <c r="G223" s="25">
-        <v>0.35399999999999998</v>
+    <row r="223" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A223" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="B223" s="18" t="s">
+        <v>619</v>
+      </c>
+      <c r="C223" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="D223" s="19">
+        <v>2</v>
+      </c>
+      <c r="E223" s="20" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F223" s="21">
+        <v>38.6</v>
+      </c>
+      <c r="G223" s="21">
+        <v>0.36799999999999999</v>
       </c>
       <c r="H223" s="15"/>
       <c r="I223" s="15"/>
@@ -13959,27 +14225,27 @@
       <c r="Y223" s="15"/>
       <c r="Z223" s="15"/>
     </row>
-    <row r="224" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="16" t="s">
-        <v>404</v>
-      </c>
-      <c r="B224" s="18" t="s">
-        <v>624</v>
-      </c>
-      <c r="C224" s="18" t="s">
-        <v>405</v>
-      </c>
-      <c r="D224" s="19">
-        <v>4</v>
-      </c>
-      <c r="E224" s="20" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F224" s="21">
-        <v>24</v>
-      </c>
-      <c r="G224" s="21">
-        <v>0.214</v>
+    <row r="224" spans="1:26" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="B224" s="22" t="s">
+        <v>620</v>
+      </c>
+      <c r="C224" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="D224" s="23">
+        <v>2</v>
+      </c>
+      <c r="E224" s="24" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F224" s="25">
+        <v>30.8</v>
+      </c>
+      <c r="G224" s="25">
+        <v>0.32400000000000001</v>
       </c>
       <c r="H224" s="15"/>
       <c r="I224" s="15"/>
@@ -14001,27 +14267,27 @@
       <c r="Y224" s="15"/>
       <c r="Z224" s="15"/>
     </row>
-    <row r="225" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="17" t="s">
-        <v>406</v>
-      </c>
-      <c r="B225" s="22" t="s">
-        <v>625</v>
-      </c>
-      <c r="C225" s="22" t="s">
-        <v>407</v>
-      </c>
-      <c r="D225" s="23">
-        <v>4</v>
-      </c>
-      <c r="E225" s="24" t="s">
-        <v>1047</v>
-      </c>
-      <c r="F225" s="25">
-        <v>18</v>
-      </c>
-      <c r="G225" s="25">
-        <v>0.09</v>
+    <row r="225" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="B225" s="18" t="s">
+        <v>621</v>
+      </c>
+      <c r="C225" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="D225" s="19">
+        <v>2</v>
+      </c>
+      <c r="E225" s="20" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F225" s="21">
+        <v>24</v>
+      </c>
+      <c r="G225" s="21">
+        <v>0.218</v>
       </c>
       <c r="H225" s="15"/>
       <c r="I225" s="15"/>
@@ -14043,27 +14309,27 @@
       <c r="Y225" s="15"/>
       <c r="Z225" s="15"/>
     </row>
-    <row r="226" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="16" t="s">
-        <v>408</v>
-      </c>
-      <c r="B226" s="18" t="s">
-        <v>626</v>
-      </c>
-      <c r="C226" s="18" t="s">
-        <v>409</v>
-      </c>
-      <c r="D226" s="19">
-        <v>23</v>
-      </c>
-      <c r="E226" s="20" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F226" s="21">
-        <v>24</v>
-      </c>
-      <c r="G226" s="21">
-        <v>0.253</v>
+    <row r="226" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="17" t="s">
+        <v>401</v>
+      </c>
+      <c r="B226" s="22" t="s">
+        <v>622</v>
+      </c>
+      <c r="C226" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="D226" s="23">
+        <v>0</v>
+      </c>
+      <c r="E226" s="24" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F226" s="25">
+        <v>33.6</v>
+      </c>
+      <c r="G226" s="25">
+        <v>0.35399999999999998</v>
       </c>
       <c r="H226" s="15"/>
       <c r="I226" s="15"/>
@@ -14086,26 +14352,26 @@
       <c r="Z226" s="15"/>
     </row>
     <row r="227" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="17" t="s">
-        <v>410</v>
-      </c>
-      <c r="B227" s="22" t="s">
-        <v>627</v>
-      </c>
-      <c r="C227" s="22" t="s">
-        <v>411</v>
-      </c>
-      <c r="D227" s="23">
-        <v>22</v>
-      </c>
-      <c r="E227" s="24" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F227" s="25">
+      <c r="A227" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="B227" s="18" t="s">
+        <v>623</v>
+      </c>
+      <c r="C227" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="D227" s="19">
+        <v>4</v>
+      </c>
+      <c r="E227" s="20" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F227" s="21">
         <v>24</v>
       </c>
-      <c r="G227" s="25">
-        <v>0.24</v>
+      <c r="G227" s="21">
+        <v>0.214</v>
       </c>
       <c r="H227" s="15"/>
       <c r="I227" s="15"/>
@@ -14127,27 +14393,27 @@
       <c r="Y227" s="15"/>
       <c r="Z227" s="15"/>
     </row>
-    <row r="228" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="B228" s="18" t="s">
-        <v>628</v>
-      </c>
-      <c r="C228" s="18" t="s">
-        <v>415</v>
-      </c>
-      <c r="D228" s="19">
-        <v>8</v>
-      </c>
-      <c r="E228" s="20" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F228" s="21">
-        <v>21.6</v>
-      </c>
-      <c r="G228" s="21">
-        <v>0.24</v>
+    <row r="228" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="B228" s="22" t="s">
+        <v>624</v>
+      </c>
+      <c r="C228" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="D228" s="23">
+        <v>4</v>
+      </c>
+      <c r="E228" s="24" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F228" s="25">
+        <v>18</v>
+      </c>
+      <c r="G228" s="25">
+        <v>0.09</v>
       </c>
       <c r="H228" s="15"/>
       <c r="I228" s="15"/>
@@ -14169,27 +14435,27 @@
       <c r="Y228" s="15"/>
       <c r="Z228" s="15"/>
     </row>
-    <row r="229" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="17" t="s">
-        <v>412</v>
-      </c>
-      <c r="B229" s="22" t="s">
-        <v>629</v>
-      </c>
-      <c r="C229" s="22" t="s">
-        <v>413</v>
-      </c>
-      <c r="D229" s="23">
-        <v>0</v>
-      </c>
-      <c r="E229" s="24" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F229" s="25">
-        <v>21.9</v>
-      </c>
-      <c r="G229" s="25">
-        <v>0.24299999999999999</v>
+    <row r="229" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="B229" s="18" t="s">
+        <v>625</v>
+      </c>
+      <c r="C229" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="D229" s="19">
+        <v>23</v>
+      </c>
+      <c r="E229" s="20" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F229" s="21">
+        <v>24</v>
+      </c>
+      <c r="G229" s="21">
+        <v>0.253</v>
       </c>
       <c r="H229" s="15"/>
       <c r="I229" s="15"/>
@@ -14211,27 +14477,27 @@
       <c r="Y229" s="15"/>
       <c r="Z229" s="15"/>
     </row>
-    <row r="230" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="16" t="s">
-        <v>416</v>
-      </c>
-      <c r="B230" s="18" t="s">
-        <v>630</v>
-      </c>
-      <c r="C230" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D230" s="19">
-        <v>14</v>
-      </c>
-      <c r="E230" s="20" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F230" s="21">
-        <v>18</v>
-      </c>
-      <c r="G230" s="21">
-        <v>0.2</v>
+    <row r="230" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="B230" s="22" t="s">
+        <v>626</v>
+      </c>
+      <c r="C230" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="D230" s="23">
+        <v>22</v>
+      </c>
+      <c r="E230" s="24" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F230" s="25">
+        <v>24</v>
+      </c>
+      <c r="G230" s="25">
+        <v>0.24</v>
       </c>
       <c r="H230" s="15"/>
       <c r="I230" s="15"/>
@@ -14253,27 +14519,27 @@
       <c r="Y230" s="15"/>
       <c r="Z230" s="15"/>
     </row>
-    <row r="231" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="17" t="s">
-        <v>417</v>
-      </c>
-      <c r="B231" s="22" t="s">
-        <v>631</v>
-      </c>
-      <c r="C231" s="22" t="s">
-        <v>418</v>
-      </c>
-      <c r="D231" s="23">
-        <v>2</v>
-      </c>
-      <c r="E231" s="24" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F231" s="25">
-        <v>22.8</v>
-      </c>
-      <c r="G231" s="25">
-        <v>0.26800000000000002</v>
+    <row r="231" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="B231" s="18" t="s">
+        <v>627</v>
+      </c>
+      <c r="C231" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="D231" s="19">
+        <v>6</v>
+      </c>
+      <c r="E231" s="20" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F231" s="21">
+        <v>21.6</v>
+      </c>
+      <c r="G231" s="21">
+        <v>0.24</v>
       </c>
       <c r="H231" s="15"/>
       <c r="I231" s="15"/>
@@ -14295,27 +14561,27 @@
       <c r="Y231" s="15"/>
       <c r="Z231" s="15"/>
     </row>
-    <row r="232" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="16" t="s">
-        <v>419</v>
-      </c>
-      <c r="B232" s="18" t="s">
-        <v>632</v>
-      </c>
-      <c r="C232" s="18" t="s">
-        <v>420</v>
-      </c>
-      <c r="D232" s="19">
+    <row r="232" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="B232" s="22" t="s">
+        <v>628</v>
+      </c>
+      <c r="C232" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="D232" s="23">
         <v>2</v>
       </c>
-      <c r="E232" s="20" t="s">
-        <v>1054</v>
-      </c>
-      <c r="F232" s="21">
-        <v>28.9</v>
-      </c>
-      <c r="G232" s="21">
-        <v>0.32100000000000001</v>
+      <c r="E232" s="24" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F232" s="25">
+        <v>21.9</v>
+      </c>
+      <c r="G232" s="25">
+        <v>0.24299999999999999</v>
       </c>
       <c r="H232" s="15"/>
       <c r="I232" s="15"/>
@@ -14337,14 +14603,28 @@
       <c r="Y232" s="15"/>
       <c r="Z232" s="15"/>
     </row>
-    <row r="233" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="15"/>
-      <c r="B233" s="15"/>
-      <c r="C233" s="15"/>
-      <c r="D233" s="15"/>
-      <c r="E233" s="15"/>
-      <c r="F233" s="15"/>
-      <c r="G233" s="15"/>
+    <row r="233" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="B233" s="18" t="s">
+        <v>629</v>
+      </c>
+      <c r="C233" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D233" s="19">
+        <v>14</v>
+      </c>
+      <c r="E233" s="20" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F233" s="21">
+        <v>18</v>
+      </c>
+      <c r="G233" s="21">
+        <v>0.2</v>
+      </c>
       <c r="H233" s="15"/>
       <c r="I233" s="15"/>
       <c r="J233" s="15"/>
@@ -14365,14 +14645,28 @@
       <c r="Y233" s="15"/>
       <c r="Z233" s="15"/>
     </row>
-    <row r="234" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="15"/>
-      <c r="B234" s="15"/>
-      <c r="C234" s="15"/>
-      <c r="D234" s="15"/>
-      <c r="E234" s="15"/>
-      <c r="F234" s="15"/>
-      <c r="G234" s="15"/>
+    <row r="234" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="B234" s="22" t="s">
+        <v>630</v>
+      </c>
+      <c r="C234" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="D234" s="23">
+        <v>2</v>
+      </c>
+      <c r="E234" s="24" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F234" s="25">
+        <v>22.8</v>
+      </c>
+      <c r="G234" s="25">
+        <v>0.26800000000000002</v>
+      </c>
       <c r="H234" s="15"/>
       <c r="I234" s="15"/>
       <c r="J234" s="15"/>
@@ -14393,14 +14687,28 @@
       <c r="Y234" s="15"/>
       <c r="Z234" s="15"/>
     </row>
-    <row r="235" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="15"/>
-      <c r="B235" s="15"/>
-      <c r="C235" s="15"/>
-      <c r="D235" s="15"/>
-      <c r="E235" s="15"/>
-      <c r="F235" s="15"/>
-      <c r="G235" s="15"/>
+    <row r="235" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A235" s="31" t="s">
+        <v>418</v>
+      </c>
+      <c r="B235" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="C235" s="32" t="s">
+        <v>419</v>
+      </c>
+      <c r="D235" s="33">
+        <v>2</v>
+      </c>
+      <c r="E235" s="32" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F235" s="21">
+        <v>28.9</v>
+      </c>
+      <c r="G235" s="21">
+        <v>0.32100000000000001</v>
+      </c>
       <c r="H235" s="15"/>
       <c r="I235" s="15"/>
       <c r="J235" s="15"/>
@@ -35954,8 +36262,8 @@
       <c r="Z1004" s="15"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F219">
-    <sortCondition ref="A2:A219"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z235">
+    <sortCondition ref="A2:A235"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -35975,1567 +36283,1567 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>652</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B2" s="2">
         <v>48600</v>
       </c>
       <c r="C2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B3" s="2">
         <v>27380</v>
       </c>
       <c r="C3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B4" s="2">
         <v>22740</v>
       </c>
       <c r="C4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B5" s="2">
         <v>12510</v>
       </c>
       <c r="C5" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B6" s="2">
         <v>10950</v>
       </c>
       <c r="C6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B7" s="2">
         <v>10830</v>
       </c>
       <c r="C7" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B8" s="2">
         <v>9631</v>
       </c>
       <c r="C8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B9" s="2">
         <v>8380</v>
       </c>
       <c r="C9" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B10" s="2">
         <v>5568</v>
       </c>
       <c r="C10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B11" s="2">
         <v>5400</v>
       </c>
       <c r="C11" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B12" s="2">
         <v>4395</v>
       </c>
       <c r="C12" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B13" s="2">
         <v>4110</v>
       </c>
       <c r="C13" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B14" s="2">
         <v>4080</v>
       </c>
       <c r="C14" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B15" s="2">
         <v>3660</v>
       </c>
       <c r="C15" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B16" s="2">
         <v>3200</v>
       </c>
       <c r="C16" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B17" s="2">
         <v>3165</v>
       </c>
       <c r="C17" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B18" s="2">
         <v>2765</v>
       </c>
       <c r="C18" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B19" s="2">
         <v>2265</v>
       </c>
       <c r="C19" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B20" s="2">
         <v>2185</v>
       </c>
       <c r="C20" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B21" s="2">
         <v>2070</v>
       </c>
       <c r="C21" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B22" s="2">
         <v>1925</v>
       </c>
       <c r="C22" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B23" s="2">
         <v>1895</v>
       </c>
       <c r="C23" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B24" s="2">
         <v>1370</v>
       </c>
       <c r="C24" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B25" s="2">
         <v>1300</v>
       </c>
       <c r="C25" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B26" s="2">
         <v>1215</v>
       </c>
       <c r="C26" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B27" s="2">
         <v>1020</v>
       </c>
       <c r="C27" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B28" s="2">
         <v>1010</v>
       </c>
       <c r="C28" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B29" s="2">
         <v>945</v>
       </c>
       <c r="C29" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B30" s="2">
         <v>840</v>
       </c>
       <c r="C30" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B31" s="2">
         <v>780</v>
       </c>
       <c r="C31" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B32" s="2">
         <v>770</v>
       </c>
       <c r="C32" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B33" s="2">
         <v>730</v>
       </c>
       <c r="C33" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B34" s="2">
         <v>630</v>
       </c>
       <c r="C34" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B35" s="2">
         <v>630</v>
       </c>
       <c r="C35" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B36" s="2">
         <v>580</v>
       </c>
       <c r="C36" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B37" s="2">
         <v>540</v>
       </c>
       <c r="C37" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B38" s="2">
         <v>525</v>
       </c>
       <c r="C38" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B39" s="2">
         <v>525</v>
       </c>
       <c r="C39" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B40" s="2">
         <v>524</v>
       </c>
       <c r="C40" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B41" s="2">
         <v>495</v>
       </c>
       <c r="C41" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B42" s="2">
         <v>495</v>
       </c>
       <c r="C42" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B43" s="2">
         <v>490</v>
       </c>
       <c r="C43" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B44" s="2">
         <v>450</v>
       </c>
       <c r="C44" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B45" s="2">
         <v>450</v>
       </c>
       <c r="C45" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B46" s="2">
         <v>360</v>
       </c>
       <c r="C46" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B47" s="2">
         <v>345</v>
       </c>
       <c r="C47" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B48" s="2">
         <v>330</v>
       </c>
       <c r="C48" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B49" s="2">
         <v>300</v>
       </c>
       <c r="C49" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B50" s="2">
         <v>300</v>
       </c>
       <c r="C50" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B51" s="2">
         <v>285</v>
       </c>
       <c r="C51" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B52" s="2">
         <v>265</v>
       </c>
       <c r="C52" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B53" s="2">
         <v>260</v>
       </c>
       <c r="C53" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B54" s="2">
         <v>245</v>
       </c>
       <c r="C54" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B55" s="2">
         <v>240</v>
       </c>
       <c r="C55" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B56" s="2">
         <v>240</v>
       </c>
       <c r="C56" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B57" s="2">
         <v>240</v>
       </c>
       <c r="C57" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B58" s="2">
         <v>210</v>
       </c>
       <c r="C58" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B59" s="2">
         <v>210</v>
       </c>
       <c r="C59" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B60" s="2">
         <v>200</v>
       </c>
       <c r="C60" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B61" s="2">
         <v>194</v>
       </c>
       <c r="C61" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B62" s="2">
         <v>180</v>
       </c>
       <c r="C62" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B63" s="2">
         <v>180</v>
       </c>
       <c r="C63" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B64" s="2">
         <v>180</v>
       </c>
       <c r="C64" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B65" s="2">
         <v>180</v>
       </c>
       <c r="C65" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B66" s="2">
         <v>175</v>
       </c>
       <c r="C66" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B67" s="2">
         <v>170</v>
       </c>
       <c r="C67" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B68" s="2">
         <v>160</v>
       </c>
       <c r="C68" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B69" s="2">
         <v>155</v>
       </c>
       <c r="C69" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B70" s="2">
         <v>150</v>
       </c>
       <c r="C70" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B71" s="2">
         <v>150</v>
       </c>
       <c r="C71" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B72" s="2">
         <v>145</v>
       </c>
       <c r="C72" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B73" s="2">
         <v>135</v>
       </c>
       <c r="C73" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B74" s="2">
         <v>132</v>
       </c>
       <c r="C74" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B75" s="2">
         <v>131</v>
       </c>
       <c r="C75" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B76" s="2">
         <v>120</v>
       </c>
       <c r="C76" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B77" s="2">
         <v>120</v>
       </c>
       <c r="C77" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B78" s="2">
         <v>120</v>
       </c>
       <c r="C78" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B79" s="2">
         <v>120</v>
       </c>
       <c r="C79" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B80" s="2">
         <v>120</v>
       </c>
       <c r="C80" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B81" s="2">
         <v>120</v>
       </c>
       <c r="C81" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B82" s="2">
         <v>105</v>
       </c>
       <c r="C82" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B83" s="2">
         <v>100</v>
       </c>
       <c r="C83" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B84" s="2">
         <v>100</v>
       </c>
       <c r="C84" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B85" s="2">
         <v>95</v>
       </c>
       <c r="C85" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B86" s="2">
         <v>93</v>
       </c>
       <c r="C86" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B87" s="2">
         <v>90</v>
       </c>
       <c r="C87" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B88" s="2">
         <v>90</v>
       </c>
       <c r="C88" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B89" s="2">
         <v>81</v>
       </c>
       <c r="C89" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B90" s="2">
         <v>80</v>
       </c>
       <c r="C90" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B91" s="2">
         <v>64</v>
       </c>
       <c r="C91" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B92" s="2">
         <v>60</v>
       </c>
       <c r="C92" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B93" s="2">
         <v>60</v>
       </c>
       <c r="C93" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B94" s="2">
         <v>60</v>
       </c>
       <c r="C94" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B95" s="2">
         <v>60</v>
       </c>
       <c r="C95" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B96" s="2">
         <v>50</v>
       </c>
       <c r="C96" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B97" s="2">
         <v>50</v>
       </c>
       <c r="C97" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B98" s="2">
         <v>49</v>
       </c>
       <c r="C98" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B99" s="2">
         <v>45</v>
       </c>
       <c r="C99" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B100" s="2">
         <v>45</v>
       </c>
       <c r="C100" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B101" s="2">
         <v>40</v>
       </c>
       <c r="C101" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B102" s="2">
         <v>35</v>
       </c>
       <c r="C102" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B103" s="2">
         <v>32.5</v>
       </c>
       <c r="C103" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B104" s="2">
         <v>30</v>
       </c>
       <c r="C104" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B105" s="2">
         <v>30</v>
       </c>
       <c r="C105" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B106" s="2">
         <v>30</v>
       </c>
       <c r="C106" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B107" s="2">
         <v>30</v>
       </c>
       <c r="C107" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B108" s="2">
         <v>30</v>
       </c>
       <c r="C108" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B109" s="2">
         <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B110" s="2">
         <v>24</v>
       </c>
       <c r="C110" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B111" s="2">
         <v>21</v>
       </c>
       <c r="C111" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B112" s="2">
         <v>20</v>
       </c>
       <c r="C112" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B113" s="2">
         <v>20</v>
       </c>
       <c r="C113" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B114" s="2">
         <v>18</v>
       </c>
       <c r="C114" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B115" s="2">
         <v>17.5</v>
       </c>
       <c r="C115" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B116" s="2">
         <v>16</v>
       </c>
       <c r="C116" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B117" s="2">
         <v>15</v>
       </c>
       <c r="C117" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B118" s="2">
         <v>15</v>
       </c>
       <c r="C118" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B119" s="2">
         <v>15</v>
       </c>
       <c r="C119" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B120" s="2">
         <v>15</v>
       </c>
       <c r="C120" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B121" s="2">
         <v>14</v>
       </c>
       <c r="C121" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B122" s="2">
         <v>11</v>
       </c>
       <c r="C122" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B123" s="2">
         <v>8</v>
       </c>
       <c r="C123" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B124" s="2">
         <v>7</v>
       </c>
       <c r="C124" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B125" s="2">
         <v>7</v>
       </c>
       <c r="C125" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B126" s="2">
         <v>6</v>
       </c>
       <c r="C126" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B127" s="2">
         <v>5</v>
       </c>
       <c r="C127" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B128" s="2">
         <v>5</v>
       </c>
       <c r="C128" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B129" s="2">
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B130" s="2">
         <v>3</v>
       </c>
       <c r="C130" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B131" s="2">
         <v>3</v>
       </c>
       <c r="C131" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B132" s="2">
         <v>2.5</v>
       </c>
       <c r="C132" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B133" s="2">
         <v>2</v>
       </c>
       <c r="C133" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B134" s="2">
         <v>2</v>
       </c>
       <c r="C134" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B135" s="2">
         <v>2</v>
       </c>
       <c r="C135" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B136" s="2">
         <v>2</v>
       </c>
       <c r="C136" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B137" s="2">
         <v>2</v>
       </c>
       <c r="C137" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B138" s="2">
         <v>2</v>
       </c>
       <c r="C138" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B139" s="2">
         <v>1</v>
       </c>
       <c r="C139" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B140" s="2">
         <v>1</v>
       </c>
       <c r="C140" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B141" s="2">
         <v>1</v>
       </c>
       <c r="C141" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B142" s="2">
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
   </sheetData>
@@ -37551,8 +37859,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA69CBB7-549A-4D03-BEAC-D89B9E44A09C}">
-  <dimension ref="A1:D95"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA69CBB7-549A-4D03-BEAC-D89B9E44A09C}">
+  <dimension ref="A1:G108"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
@@ -37561,33 +37869,33 @@
     <col min="4" max="4" width="20.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="D4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>802</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>803</v>
       </c>
       <c r="B5" s="7">
         <v>57497.5</v>
@@ -37601,9 +37909,9 @@
         <v>82.13928571428572</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B6" s="7">
         <v>21048</v>
@@ -37617,9 +37925,9 @@
         <v>30.068571428571428</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B7" s="7">
         <v>17360</v>
@@ -37633,9 +37941,9 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B8" s="7">
         <v>0</v>
@@ -37649,9 +37957,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B9" s="8">
         <f>SUM(B5:B8)</f>
@@ -37666,885 +37974,1208 @@
         <v>137.00785714285715</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>802</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>651</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B13" s="2">
         <v>22740</v>
       </c>
       <c r="C13" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E13" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B14" s="2">
         <v>10950</v>
       </c>
       <c r="C14" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E14" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B15" s="2">
         <v>4395</v>
       </c>
       <c r="C15" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E15" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B16" s="2">
         <v>3660</v>
       </c>
       <c r="C16" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E16" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B17" s="2">
         <v>3200</v>
       </c>
       <c r="C17" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E17" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B18" s="2">
         <v>2765</v>
       </c>
       <c r="C18" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E18" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B19" s="2">
         <v>1895</v>
       </c>
       <c r="C19" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E19" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B20" s="2">
         <v>1215</v>
       </c>
       <c r="C20" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E20" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B21" s="2">
         <v>1010</v>
       </c>
       <c r="C21" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E21" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B22" s="2">
         <v>840</v>
       </c>
       <c r="C22" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E22" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B23" s="2">
         <v>780</v>
       </c>
       <c r="C23" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E23" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B24" s="2">
         <v>730</v>
       </c>
       <c r="C24" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E24" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B25" s="2">
         <v>495</v>
       </c>
       <c r="C25" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E25" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B26" s="2">
         <v>450</v>
       </c>
       <c r="C26" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E26" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B27" s="2">
         <v>345</v>
       </c>
       <c r="C27" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E27" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B28" s="2">
         <v>285</v>
       </c>
       <c r="C28" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E28" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B29" s="2">
         <v>265</v>
       </c>
       <c r="C29" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E29" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B30" s="2">
         <v>240</v>
       </c>
       <c r="C30" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E30" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B31" s="2">
         <v>210</v>
       </c>
       <c r="C31" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E31" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B32" s="2">
         <v>180</v>
       </c>
       <c r="C32" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E32" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B33" s="2">
         <v>180</v>
       </c>
       <c r="C33" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E33" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B34" s="2">
         <v>180</v>
       </c>
       <c r="C34" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E34" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B35" s="2">
         <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E35" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B36" s="2">
         <v>120</v>
       </c>
       <c r="C36" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E36" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B37" s="2">
         <v>60</v>
       </c>
       <c r="C37" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E37" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B38" s="2">
         <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E38" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B39" s="2">
         <v>60</v>
       </c>
       <c r="C39" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E39" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B40" s="2">
         <v>32.5</v>
       </c>
       <c r="C40" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E40" s="27">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B41" s="2">
         <v>20</v>
       </c>
       <c r="C41" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E41" s="27">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B42" s="2">
         <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E42" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B43" s="2">
         <v>16</v>
       </c>
       <c r="C43" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+      <c r="E43" s="27">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>651</v>
+      </c>
+      <c r="E46" s="26" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B47" s="2">
         <v>4110</v>
       </c>
       <c r="C47" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E47" s="27">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B48" s="2">
         <v>4080</v>
       </c>
       <c r="C48" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E48" s="27">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B49" s="2">
         <v>3165</v>
       </c>
       <c r="C49" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E49" s="27">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B50" s="2">
         <v>2185</v>
       </c>
       <c r="C50" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E50" s="27">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B51" s="2">
         <v>1925</v>
       </c>
       <c r="C51" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E51" s="27">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B52" s="2">
         <v>540</v>
       </c>
       <c r="C52" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E52" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B53" s="2">
         <v>525</v>
       </c>
       <c r="C53" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E53" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B54" s="2">
         <v>524</v>
       </c>
       <c r="C54" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E54" s="27">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B55" s="2">
         <v>495</v>
       </c>
       <c r="C55" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E55" s="27">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B56" s="2">
         <v>490</v>
       </c>
       <c r="C56" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E56" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B57" s="2">
         <v>450</v>
       </c>
       <c r="C57" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E57" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B58" s="2">
         <v>330</v>
       </c>
       <c r="C58" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E58" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B59" s="2">
         <v>245</v>
       </c>
       <c r="C59" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E59" s="27">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B60" s="2">
         <v>240</v>
       </c>
       <c r="C60" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E60" s="27">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B61" s="2">
         <v>210</v>
       </c>
       <c r="C61" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E61" s="27">
+        <v>0.42299999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B62" s="2">
         <v>200</v>
       </c>
       <c r="C62" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E62" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B63" s="2">
         <v>194</v>
       </c>
       <c r="C63" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E63" s="27">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B64" s="2">
         <v>180</v>
       </c>
       <c r="C64" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E64" s="27">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B65" s="2">
         <v>170</v>
       </c>
       <c r="C65" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E65" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B66" s="2">
         <v>155</v>
       </c>
       <c r="C66" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E66" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B67" s="2">
         <v>120</v>
       </c>
       <c r="C67" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E67" s="27">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B68" s="2">
         <v>105</v>
       </c>
       <c r="C68" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E68" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B69" s="2">
         <v>90</v>
       </c>
       <c r="C69" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E69" s="27">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B70" s="2">
         <v>90</v>
       </c>
       <c r="C70" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E70" s="27">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B71" s="2">
         <v>80</v>
       </c>
       <c r="C71" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E71" s="27">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B72" s="2">
         <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E72" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B73" s="2">
         <v>30</v>
       </c>
       <c r="C73" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E73" s="27">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B74" s="2">
         <v>30</v>
       </c>
       <c r="C74" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E74" s="27">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B75" s="2">
         <v>20</v>
       </c>
       <c r="C75" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E75" s="27">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B76" s="2">
         <v>15</v>
       </c>
       <c r="C76" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E76" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B77" s="2">
         <v>15</v>
       </c>
       <c r="C77" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E77" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+        <v>651</v>
+      </c>
+      <c r="E80" s="26" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B81" s="2">
         <v>12510</v>
       </c>
       <c r="C81" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E81" s="27">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B82" s="2">
         <v>2265</v>
       </c>
       <c r="C82" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E82" s="27">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B83" s="2">
         <v>1300</v>
       </c>
       <c r="C83" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E83" s="27">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B84" s="2">
         <v>945</v>
       </c>
       <c r="C84" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E84" s="27">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B85" s="2">
         <v>175</v>
       </c>
       <c r="C85" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E85" s="27">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B86" s="2">
         <v>120</v>
       </c>
       <c r="C86" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E86" s="27">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B87" s="2">
         <v>45</v>
       </c>
       <c r="C87" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+        <v>653</v>
+      </c>
+      <c r="E87" s="27">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="11" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+        <v>651</v>
+      </c>
+      <c r="E90" s="26" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B91" s="2">
         <v>150</v>
       </c>
       <c r="C91" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+      <c r="E91" s="27">
+        <v>0.44700000000000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B92" s="2">
         <v>30</v>
       </c>
       <c r="C92" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+      <c r="E92" s="27">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B93" s="2">
         <v>18</v>
       </c>
       <c r="C93" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+        <v>724</v>
+      </c>
+      <c r="E93" s="27">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B94" s="2">
         <v>4</v>
       </c>
       <c r="C94" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+        <v>763</v>
+      </c>
+      <c r="E94" s="27">
+        <v>0.44700000000000001</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B95" s="2">
         <v>2</v>
       </c>
       <c r="C95" t="s">
-        <v>788</v>
+        <v>787</v>
+      </c>
+      <c r="E95" s="27">
+        <v>0.44700000000000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="29" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="11" t="s">
+        <v>649</v>
+      </c>
+      <c r="E99" s="11" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E100" s="27">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E101" s="27">
+        <v>0.16500000000000001</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E102" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E103" s="27">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E104" s="27">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E105" s="27">
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E106" s="27">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>654</v>
+      </c>
+      <c r="E107" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E108" s="27">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/cocktail_source.xlsx
+++ b/cocktail_source.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\06GBA\OneDrive - Bain\Documents\GitHub\Greg's Bar\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bainandcompany-my.sharepoint.com/personal/gregoire_baudry_bain_com/Documents/Documents/GitHub/Greg's Bar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187AF605-8261-4BA5-8C1A-4BB3A5BE4362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{187AF605-8261-4BA5-8C1A-4BB3A5BE4362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08F9C602-CDC2-4E90-82FA-5DDD14489615}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,6 +38,64 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Gregoire Baudry</author>
+  </authors>
+  <commentList>
+    <comment ref="F162" authorId="0" shapeId="0" xr:uid="{0950EA97-0E15-40A9-9B75-CCD1192AA6DA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Gregoire Baudry:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Gin 52 ml @ 40% + Triple Sec 22 ml @ 30%. Lime juice is 0% ABV; the 2 bitters dashes are excluded (same convention as other rows).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G162" authorId="0" shapeId="0" xr:uid="{9BD060FA-582D-4246-9C0C-8D1802112DAB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Gregoire Baudry:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Alcohol ml / liquid volume of measured ingredients (52+22+15 ml). Dashes and garnishes excluded.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Gregoire Baudry</author>
@@ -142,7 +200,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="1112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="1116">
   <si>
     <t>Abbey</t>
   </si>
@@ -4250,6 +4308,22 @@
   <si>
     <t>The Sea Breeze</t>
   </si>
+  <si>
+    <t>Pegu Club</t>
+  </si>
+  <si>
+    <t>The signature drink of the Pegu Club, a long closed gentlemen's club in Rangoon, Burma. The cocktail is now served at the Pegu Club bar in New York City's SoHo district.</t>
+  </si>
+  <si>
+    <t>Gin – 52 ml
+Triple Sec – 22 ml
+Lime Juice – 15 ml
+Orange Bitters – 1 dash
+Angostura Bitters – 1 dash</t>
+  </si>
+  <si>
+    <t>images/cocktails/pegu-club.jpg</t>
+  </si>
 </sst>
 </file>
 
@@ -4258,15 +4332,21 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.#"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -4536,79 +4616,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4828,8 +4914,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1004"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Z1005"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -11603,27 +11689,29 @@
       <c r="Y161" s="15"/>
       <c r="Z161" s="15"/>
     </row>
-    <row r="162" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="B162" s="18" t="s">
-        <v>570</v>
-      </c>
-      <c r="C162" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="D162" s="19">
-        <v>5</v>
-      </c>
-      <c r="E162" s="20" t="s">
-        <v>992</v>
-      </c>
-      <c r="F162" s="21">
-        <v>20</v>
-      </c>
-      <c r="G162" s="21">
-        <v>0.23499999999999999</v>
+    <row r="162" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="17" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B162" s="35" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C162" s="35" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D162" s="23">
+        <v>0</v>
+      </c>
+      <c r="E162" s="36" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F162" s="25">
+        <f>ROUND(52*'Alcohol by Category'!$E$14+22*'Alcohol by Category'!$E$50,1)</f>
+        <v>27.4</v>
+      </c>
+      <c r="G162" s="25">
+        <f>ROUND(F162/(52+22+15),3)</f>
+        <v>0.308</v>
       </c>
       <c r="H162" s="15"/>
       <c r="I162" s="15"/>
@@ -11645,27 +11733,27 @@
       <c r="Y162" s="15"/>
       <c r="Z162" s="15"/>
     </row>
-    <row r="163" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="B163" s="22" t="s">
-        <v>571</v>
-      </c>
-      <c r="C163" s="22" t="s">
-        <v>301</v>
-      </c>
-      <c r="D163" s="23">
-        <v>1</v>
-      </c>
-      <c r="E163" s="24" t="s">
-        <v>993</v>
-      </c>
-      <c r="F163" s="25">
+    <row r="163" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="B163" s="18" t="s">
+        <v>570</v>
+      </c>
+      <c r="C163" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="D163" s="19">
         <v>5</v>
       </c>
-      <c r="G163" s="25">
-        <v>4.2999999999999997E-2</v>
+      <c r="E163" s="20" t="s">
+        <v>992</v>
+      </c>
+      <c r="F163" s="21">
+        <v>20</v>
+      </c>
+      <c r="G163" s="21">
+        <v>0.23499999999999999</v>
       </c>
       <c r="H163" s="15"/>
       <c r="I163" s="15"/>
@@ -11687,27 +11775,27 @@
       <c r="Y163" s="15"/>
       <c r="Z163" s="15"/>
     </row>
-    <row r="164" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="B164" s="18" t="s">
-        <v>572</v>
-      </c>
-      <c r="C164" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="D164" s="19">
+    <row r="164" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="B164" s="22" t="s">
+        <v>571</v>
+      </c>
+      <c r="C164" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="D164" s="23">
+        <v>1</v>
+      </c>
+      <c r="E164" s="24" t="s">
+        <v>993</v>
+      </c>
+      <c r="F164" s="25">
         <v>5</v>
       </c>
-      <c r="E164" s="20" t="s">
-        <v>994</v>
-      </c>
-      <c r="F164" s="21">
-        <v>35.1</v>
-      </c>
-      <c r="G164" s="21">
-        <v>0.33400000000000002</v>
+      <c r="G164" s="25">
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="H164" s="15"/>
       <c r="I164" s="15"/>
@@ -11729,27 +11817,27 @@
       <c r="Y164" s="15"/>
       <c r="Z164" s="15"/>
     </row>
-    <row r="165" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="B165" s="22" t="s">
-        <v>573</v>
-      </c>
-      <c r="C165" s="22" t="s">
-        <v>305</v>
-      </c>
-      <c r="D165" s="23">
-        <v>3</v>
-      </c>
-      <c r="E165" s="24" t="s">
-        <v>995</v>
-      </c>
-      <c r="F165" s="25">
-        <v>15</v>
-      </c>
-      <c r="G165" s="25">
-        <v>7.6999999999999999E-2</v>
+    <row r="165" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="B165" s="18" t="s">
+        <v>572</v>
+      </c>
+      <c r="C165" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="D165" s="19">
+        <v>5</v>
+      </c>
+      <c r="E165" s="20" t="s">
+        <v>994</v>
+      </c>
+      <c r="F165" s="21">
+        <v>35.1</v>
+      </c>
+      <c r="G165" s="21">
+        <v>0.33400000000000002</v>
       </c>
       <c r="H165" s="15"/>
       <c r="I165" s="15"/>
@@ -11771,27 +11859,27 @@
       <c r="Y165" s="15"/>
       <c r="Z165" s="15"/>
     </row>
-    <row r="166" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="B166" s="18" t="s">
-        <v>574</v>
-      </c>
-      <c r="C166" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="D166" s="19">
+    <row r="166" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="B166" s="22" t="s">
+        <v>573</v>
+      </c>
+      <c r="C166" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="D166" s="23">
+        <v>3</v>
+      </c>
+      <c r="E166" s="24" t="s">
+        <v>995</v>
+      </c>
+      <c r="F166" s="25">
         <v>15</v>
       </c>
-      <c r="E166" s="20" t="s">
-        <v>996</v>
-      </c>
-      <c r="F166" s="21">
-        <v>24</v>
-      </c>
-      <c r="G166" s="21">
-        <v>0.192</v>
+      <c r="G166" s="25">
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="H166" s="15"/>
       <c r="I166" s="15"/>
@@ -11813,27 +11901,27 @@
       <c r="Y166" s="15"/>
       <c r="Z166" s="15"/>
     </row>
-    <row r="167" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="B167" s="22" t="s">
-        <v>575</v>
-      </c>
-      <c r="C167" s="22" t="s">
-        <v>309</v>
-      </c>
-      <c r="D167" s="23">
-        <v>5</v>
-      </c>
-      <c r="E167" s="24" t="s">
-        <v>997</v>
-      </c>
-      <c r="F167" s="25">
-        <v>25.9</v>
-      </c>
-      <c r="G167" s="25">
-        <v>0.247</v>
+    <row r="167" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="B167" s="18" t="s">
+        <v>574</v>
+      </c>
+      <c r="C167" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="D167" s="19">
+        <v>15</v>
+      </c>
+      <c r="E167" s="20" t="s">
+        <v>996</v>
+      </c>
+      <c r="F167" s="21">
+        <v>24</v>
+      </c>
+      <c r="G167" s="21">
+        <v>0.192</v>
       </c>
       <c r="H167" s="15"/>
       <c r="I167" s="15"/>
@@ -11855,27 +11943,27 @@
       <c r="Y167" s="15"/>
       <c r="Z167" s="15"/>
     </row>
-    <row r="168" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="B168" s="18" t="s">
-        <v>576</v>
-      </c>
-      <c r="C168" s="18" t="s">
-        <v>311</v>
-      </c>
-      <c r="D168" s="19">
-        <v>0</v>
-      </c>
-      <c r="E168" s="20" t="s">
-        <v>998</v>
-      </c>
-      <c r="F168" s="21">
-        <v>24</v>
-      </c>
-      <c r="G168" s="21">
-        <v>0.33300000000000002</v>
+    <row r="168" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="B168" s="22" t="s">
+        <v>575</v>
+      </c>
+      <c r="C168" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="D168" s="23">
+        <v>5</v>
+      </c>
+      <c r="E168" s="24" t="s">
+        <v>997</v>
+      </c>
+      <c r="F168" s="25">
+        <v>25.9</v>
+      </c>
+      <c r="G168" s="25">
+        <v>0.247</v>
       </c>
       <c r="H168" s="15"/>
       <c r="I168" s="15"/>
@@ -11897,27 +11985,27 @@
       <c r="Y168" s="15"/>
       <c r="Z168" s="15"/>
     </row>
-    <row r="169" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="17" t="s">
-        <v>312</v>
-      </c>
-      <c r="B169" s="22" t="s">
-        <v>577</v>
-      </c>
-      <c r="C169" s="22" t="s">
-        <v>313</v>
-      </c>
-      <c r="D169" s="23">
-        <v>2</v>
-      </c>
-      <c r="E169" s="24" t="s">
-        <v>999</v>
-      </c>
-      <c r="F169" s="25">
-        <v>15.6</v>
-      </c>
-      <c r="G169" s="25">
-        <v>0.161</v>
+    <row r="169" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="B169" s="18" t="s">
+        <v>576</v>
+      </c>
+      <c r="C169" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="D169" s="19">
+        <v>0</v>
+      </c>
+      <c r="E169" s="20" t="s">
+        <v>998</v>
+      </c>
+      <c r="F169" s="21">
+        <v>24</v>
+      </c>
+      <c r="G169" s="21">
+        <v>0.33300000000000002</v>
       </c>
       <c r="H169" s="15"/>
       <c r="I169" s="15"/>
@@ -11939,27 +12027,27 @@
       <c r="Y169" s="15"/>
       <c r="Z169" s="15"/>
     </row>
-    <row r="170" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="B170" s="18" t="s">
-        <v>578</v>
-      </c>
-      <c r="C170" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="D170" s="19">
-        <v>12</v>
-      </c>
-      <c r="E170" s="20" t="s">
-        <v>1000</v>
-      </c>
-      <c r="F170" s="21">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="G170" s="21">
-        <v>0.189</v>
+    <row r="170" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A170" s="17" t="s">
+        <v>312</v>
+      </c>
+      <c r="B170" s="22" t="s">
+        <v>577</v>
+      </c>
+      <c r="C170" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="D170" s="23">
+        <v>2</v>
+      </c>
+      <c r="E170" s="24" t="s">
+        <v>999</v>
+      </c>
+      <c r="F170" s="25">
+        <v>15.6</v>
+      </c>
+      <c r="G170" s="25">
+        <v>0.161</v>
       </c>
       <c r="H170" s="15"/>
       <c r="I170" s="15"/>
@@ -11981,27 +12069,27 @@
       <c r="Y170" s="15"/>
       <c r="Z170" s="15"/>
     </row>
-    <row r="171" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="B171" s="22" t="s">
-        <v>579</v>
-      </c>
-      <c r="C171" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="D171" s="23">
-        <v>0</v>
-      </c>
-      <c r="E171" s="24" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F171" s="25">
-        <v>19.5</v>
-      </c>
-      <c r="G171" s="25">
-        <v>0.108</v>
+    <row r="171" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A171" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="B171" s="18" t="s">
+        <v>578</v>
+      </c>
+      <c r="C171" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="D171" s="19">
+        <v>12</v>
+      </c>
+      <c r="E171" s="20" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F171" s="21">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="G171" s="21">
+        <v>0.189</v>
       </c>
       <c r="H171" s="15"/>
       <c r="I171" s="15"/>
@@ -12023,27 +12111,27 @@
       <c r="Y171" s="15"/>
       <c r="Z171" s="15"/>
     </row>
-    <row r="172" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="B172" s="18" t="s">
-        <v>580</v>
-      </c>
-      <c r="C172" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="D172" s="19">
-        <v>10</v>
-      </c>
-      <c r="E172" s="20" t="s">
-        <v>1002</v>
-      </c>
-      <c r="F172" s="21">
-        <v>24</v>
-      </c>
-      <c r="G172" s="21">
-        <v>0.17799999999999999</v>
+    <row r="172" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A172" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="B172" s="22" t="s">
+        <v>579</v>
+      </c>
+      <c r="C172" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="D172" s="23">
+        <v>0</v>
+      </c>
+      <c r="E172" s="24" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F172" s="25">
+        <v>19.5</v>
+      </c>
+      <c r="G172" s="25">
+        <v>0.108</v>
       </c>
       <c r="H172" s="15"/>
       <c r="I172" s="15"/>
@@ -12066,26 +12154,26 @@
       <c r="Z172" s="15"/>
     </row>
     <row r="173" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="B173" s="22" t="s">
-        <v>581</v>
-      </c>
-      <c r="C173" s="22" t="s">
-        <v>321</v>
-      </c>
-      <c r="D173" s="23">
-        <v>7</v>
-      </c>
-      <c r="E173" s="24" t="s">
-        <v>1003</v>
-      </c>
-      <c r="F173" s="25">
-        <v>21</v>
-      </c>
-      <c r="G173" s="25">
-        <v>0.13300000000000001</v>
+      <c r="A173" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="B173" s="18" t="s">
+        <v>580</v>
+      </c>
+      <c r="C173" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="D173" s="19">
+        <v>10</v>
+      </c>
+      <c r="E173" s="20" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F173" s="21">
+        <v>24</v>
+      </c>
+      <c r="G173" s="21">
+        <v>0.17799999999999999</v>
       </c>
       <c r="H173" s="15"/>
       <c r="I173" s="15"/>
@@ -12108,26 +12196,26 @@
       <c r="Z173" s="15"/>
     </row>
     <row r="174" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="B174" s="18" t="s">
-        <v>582</v>
-      </c>
-      <c r="C174" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="D174" s="19">
-        <v>0</v>
-      </c>
-      <c r="E174" s="20" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F174" s="21">
-        <v>9</v>
-      </c>
-      <c r="G174" s="21">
-        <v>0.03</v>
+      <c r="A174" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="B174" s="22" t="s">
+        <v>581</v>
+      </c>
+      <c r="C174" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="D174" s="23">
+        <v>7</v>
+      </c>
+      <c r="E174" s="24" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F174" s="25">
+        <v>21</v>
+      </c>
+      <c r="G174" s="25">
+        <v>0.13300000000000001</v>
       </c>
       <c r="H174" s="15"/>
       <c r="I174" s="15"/>
@@ -12149,27 +12237,27 @@
       <c r="Y174" s="15"/>
       <c r="Z174" s="15"/>
     </row>
-    <row r="175" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="B175" s="22" t="s">
-        <v>583</v>
-      </c>
-      <c r="C175" s="22" t="s">
-        <v>325</v>
-      </c>
-      <c r="D175" s="23">
-        <v>2</v>
-      </c>
-      <c r="E175" s="24" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F175" s="25">
-        <v>19.5</v>
-      </c>
-      <c r="G175" s="25">
-        <v>0.13</v>
+    <row r="175" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A175" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="B175" s="18" t="s">
+        <v>582</v>
+      </c>
+      <c r="C175" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="D175" s="19">
+        <v>0</v>
+      </c>
+      <c r="E175" s="20" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F175" s="21">
+        <v>9</v>
+      </c>
+      <c r="G175" s="21">
+        <v>0.03</v>
       </c>
       <c r="H175" s="15"/>
       <c r="I175" s="15"/>
@@ -12191,27 +12279,27 @@
       <c r="Y175" s="15"/>
       <c r="Z175" s="15"/>
     </row>
-    <row r="176" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="B176" s="18" t="s">
-        <v>584</v>
-      </c>
-      <c r="C176" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="D176" s="19">
+    <row r="176" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A176" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="B176" s="22" t="s">
+        <v>583</v>
+      </c>
+      <c r="C176" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="D176" s="23">
         <v>2</v>
       </c>
-      <c r="E176" s="20" t="s">
-        <v>1006</v>
-      </c>
-      <c r="F176" s="21">
-        <v>24</v>
-      </c>
-      <c r="G176" s="21">
-        <v>0.17299999999999999</v>
+      <c r="E176" s="24" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F176" s="25">
+        <v>19.5</v>
+      </c>
+      <c r="G176" s="25">
+        <v>0.13</v>
       </c>
       <c r="H176" s="15"/>
       <c r="I176" s="15"/>
@@ -12233,27 +12321,27 @@
       <c r="Y176" s="15"/>
       <c r="Z176" s="15"/>
     </row>
-    <row r="177" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="B177" s="22" t="s">
-        <v>585</v>
-      </c>
-      <c r="C177" s="22" t="s">
-        <v>329</v>
-      </c>
-      <c r="D177" s="23">
-        <v>1</v>
-      </c>
-      <c r="E177" s="24" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F177" s="25">
-        <v>9</v>
-      </c>
-      <c r="G177" s="25">
-        <v>4.2999999999999997E-2</v>
+    <row r="177" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="B177" s="18" t="s">
+        <v>584</v>
+      </c>
+      <c r="C177" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="D177" s="19">
+        <v>2</v>
+      </c>
+      <c r="E177" s="20" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F177" s="21">
+        <v>24</v>
+      </c>
+      <c r="G177" s="21">
+        <v>0.17299999999999999</v>
       </c>
       <c r="H177" s="15"/>
       <c r="I177" s="15"/>
@@ -12275,27 +12363,27 @@
       <c r="Y177" s="15"/>
       <c r="Z177" s="15"/>
     </row>
-    <row r="178" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="B178" s="18" t="s">
-        <v>586</v>
-      </c>
-      <c r="C178" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="D178" s="19">
-        <v>2</v>
-      </c>
-      <c r="E178" s="20" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F178" s="21">
-        <v>24</v>
-      </c>
-      <c r="G178" s="21">
-        <v>0.22900000000000001</v>
+    <row r="178" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A178" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="B178" s="22" t="s">
+        <v>585</v>
+      </c>
+      <c r="C178" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="D178" s="23">
+        <v>1</v>
+      </c>
+      <c r="E178" s="24" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F178" s="25">
+        <v>9</v>
+      </c>
+      <c r="G178" s="25">
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="H178" s="15"/>
       <c r="I178" s="15"/>
@@ -12318,26 +12406,26 @@
       <c r="Z178" s="15"/>
     </row>
     <row r="179" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="B179" s="22" t="s">
-        <v>587</v>
-      </c>
-      <c r="C179" s="22" t="s">
-        <v>333</v>
-      </c>
-      <c r="D179" s="23">
-        <v>0</v>
-      </c>
-      <c r="E179" s="24" t="s">
-        <v>1009</v>
-      </c>
-      <c r="F179" s="25">
-        <v>28.8</v>
-      </c>
-      <c r="G179" s="25">
-        <v>0.32</v>
+      <c r="A179" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="B179" s="18" t="s">
+        <v>586</v>
+      </c>
+      <c r="C179" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="D179" s="19">
+        <v>2</v>
+      </c>
+      <c r="E179" s="20" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F179" s="21">
+        <v>24</v>
+      </c>
+      <c r="G179" s="21">
+        <v>0.22900000000000001</v>
       </c>
       <c r="H179" s="15"/>
       <c r="I179" s="15"/>
@@ -12359,27 +12447,27 @@
       <c r="Y179" s="15"/>
       <c r="Z179" s="15"/>
     </row>
-    <row r="180" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="B180" s="18" t="s">
-        <v>588</v>
-      </c>
-      <c r="C180" s="18" t="s">
-        <v>335</v>
-      </c>
-      <c r="D180" s="19">
+    <row r="180" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="B180" s="22" t="s">
+        <v>587</v>
+      </c>
+      <c r="C180" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="D180" s="23">
         <v>0</v>
       </c>
-      <c r="E180" s="20" t="s">
-        <v>1010</v>
-      </c>
-      <c r="F180" s="21">
-        <v>30.6</v>
-      </c>
-      <c r="G180" s="21">
-        <v>0.29099999999999998</v>
+      <c r="E180" s="24" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F180" s="25">
+        <v>28.8</v>
+      </c>
+      <c r="G180" s="25">
+        <v>0.32</v>
       </c>
       <c r="H180" s="15"/>
       <c r="I180" s="15"/>
@@ -12401,27 +12489,27 @@
       <c r="Y180" s="15"/>
       <c r="Z180" s="15"/>
     </row>
-    <row r="181" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="B181" s="22" t="s">
-        <v>589</v>
-      </c>
-      <c r="C181" s="22" t="s">
-        <v>337</v>
-      </c>
-      <c r="D181" s="23">
-        <v>2</v>
-      </c>
-      <c r="E181" s="24" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F181" s="25">
-        <v>32</v>
-      </c>
-      <c r="G181" s="25">
-        <v>0.4</v>
+    <row r="181" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="B181" s="18" t="s">
+        <v>588</v>
+      </c>
+      <c r="C181" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="D181" s="19">
+        <v>0</v>
+      </c>
+      <c r="E181" s="20" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F181" s="21">
+        <v>30.6</v>
+      </c>
+      <c r="G181" s="21">
+        <v>0.29099999999999998</v>
       </c>
       <c r="H181" s="15"/>
       <c r="I181" s="15"/>
@@ -12444,26 +12532,26 @@
       <c r="Z181" s="15"/>
     </row>
     <row r="182" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="B182" s="18" t="s">
-        <v>590</v>
-      </c>
-      <c r="C182" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="D182" s="19">
-        <v>1</v>
-      </c>
-      <c r="E182" s="20" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F182" s="21">
-        <v>24</v>
-      </c>
-      <c r="G182" s="21">
-        <v>0.32</v>
+      <c r="A182" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="B182" s="22" t="s">
+        <v>589</v>
+      </c>
+      <c r="C182" s="22" t="s">
+        <v>337</v>
+      </c>
+      <c r="D182" s="23">
+        <v>2</v>
+      </c>
+      <c r="E182" s="24" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F182" s="25">
+        <v>32</v>
+      </c>
+      <c r="G182" s="25">
+        <v>0.4</v>
       </c>
       <c r="H182" s="15"/>
       <c r="I182" s="15"/>
@@ -12485,27 +12573,27 @@
       <c r="Y182" s="15"/>
       <c r="Z182" s="15"/>
     </row>
-    <row r="183" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="B183" s="22" t="s">
-        <v>591</v>
-      </c>
-      <c r="C183" s="22" t="s">
-        <v>341</v>
-      </c>
-      <c r="D183" s="23">
-        <v>0</v>
-      </c>
-      <c r="E183" s="24" t="s">
-        <v>1013</v>
-      </c>
-      <c r="F183" s="25">
-        <v>27.6</v>
-      </c>
-      <c r="G183" s="25">
-        <v>0.27100000000000002</v>
+    <row r="183" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="B183" s="18" t="s">
+        <v>590</v>
+      </c>
+      <c r="C183" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="D183" s="19">
+        <v>1</v>
+      </c>
+      <c r="E183" s="20" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F183" s="21">
+        <v>24</v>
+      </c>
+      <c r="G183" s="21">
+        <v>0.32</v>
       </c>
       <c r="H183" s="15"/>
       <c r="I183" s="15"/>
@@ -12527,27 +12615,27 @@
       <c r="Y183" s="15"/>
       <c r="Z183" s="15"/>
     </row>
-    <row r="184" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="B184" s="18" t="s">
-        <v>592</v>
-      </c>
-      <c r="C184" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="D184" s="19">
+    <row r="184" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="17" t="s">
+        <v>340</v>
+      </c>
+      <c r="B184" s="22" t="s">
+        <v>591</v>
+      </c>
+      <c r="C184" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="D184" s="23">
         <v>0</v>
       </c>
-      <c r="E184" s="20" t="s">
-        <v>1014</v>
-      </c>
-      <c r="F184" s="21">
-        <v>21.8</v>
-      </c>
-      <c r="G184" s="21">
-        <v>0.13200000000000001</v>
+      <c r="E184" s="24" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F184" s="25">
+        <v>27.6</v>
+      </c>
+      <c r="G184" s="25">
+        <v>0.27100000000000002</v>
       </c>
       <c r="H184" s="15"/>
       <c r="I184" s="15"/>
@@ -12569,27 +12657,27 @@
       <c r="Y184" s="15"/>
       <c r="Z184" s="15"/>
     </row>
-    <row r="185" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="17" t="s">
-        <v>344</v>
-      </c>
-      <c r="B185" s="22" t="s">
-        <v>593</v>
-      </c>
-      <c r="C185" s="22" t="s">
-        <v>345</v>
-      </c>
-      <c r="D185" s="23">
+    <row r="185" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="B185" s="18" t="s">
+        <v>592</v>
+      </c>
+      <c r="C185" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="D185" s="19">
         <v>0</v>
       </c>
-      <c r="E185" s="24" t="s">
-        <v>1015</v>
-      </c>
-      <c r="F185" s="25">
-        <v>18</v>
-      </c>
-      <c r="G185" s="25">
-        <v>0.109</v>
+      <c r="E185" s="20" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F185" s="21">
+        <v>21.8</v>
+      </c>
+      <c r="G185" s="21">
+        <v>0.13200000000000001</v>
       </c>
       <c r="H185" s="15"/>
       <c r="I185" s="15"/>
@@ -12611,27 +12699,27 @@
       <c r="Y185" s="15"/>
       <c r="Z185" s="15"/>
     </row>
-    <row r="186" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="17" t="s">
-        <v>1055</v>
+        <v>344</v>
       </c>
       <c r="B186" s="22" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C186" s="18" t="s">
-        <v>1057</v>
+        <v>593</v>
+      </c>
+      <c r="C186" s="22" t="s">
+        <v>345</v>
       </c>
       <c r="D186" s="23">
         <v>0</v>
       </c>
-      <c r="E186" s="20" t="s">
-        <v>1058</v>
+      <c r="E186" s="24" t="s">
+        <v>1015</v>
       </c>
       <c r="F186" s="25">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G186" s="25">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="H186" s="15"/>
       <c r="I186" s="15"/>
@@ -12653,21 +12741,21 @@
       <c r="Y186" s="15"/>
       <c r="Z186" s="15"/>
     </row>
-    <row r="187" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="17" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="B187" s="22" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="C187" s="18" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="D187" s="23">
         <v>0</v>
       </c>
       <c r="E187" s="20" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="F187" s="25">
         <v>0</v>
@@ -12695,27 +12783,27 @@
       <c r="Y187" s="15"/>
       <c r="Z187" s="15"/>
     </row>
-    <row r="188" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="17" t="s">
-        <v>347</v>
+        <v>1059</v>
       </c>
       <c r="B188" s="22" t="s">
-        <v>595</v>
-      </c>
-      <c r="C188" s="22" t="s">
-        <v>348</v>
+        <v>1060</v>
+      </c>
+      <c r="C188" s="18" t="s">
+        <v>1061</v>
       </c>
       <c r="D188" s="23">
         <v>0</v>
       </c>
-      <c r="E188" s="24" t="s">
-        <v>1017</v>
+      <c r="E188" s="20" t="s">
+        <v>1062</v>
       </c>
       <c r="F188" s="25">
-        <v>32.4</v>
+        <v>0</v>
       </c>
       <c r="G188" s="25">
-        <v>0.19600000000000001</v>
+        <v>0</v>
       </c>
       <c r="H188" s="15"/>
       <c r="I188" s="15"/>
@@ -12737,27 +12825,27 @@
       <c r="Y188" s="15"/>
       <c r="Z188" s="15"/>
     </row>
-    <row r="189" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="B189" s="18" t="s">
-        <v>596</v>
-      </c>
-      <c r="C189" s="18" t="s">
-        <v>350</v>
-      </c>
-      <c r="D189" s="19">
-        <v>2</v>
-      </c>
-      <c r="E189" s="20" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F189" s="21">
-        <v>12</v>
-      </c>
-      <c r="G189" s="21">
-        <v>3.5999999999999997E-2</v>
+    <row r="189" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="17" t="s">
+        <v>347</v>
+      </c>
+      <c r="B189" s="22" t="s">
+        <v>595</v>
+      </c>
+      <c r="C189" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="D189" s="23">
+        <v>0</v>
+      </c>
+      <c r="E189" s="24" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F189" s="25">
+        <v>32.4</v>
+      </c>
+      <c r="G189" s="25">
+        <v>0.19600000000000001</v>
       </c>
       <c r="H189" s="15"/>
       <c r="I189" s="15"/>
@@ -12779,27 +12867,27 @@
       <c r="Y189" s="15"/>
       <c r="Z189" s="15"/>
     </row>
-    <row r="190" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="17" t="s">
-        <v>351</v>
-      </c>
-      <c r="B190" s="22" t="s">
-        <v>597</v>
-      </c>
-      <c r="C190" s="22" t="s">
-        <v>352</v>
-      </c>
-      <c r="D190" s="23">
+    <row r="190" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A190" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="B190" s="18" t="s">
+        <v>596</v>
+      </c>
+      <c r="C190" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="D190" s="19">
         <v>2</v>
       </c>
-      <c r="E190" s="24" t="s">
-        <v>1019</v>
-      </c>
-      <c r="F190" s="25">
-        <v>33</v>
-      </c>
-      <c r="G190" s="25">
-        <v>0.3</v>
+      <c r="E190" s="20" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F190" s="21">
+        <v>12</v>
+      </c>
+      <c r="G190" s="21">
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="H190" s="15"/>
       <c r="I190" s="15"/>
@@ -12822,26 +12910,26 @@
       <c r="Z190" s="15"/>
     </row>
     <row r="191" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="16" t="s">
-        <v>353</v>
-      </c>
-      <c r="B191" s="18" t="s">
-        <v>598</v>
-      </c>
-      <c r="C191" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="D191" s="19">
-        <v>1</v>
-      </c>
-      <c r="E191" s="20" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F191" s="21">
-        <v>21.8</v>
-      </c>
-      <c r="G191" s="21">
-        <v>0.20799999999999999</v>
+      <c r="A191" s="17" t="s">
+        <v>351</v>
+      </c>
+      <c r="B191" s="22" t="s">
+        <v>597</v>
+      </c>
+      <c r="C191" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="D191" s="23">
+        <v>2</v>
+      </c>
+      <c r="E191" s="24" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F191" s="25">
+        <v>33</v>
+      </c>
+      <c r="G191" s="25">
+        <v>0.3</v>
       </c>
       <c r="H191" s="15"/>
       <c r="I191" s="15"/>
@@ -12864,26 +12952,26 @@
       <c r="Z191" s="15"/>
     </row>
     <row r="192" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="17" t="s">
-        <v>355</v>
-      </c>
-      <c r="B192" s="22" t="s">
-        <v>599</v>
-      </c>
-      <c r="C192" s="22" t="s">
-        <v>356</v>
-      </c>
-      <c r="D192" s="23">
-        <v>61</v>
-      </c>
-      <c r="E192" s="24" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F192" s="25">
-        <v>24</v>
-      </c>
-      <c r="G192" s="25">
-        <v>0.14499999999999999</v>
+      <c r="A192" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="B192" s="18" t="s">
+        <v>598</v>
+      </c>
+      <c r="C192" s="18" t="s">
+        <v>354</v>
+      </c>
+      <c r="D192" s="19">
+        <v>1</v>
+      </c>
+      <c r="E192" s="20" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F192" s="21">
+        <v>21.8</v>
+      </c>
+      <c r="G192" s="21">
+        <v>0.20799999999999999</v>
       </c>
       <c r="H192" s="15"/>
       <c r="I192" s="15"/>
@@ -12905,27 +12993,27 @@
       <c r="Y192" s="15"/>
       <c r="Z192" s="15"/>
     </row>
-    <row r="193" spans="1:26" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="16" t="s">
-        <v>357</v>
-      </c>
-      <c r="B193" s="18" t="s">
-        <v>600</v>
-      </c>
-      <c r="C193" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="D193" s="19">
-        <v>2</v>
-      </c>
-      <c r="E193" s="20" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F193" s="21">
-        <v>32</v>
-      </c>
-      <c r="G193" s="21">
-        <v>0.25600000000000001</v>
+    <row r="193" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A193" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="B193" s="22" t="s">
+        <v>599</v>
+      </c>
+      <c r="C193" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="D193" s="23">
+        <v>61</v>
+      </c>
+      <c r="E193" s="24" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F193" s="25">
+        <v>24</v>
+      </c>
+      <c r="G193" s="25">
+        <v>0.14499999999999999</v>
       </c>
       <c r="H193" s="15"/>
       <c r="I193" s="15"/>
@@ -12947,27 +13035,27 @@
       <c r="Y193" s="15"/>
       <c r="Z193" s="15"/>
     </row>
-    <row r="194" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="17" t="s">
-        <v>359</v>
-      </c>
-      <c r="B194" s="22" t="s">
-        <v>601</v>
-      </c>
-      <c r="C194" s="22" t="s">
-        <v>360</v>
-      </c>
-      <c r="D194" s="23">
-        <v>54</v>
-      </c>
-      <c r="E194" s="24" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F194" s="25">
-        <v>16</v>
-      </c>
-      <c r="G194" s="25">
-        <v>8.4000000000000005E-2</v>
+    <row r="194" spans="1:26" ht="135.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="B194" s="18" t="s">
+        <v>600</v>
+      </c>
+      <c r="C194" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="D194" s="19">
+        <v>2</v>
+      </c>
+      <c r="E194" s="20" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F194" s="21">
+        <v>32</v>
+      </c>
+      <c r="G194" s="21">
+        <v>0.25600000000000001</v>
       </c>
       <c r="H194" s="15"/>
       <c r="I194" s="15"/>
@@ -12989,27 +13077,27 @@
       <c r="Y194" s="15"/>
       <c r="Z194" s="15"/>
     </row>
-    <row r="195" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="B195" s="18" t="s">
-        <v>602</v>
-      </c>
-      <c r="C195" s="18" t="s">
-        <v>362</v>
-      </c>
-      <c r="D195" s="19">
-        <v>50</v>
-      </c>
-      <c r="E195" s="20" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F195" s="21">
-        <v>11.7</v>
-      </c>
-      <c r="G195" s="21">
-        <v>7.1999999999999995E-2</v>
+    <row r="195" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="B195" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="C195" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="D195" s="23">
+        <v>54</v>
+      </c>
+      <c r="E195" s="24" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F195" s="25">
+        <v>16</v>
+      </c>
+      <c r="G195" s="25">
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="H195" s="15"/>
       <c r="I195" s="15"/>
@@ -13031,27 +13119,27 @@
       <c r="Y195" s="15"/>
       <c r="Z195" s="15"/>
     </row>
-    <row r="196" spans="1:26" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="17" t="s">
-        <v>363</v>
-      </c>
-      <c r="B196" s="22" t="s">
-        <v>603</v>
-      </c>
-      <c r="C196" s="22" t="s">
-        <v>364</v>
-      </c>
-      <c r="D196" s="23">
-        <v>0</v>
-      </c>
-      <c r="E196" s="24" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F196" s="25">
-        <v>25.7</v>
-      </c>
-      <c r="G196" s="25">
-        <v>0.30599999999999999</v>
+    <row r="196" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="B196" s="18" t="s">
+        <v>602</v>
+      </c>
+      <c r="C196" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="D196" s="19">
+        <v>50</v>
+      </c>
+      <c r="E196" s="20" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F196" s="21">
+        <v>11.7</v>
+      </c>
+      <c r="G196" s="21">
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="H196" s="15"/>
       <c r="I196" s="15"/>
@@ -13073,27 +13161,27 @@
       <c r="Y196" s="15"/>
       <c r="Z196" s="15"/>
     </row>
-    <row r="197" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="B197" s="18" t="s">
-        <v>604</v>
-      </c>
-      <c r="C197" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="D197" s="19">
-        <v>1</v>
-      </c>
-      <c r="E197" s="20" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F197" s="21">
-        <v>31.7</v>
-      </c>
-      <c r="G197" s="21">
-        <v>0.31900000000000001</v>
+    <row r="197" spans="1:26" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A197" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="B197" s="22" t="s">
+        <v>603</v>
+      </c>
+      <c r="C197" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="D197" s="23">
+        <v>0</v>
+      </c>
+      <c r="E197" s="24" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F197" s="25">
+        <v>25.7</v>
+      </c>
+      <c r="G197" s="25">
+        <v>0.30599999999999999</v>
       </c>
       <c r="H197" s="15"/>
       <c r="I197" s="15"/>
@@ -13115,27 +13203,27 @@
       <c r="Y197" s="15"/>
       <c r="Z197" s="15"/>
     </row>
-    <row r="198" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="17" t="s">
-        <v>367</v>
-      </c>
-      <c r="B198" s="22" t="s">
-        <v>605</v>
-      </c>
-      <c r="C198" s="22" t="s">
-        <v>368</v>
-      </c>
-      <c r="D198" s="23">
-        <v>115</v>
-      </c>
-      <c r="E198" s="24" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F198" s="25">
-        <v>11.6</v>
-      </c>
-      <c r="G198" s="25">
-        <v>9.7000000000000003E-2</v>
+    <row r="198" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A198" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="B198" s="18" t="s">
+        <v>604</v>
+      </c>
+      <c r="C198" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="D198" s="19">
+        <v>1</v>
+      </c>
+      <c r="E198" s="20" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F198" s="21">
+        <v>31.7</v>
+      </c>
+      <c r="G198" s="21">
+        <v>0.31900000000000001</v>
       </c>
       <c r="H198" s="15"/>
       <c r="I198" s="15"/>
@@ -13159,27 +13247,25 @@
     </row>
     <row r="199" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="17" t="s">
-        <v>1063</v>
+        <v>367</v>
       </c>
       <c r="B199" s="22" t="s">
-        <v>1064</v>
+        <v>605</v>
       </c>
       <c r="C199" s="22" t="s">
-        <v>1065</v>
+        <v>368</v>
       </c>
       <c r="D199" s="23">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E199" s="24" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F199" s="30" cm="1">
-        <f t="array" ref="F199">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C199,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
-        <v>18.8</v>
-      </c>
-      <c r="G199" s="30" cm="1">
-        <f t="array" ref="G199">ROUND(F199/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C199,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
-        <v>0.157</v>
+        <v>1027</v>
+      </c>
+      <c r="F199" s="25">
+        <v>11.6</v>
+      </c>
+      <c r="G199" s="25">
+        <v>9.7000000000000003E-2</v>
       </c>
       <c r="H199" s="15"/>
       <c r="I199" s="15"/>
@@ -13203,27 +13289,27 @@
     </row>
     <row r="200" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="17" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="B200" s="22" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="C200" s="22" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="D200" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E200" s="24" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="F200" s="30" cm="1">
         <f t="array" ref="F200">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C200,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
-        <v>17.2</v>
+        <v>18.8</v>
       </c>
       <c r="G200" s="30" cm="1">
         <f t="array" ref="G200">ROUND(F200/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C200,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
-        <v>0.14299999999999999</v>
+        <v>0.157</v>
       </c>
       <c r="H200" s="15"/>
       <c r="I200" s="15"/>
@@ -13247,27 +13333,27 @@
     </row>
     <row r="201" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="17" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="B201" s="22" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="C201" s="22" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="D201" s="23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E201" s="24" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="F201" s="30" cm="1">
         <f t="array" ref="F201">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C201,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
-        <v>13.8</v>
+        <v>17.2</v>
       </c>
       <c r="G201" s="30" cm="1">
         <f t="array" ref="G201">ROUND(F201/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C201,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
-        <v>0.115</v>
+        <v>0.14299999999999999</v>
       </c>
       <c r="H201" s="15"/>
       <c r="I201" s="15"/>
@@ -13291,27 +13377,27 @@
     </row>
     <row r="202" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="17" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="B202" s="22" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="C202" s="22" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="D202" s="23">
         <v>3</v>
       </c>
       <c r="E202" s="24" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F202" s="30" cm="1">
         <f t="array" ref="F202">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C202,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
-        <v>15.2</v>
+        <v>13.8</v>
       </c>
       <c r="G202" s="30" cm="1">
         <f t="array" ref="G202">ROUND(F202/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C202,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
-        <v>0.127</v>
+        <v>0.115</v>
       </c>
       <c r="H202" s="15"/>
       <c r="I202" s="15"/>
@@ -13335,19 +13421,19 @@
     </row>
     <row r="203" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="17" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="B203" s="22" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="C203" s="22" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="D203" s="23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E203" s="24" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="F203" s="30" cm="1">
         <f t="array" ref="F203">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C203,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
@@ -13379,27 +13465,27 @@
     </row>
     <row r="204" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="17" t="s">
-        <v>1088</v>
+        <v>1079</v>
       </c>
       <c r="B204" s="22" t="s">
-        <v>1089</v>
+        <v>1080</v>
       </c>
       <c r="C204" s="22" t="s">
-        <v>1090</v>
+        <v>1081</v>
       </c>
       <c r="D204" s="23">
         <v>0</v>
       </c>
       <c r="E204" s="24" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="F204" s="30" cm="1">
         <f t="array" ref="F204">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C204,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="G204" s="30" cm="1">
         <f t="array" ref="G204">ROUND(F204/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C204,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
-        <v>0.16</v>
+        <v>0.127</v>
       </c>
       <c r="H204" s="15"/>
       <c r="I204" s="15"/>
@@ -13421,29 +13507,29 @@
       <c r="Y204" s="15"/>
       <c r="Z204" s="15"/>
     </row>
-    <row r="205" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="17" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="B205" s="22" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="C205" s="22" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="D205" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E205" s="24" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="F205" s="30" cm="1">
         <f t="array" ref="F205">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C205,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
-        <v>12.8</v>
+        <v>19.2</v>
       </c>
       <c r="G205" s="30" cm="1">
         <f t="array" ref="G205">ROUND(F205/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C205,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
-        <v>0.10199999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="H205" s="15"/>
       <c r="I205" s="15"/>
@@ -13465,29 +13551,29 @@
       <c r="Y205" s="15"/>
       <c r="Z205" s="15"/>
     </row>
-    <row r="206" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="17" t="s">
-        <v>1083</v>
+        <v>1092</v>
       </c>
       <c r="B206" s="22" t="s">
-        <v>1084</v>
+        <v>1093</v>
       </c>
       <c r="C206" s="22" t="s">
-        <v>1085</v>
+        <v>1094</v>
       </c>
       <c r="D206" s="23">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E206" s="24" t="s">
-        <v>1086</v>
+        <v>1095</v>
       </c>
       <c r="F206" s="30" cm="1">
         <f t="array" ref="F206">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C206,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
-        <v>14.2</v>
+        <v>12.8</v>
       </c>
       <c r="G206" s="30" cm="1">
         <f t="array" ref="G206">ROUND(F206/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C206,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
-        <v>0.11799999999999999</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="H206" s="15"/>
       <c r="I206" s="15"/>
@@ -13511,25 +13597,27 @@
     </row>
     <row r="207" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="17" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="B207" s="22" t="s">
-        <v>521</v>
+        <v>1084</v>
       </c>
       <c r="C207" s="22" t="s">
-        <v>202</v>
+        <v>1085</v>
       </c>
       <c r="D207" s="23">
         <v>6</v>
       </c>
       <c r="E207" s="24" t="s">
-        <v>920</v>
-      </c>
-      <c r="F207" s="25">
-        <v>15.2</v>
-      </c>
-      <c r="G207" s="25">
-        <v>0.127</v>
+        <v>1086</v>
+      </c>
+      <c r="F207" s="30" cm="1">
+        <f t="array" ref="F207">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C207,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$107,'Alcohol by Category'!$E$99:$E$107),0)),_xlpm.amt*_xlpm.abv)),1)</f>
+        <v>14.2</v>
+      </c>
+      <c r="G207" s="30" cm="1">
+        <f t="array" ref="G207">ROUND(F207/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C207,,CHAR(10)),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.lines," – ")," ")),_xlpm.amt)),3)</f>
+        <v>0.11799999999999999</v>
       </c>
       <c r="H207" s="15"/>
       <c r="I207" s="15"/>
@@ -13551,27 +13639,27 @@
       <c r="Y207" s="15"/>
       <c r="Z207" s="15"/>
     </row>
-    <row r="208" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="17" t="s">
-        <v>369</v>
+        <v>1087</v>
       </c>
       <c r="B208" s="22" t="s">
-        <v>606</v>
+        <v>521</v>
       </c>
       <c r="C208" s="22" t="s">
-        <v>370</v>
+        <v>202</v>
       </c>
       <c r="D208" s="23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E208" s="24" t="s">
-        <v>1028</v>
+        <v>920</v>
       </c>
       <c r="F208" s="25">
-        <v>21.3</v>
+        <v>15.2</v>
       </c>
       <c r="G208" s="25">
-        <v>0.158</v>
+        <v>0.127</v>
       </c>
       <c r="H208" s="15"/>
       <c r="I208" s="15"/>
@@ -13593,27 +13681,27 @@
       <c r="Y208" s="15"/>
       <c r="Z208" s="15"/>
     </row>
-    <row r="209" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="16" t="s">
-        <v>371</v>
-      </c>
-      <c r="B209" s="18" t="s">
-        <v>607</v>
-      </c>
-      <c r="C209" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="D209" s="19">
-        <v>0</v>
-      </c>
-      <c r="E209" s="20" t="s">
-        <v>1029</v>
-      </c>
-      <c r="F209" s="21">
-        <v>22.8</v>
-      </c>
-      <c r="G209" s="21">
-        <v>0.36499999999999999</v>
+    <row r="209" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A209" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="B209" s="22" t="s">
+        <v>606</v>
+      </c>
+      <c r="C209" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="D209" s="23">
+        <v>5</v>
+      </c>
+      <c r="E209" s="24" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F209" s="25">
+        <v>21.3</v>
+      </c>
+      <c r="G209" s="25">
+        <v>0.158</v>
       </c>
       <c r="H209" s="15"/>
       <c r="I209" s="15"/>
@@ -13635,27 +13723,27 @@
       <c r="Y209" s="15"/>
       <c r="Z209" s="15"/>
     </row>
-    <row r="210" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="B210" s="22" t="s">
-        <v>608</v>
-      </c>
-      <c r="C210" s="22" t="s">
-        <v>374</v>
-      </c>
-      <c r="D210" s="23">
-        <v>2</v>
-      </c>
-      <c r="E210" s="24" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F210" s="25">
-        <v>13.5</v>
-      </c>
-      <c r="G210" s="25">
-        <v>0.113</v>
+    <row r="210" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A210" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="B210" s="18" t="s">
+        <v>607</v>
+      </c>
+      <c r="C210" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="D210" s="19">
+        <v>0</v>
+      </c>
+      <c r="E210" s="20" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F210" s="21">
+        <v>22.8</v>
+      </c>
+      <c r="G210" s="21">
+        <v>0.36499999999999999</v>
       </c>
       <c r="H210" s="15"/>
       <c r="I210" s="15"/>
@@ -13677,27 +13765,27 @@
       <c r="Y210" s="15"/>
       <c r="Z210" s="15"/>
     </row>
-    <row r="211" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="B211" s="18" t="s">
-        <v>609</v>
-      </c>
-      <c r="C211" s="18" t="s">
-        <v>376</v>
-      </c>
-      <c r="D211" s="19">
-        <v>4</v>
-      </c>
-      <c r="E211" s="20" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F211" s="21">
-        <v>22.8</v>
-      </c>
-      <c r="G211" s="21">
-        <v>0.28499999999999998</v>
+    <row r="211" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="17" t="s">
+        <v>373</v>
+      </c>
+      <c r="B211" s="22" t="s">
+        <v>608</v>
+      </c>
+      <c r="C211" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="D211" s="23">
+        <v>2</v>
+      </c>
+      <c r="E211" s="24" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F211" s="25">
+        <v>13.5</v>
+      </c>
+      <c r="G211" s="25">
+        <v>0.113</v>
       </c>
       <c r="H211" s="15"/>
       <c r="I211" s="15"/>
@@ -13719,29 +13807,27 @@
       <c r="Y211" s="15"/>
       <c r="Z211" s="15"/>
     </row>
-    <row r="212" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="17" t="s">
-        <v>1106</v>
-      </c>
-      <c r="B212" s="22" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C212" s="22" t="s">
-        <v>1108</v>
-      </c>
-      <c r="D212" s="23">
-        <v>2</v>
-      </c>
-      <c r="E212" s="34" t="s">
-        <v>1109</v>
-      </c>
-      <c r="F212" s="25" cm="1">
-        <f t="array" ref="F212">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C212,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.rest,_xlfn.TEXTAFTER(_xlpm.lines," – "),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlpm.rest," ")),_xlpm.unit,TRIM(_xlfn.TEXTAFTER(_xlpm.rest," ")),_xlpm.isml,--(_xlpm.unit="ml"),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$108,'Alcohol by Category'!$E$99:$E$108),0)),_xlpm.amt*_xlpm.abv*_xlpm.isml)),1)</f>
-        <v>24</v>
-      </c>
-      <c r="G212" s="25" cm="1">
-        <f t="array" ref="G212">ROUND(F212/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C212,,CHAR(10)),_xlpm.rest,_xlfn.TEXTAFTER(_xlpm.lines," – "),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlpm.rest," ")),_xlpm.unit,TRIM(_xlfn.TEXTAFTER(_xlpm.rest," ")),_xlpm.isml,--(_xlpm.unit="ml"),_xlpm.amt*_xlpm.isml)),3)</f>
-        <v>9.6000000000000002E-2</v>
+    <row r="212" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A212" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="B212" s="18" t="s">
+        <v>609</v>
+      </c>
+      <c r="C212" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="D212" s="19">
+        <v>4</v>
+      </c>
+      <c r="E212" s="20" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F212" s="21">
+        <v>22.8</v>
+      </c>
+      <c r="G212" s="21">
+        <v>0.28499999999999998</v>
       </c>
       <c r="H212" s="15"/>
       <c r="I212" s="15"/>
@@ -13763,27 +13849,29 @@
       <c r="Y212" s="15"/>
       <c r="Z212" s="15"/>
     </row>
-    <row r="213" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="17" t="s">
-        <v>377</v>
+        <v>1106</v>
       </c>
       <c r="B213" s="22" t="s">
-        <v>610</v>
+        <v>1107</v>
       </c>
       <c r="C213" s="22" t="s">
-        <v>378</v>
+        <v>1108</v>
       </c>
       <c r="D213" s="23">
-        <v>1</v>
-      </c>
-      <c r="E213" s="24" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F213" s="25">
-        <v>36</v>
-      </c>
-      <c r="G213" s="25">
-        <v>0.4</v>
+        <v>2</v>
+      </c>
+      <c r="E213" s="34" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F213" s="25" cm="1">
+        <f t="array" ref="F213">ROUND(SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C213,,CHAR(10)),_xlpm.nm,TRIM(_xlfn.TEXTBEFORE(_xlpm.lines," – ")),_xlpm.rest,_xlfn.TEXTAFTER(_xlpm.lines," – "),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlpm.rest," ")),_xlpm.unit,TRIM(_xlfn.TEXTAFTER(_xlpm.rest," ")),_xlpm.isml,--(_xlpm.unit="ml"),_xlpm.abv,_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$13:$A$95,'Alcohol by Category'!$E$13:$E$95),_xlfn.IFNA(_xlfn.XLOOKUP(_xlpm.nm,'Alcohol by Category'!$A$99:$A$108,'Alcohol by Category'!$E$99:$E$108),0)),_xlpm.amt*_xlpm.abv*_xlpm.isml)),1)</f>
+        <v>24</v>
+      </c>
+      <c r="G213" s="25" cm="1">
+        <f t="array" ref="G213">ROUND(F213/SUM(_xlfn.LET(_xlpm.lines,_xlfn.TEXTSPLIT(C213,,CHAR(10)),_xlpm.rest,_xlfn.TEXTAFTER(_xlpm.lines," – "),_xlpm.amt,VALUE(_xlfn.TEXTBEFORE(_xlpm.rest," ")),_xlpm.unit,TRIM(_xlfn.TEXTAFTER(_xlpm.rest," ")),_xlpm.isml,--(_xlpm.unit="ml"),_xlpm.amt*_xlpm.isml)),3)</f>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H213" s="15"/>
       <c r="I213" s="15"/>
@@ -13805,27 +13893,27 @@
       <c r="Y213" s="15"/>
       <c r="Z213" s="15"/>
     </row>
-    <row r="214" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="16" t="s">
-        <v>379</v>
-      </c>
-      <c r="B214" s="18" t="s">
-        <v>611</v>
-      </c>
-      <c r="C214" s="18" t="s">
-        <v>380</v>
-      </c>
-      <c r="D214" s="19">
-        <v>2</v>
-      </c>
-      <c r="E214" s="20" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F214" s="21">
-        <v>23</v>
-      </c>
-      <c r="G214" s="21">
-        <v>0.184</v>
+    <row r="214" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A214" s="17" t="s">
+        <v>377</v>
+      </c>
+      <c r="B214" s="22" t="s">
+        <v>610</v>
+      </c>
+      <c r="C214" s="22" t="s">
+        <v>378</v>
+      </c>
+      <c r="D214" s="23">
+        <v>1</v>
+      </c>
+      <c r="E214" s="24" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F214" s="25">
+        <v>36</v>
+      </c>
+      <c r="G214" s="25">
+        <v>0.4</v>
       </c>
       <c r="H214" s="15"/>
       <c r="I214" s="15"/>
@@ -13847,27 +13935,27 @@
       <c r="Y214" s="15"/>
       <c r="Z214" s="15"/>
     </row>
-    <row r="215" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="16" t="s">
-        <v>1111</v>
+        <v>379</v>
       </c>
       <c r="B215" s="18" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="C215" s="18" t="s">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="D215" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E215" s="20" t="s">
-        <v>1016</v>
+        <v>1033</v>
       </c>
       <c r="F215" s="21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G215" s="21">
-        <v>0.16</v>
+        <v>0.184</v>
       </c>
       <c r="H215" s="15"/>
       <c r="I215" s="15"/>
@@ -13889,27 +13977,27 @@
       <c r="Y215" s="15"/>
       <c r="Z215" s="15"/>
     </row>
-    <row r="216" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="B216" s="22" t="s">
-        <v>612</v>
-      </c>
-      <c r="C216" s="22" t="s">
-        <v>382</v>
-      </c>
-      <c r="D216" s="23">
-        <v>2</v>
-      </c>
-      <c r="E216" s="24" t="s">
-        <v>1034</v>
-      </c>
-      <c r="F216" s="25">
-        <v>36.1</v>
-      </c>
-      <c r="G216" s="25">
-        <v>0.33700000000000002</v>
+    <row r="216" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="16" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B216" s="18" t="s">
+        <v>594</v>
+      </c>
+      <c r="C216" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="D216" s="19">
+        <v>1</v>
+      </c>
+      <c r="E216" s="20" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F216" s="21">
+        <v>24</v>
+      </c>
+      <c r="G216" s="21">
+        <v>0.16</v>
       </c>
       <c r="H216" s="15"/>
       <c r="I216" s="15"/>
@@ -13932,26 +14020,26 @@
       <c r="Z216" s="15"/>
     </row>
     <row r="217" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="16" t="s">
-        <v>383</v>
-      </c>
-      <c r="B217" s="18" t="s">
-        <v>613</v>
-      </c>
-      <c r="C217" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="D217" s="19">
-        <v>81</v>
-      </c>
-      <c r="E217" s="20" t="s">
-        <v>1035</v>
-      </c>
-      <c r="F217" s="21">
-        <v>18</v>
-      </c>
-      <c r="G217" s="21">
-        <v>0.09</v>
+      <c r="A217" s="17" t="s">
+        <v>381</v>
+      </c>
+      <c r="B217" s="22" t="s">
+        <v>612</v>
+      </c>
+      <c r="C217" s="22" t="s">
+        <v>382</v>
+      </c>
+      <c r="D217" s="23">
+        <v>2</v>
+      </c>
+      <c r="E217" s="24" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F217" s="25">
+        <v>36.1</v>
+      </c>
+      <c r="G217" s="25">
+        <v>0.33700000000000002</v>
       </c>
       <c r="H217" s="15"/>
       <c r="I217" s="15"/>
@@ -13974,26 +14062,26 @@
       <c r="Z217" s="15"/>
     </row>
     <row r="218" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="B218" s="22" t="s">
-        <v>614</v>
-      </c>
-      <c r="C218" s="22" t="s">
-        <v>386</v>
-      </c>
-      <c r="D218" s="23">
-        <v>1</v>
-      </c>
-      <c r="E218" s="24" t="s">
-        <v>1036</v>
-      </c>
-      <c r="F218" s="25">
-        <v>28.5</v>
-      </c>
-      <c r="G218" s="25">
-        <v>0.22800000000000001</v>
+      <c r="A218" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="B218" s="18" t="s">
+        <v>613</v>
+      </c>
+      <c r="C218" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="D218" s="19">
+        <v>81</v>
+      </c>
+      <c r="E218" s="20" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F218" s="21">
+        <v>18</v>
+      </c>
+      <c r="G218" s="21">
+        <v>0.09</v>
       </c>
       <c r="H218" s="15"/>
       <c r="I218" s="15"/>
@@ -14015,27 +14103,27 @@
       <c r="Y218" s="15"/>
       <c r="Z218" s="15"/>
     </row>
-    <row r="219" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="16" t="s">
-        <v>387</v>
-      </c>
-      <c r="B219" s="18" t="s">
-        <v>615</v>
-      </c>
-      <c r="C219" s="18" t="s">
-        <v>388</v>
-      </c>
-      <c r="D219" s="19">
+    <row r="219" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="17" t="s">
+        <v>385</v>
+      </c>
+      <c r="B219" s="22" t="s">
+        <v>614</v>
+      </c>
+      <c r="C219" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="D219" s="23">
         <v>1</v>
       </c>
-      <c r="E219" s="20" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F219" s="21">
-        <v>24</v>
-      </c>
-      <c r="G219" s="21">
-        <v>0.35799999999999998</v>
+      <c r="E219" s="24" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F219" s="25">
+        <v>28.5</v>
+      </c>
+      <c r="G219" s="25">
+        <v>0.22800000000000001</v>
       </c>
       <c r="H219" s="15"/>
       <c r="I219" s="15"/>
@@ -14058,26 +14146,26 @@
       <c r="Z219" s="15"/>
     </row>
     <row r="220" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="17" t="s">
-        <v>389</v>
-      </c>
-      <c r="B220" s="22" t="s">
-        <v>616</v>
-      </c>
-      <c r="C220" s="22" t="s">
-        <v>390</v>
-      </c>
-      <c r="D220" s="23">
+      <c r="A220" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="B220" s="18" t="s">
+        <v>615</v>
+      </c>
+      <c r="C220" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="D220" s="19">
         <v>1</v>
       </c>
-      <c r="E220" s="24" t="s">
-        <v>1038</v>
-      </c>
-      <c r="F220" s="25">
-        <v>18</v>
-      </c>
-      <c r="G220" s="25">
-        <v>9.1999999999999998E-2</v>
+      <c r="E220" s="20" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F220" s="21">
+        <v>24</v>
+      </c>
+      <c r="G220" s="21">
+        <v>0.35799999999999998</v>
       </c>
       <c r="H220" s="15"/>
       <c r="I220" s="15"/>
@@ -14099,27 +14187,27 @@
       <c r="Y220" s="15"/>
       <c r="Z220" s="15"/>
     </row>
-    <row r="221" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="16" t="s">
-        <v>391</v>
-      </c>
-      <c r="B221" s="18" t="s">
-        <v>617</v>
-      </c>
-      <c r="C221" s="18" t="s">
-        <v>392</v>
-      </c>
-      <c r="D221" s="19">
-        <v>7</v>
-      </c>
-      <c r="E221" s="20" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F221" s="21">
-        <v>24</v>
-      </c>
-      <c r="G221" s="21">
-        <v>0.26700000000000002</v>
+    <row r="221" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="B221" s="22" t="s">
+        <v>616</v>
+      </c>
+      <c r="C221" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="D221" s="23">
+        <v>1</v>
+      </c>
+      <c r="E221" s="24" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F221" s="25">
+        <v>18</v>
+      </c>
+      <c r="G221" s="25">
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="H221" s="15"/>
       <c r="I221" s="15"/>
@@ -14141,27 +14229,27 @@
       <c r="Y221" s="15"/>
       <c r="Z221" s="15"/>
     </row>
-    <row r="222" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="17" t="s">
-        <v>393</v>
-      </c>
-      <c r="B222" s="22" t="s">
-        <v>618</v>
-      </c>
-      <c r="C222" s="22" t="s">
-        <v>394</v>
-      </c>
-      <c r="D222" s="23">
-        <v>1</v>
-      </c>
-      <c r="E222" s="24" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F222" s="25">
-        <v>21.8</v>
-      </c>
-      <c r="G222" s="25">
-        <v>0.24199999999999999</v>
+    <row r="222" spans="1:26" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A222" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="B222" s="18" t="s">
+        <v>617</v>
+      </c>
+      <c r="C222" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="D222" s="19">
+        <v>7</v>
+      </c>
+      <c r="E222" s="20" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F222" s="21">
+        <v>24</v>
+      </c>
+      <c r="G222" s="21">
+        <v>0.26700000000000002</v>
       </c>
       <c r="H222" s="15"/>
       <c r="I222" s="15"/>
@@ -14184,26 +14272,26 @@
       <c r="Z222" s="15"/>
     </row>
     <row r="223" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="16" t="s">
-        <v>395</v>
-      </c>
-      <c r="B223" s="18" t="s">
-        <v>619</v>
-      </c>
-      <c r="C223" s="18" t="s">
-        <v>396</v>
-      </c>
-      <c r="D223" s="19">
-        <v>2</v>
-      </c>
-      <c r="E223" s="20" t="s">
-        <v>1041</v>
-      </c>
-      <c r="F223" s="21">
-        <v>38.6</v>
-      </c>
-      <c r="G223" s="21">
-        <v>0.36799999999999999</v>
+      <c r="A223" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="B223" s="22" t="s">
+        <v>618</v>
+      </c>
+      <c r="C223" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="D223" s="23">
+        <v>1</v>
+      </c>
+      <c r="E223" s="24" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F223" s="25">
+        <v>21.8</v>
+      </c>
+      <c r="G223" s="25">
+        <v>0.24199999999999999</v>
       </c>
       <c r="H223" s="15"/>
       <c r="I223" s="15"/>
@@ -14225,27 +14313,27 @@
       <c r="Y223" s="15"/>
       <c r="Z223" s="15"/>
     </row>
-    <row r="224" spans="1:26" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="17" t="s">
-        <v>397</v>
-      </c>
-      <c r="B224" s="22" t="s">
-        <v>620</v>
-      </c>
-      <c r="C224" s="22" t="s">
-        <v>398</v>
-      </c>
-      <c r="D224" s="23">
+    <row r="224" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="B224" s="18" t="s">
+        <v>619</v>
+      </c>
+      <c r="C224" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="D224" s="19">
         <v>2</v>
       </c>
-      <c r="E224" s="24" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F224" s="25">
-        <v>30.8</v>
-      </c>
-      <c r="G224" s="25">
-        <v>0.32400000000000001</v>
+      <c r="E224" s="20" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F224" s="21">
+        <v>38.6</v>
+      </c>
+      <c r="G224" s="21">
+        <v>0.36799999999999999</v>
       </c>
       <c r="H224" s="15"/>
       <c r="I224" s="15"/>
@@ -14267,27 +14355,27 @@
       <c r="Y224" s="15"/>
       <c r="Z224" s="15"/>
     </row>
-    <row r="225" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="16" t="s">
-        <v>399</v>
-      </c>
-      <c r="B225" s="18" t="s">
-        <v>621</v>
-      </c>
-      <c r="C225" s="18" t="s">
-        <v>400</v>
-      </c>
-      <c r="D225" s="19">
+    <row r="225" spans="1:26" ht="105.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="B225" s="22" t="s">
+        <v>620</v>
+      </c>
+      <c r="C225" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="D225" s="23">
         <v>2</v>
       </c>
-      <c r="E225" s="20" t="s">
-        <v>1043</v>
-      </c>
-      <c r="F225" s="21">
-        <v>24</v>
-      </c>
-      <c r="G225" s="21">
-        <v>0.218</v>
+      <c r="E225" s="24" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F225" s="25">
+        <v>30.8</v>
+      </c>
+      <c r="G225" s="25">
+        <v>0.32400000000000001</v>
       </c>
       <c r="H225" s="15"/>
       <c r="I225" s="15"/>
@@ -14309,27 +14397,27 @@
       <c r="Y225" s="15"/>
       <c r="Z225" s="15"/>
     </row>
-    <row r="226" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="17" t="s">
-        <v>401</v>
-      </c>
-      <c r="B226" s="22" t="s">
-        <v>622</v>
-      </c>
-      <c r="C226" s="22" t="s">
-        <v>402</v>
-      </c>
-      <c r="D226" s="23">
-        <v>0</v>
-      </c>
-      <c r="E226" s="24" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F226" s="25">
-        <v>33.6</v>
-      </c>
-      <c r="G226" s="25">
-        <v>0.35399999999999998</v>
+    <row r="226" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="B226" s="18" t="s">
+        <v>621</v>
+      </c>
+      <c r="C226" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="D226" s="19">
+        <v>2</v>
+      </c>
+      <c r="E226" s="20" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F226" s="21">
+        <v>24</v>
+      </c>
+      <c r="G226" s="21">
+        <v>0.218</v>
       </c>
       <c r="H226" s="15"/>
       <c r="I226" s="15"/>
@@ -14351,27 +14439,27 @@
       <c r="Y226" s="15"/>
       <c r="Z226" s="15"/>
     </row>
-    <row r="227" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="16" t="s">
-        <v>403</v>
-      </c>
-      <c r="B227" s="18" t="s">
-        <v>623</v>
-      </c>
-      <c r="C227" s="18" t="s">
-        <v>404</v>
-      </c>
-      <c r="D227" s="19">
-        <v>4</v>
-      </c>
-      <c r="E227" s="20" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F227" s="21">
-        <v>24</v>
-      </c>
-      <c r="G227" s="21">
-        <v>0.214</v>
+    <row r="227" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="17" t="s">
+        <v>401</v>
+      </c>
+      <c r="B227" s="22" t="s">
+        <v>622</v>
+      </c>
+      <c r="C227" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="D227" s="23">
+        <v>0</v>
+      </c>
+      <c r="E227" s="24" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F227" s="25">
+        <v>33.6</v>
+      </c>
+      <c r="G227" s="25">
+        <v>0.35399999999999998</v>
       </c>
       <c r="H227" s="15"/>
       <c r="I227" s="15"/>
@@ -14394,26 +14482,26 @@
       <c r="Z227" s="15"/>
     </row>
     <row r="228" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="17" t="s">
-        <v>405</v>
-      </c>
-      <c r="B228" s="22" t="s">
-        <v>624</v>
-      </c>
-      <c r="C228" s="22" t="s">
-        <v>406</v>
-      </c>
-      <c r="D228" s="23">
+      <c r="A228" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="B228" s="18" t="s">
+        <v>623</v>
+      </c>
+      <c r="C228" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="D228" s="19">
         <v>4</v>
       </c>
-      <c r="E228" s="24" t="s">
-        <v>1046</v>
-      </c>
-      <c r="F228" s="25">
-        <v>18</v>
-      </c>
-      <c r="G228" s="25">
-        <v>0.09</v>
+      <c r="E228" s="20" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F228" s="21">
+        <v>24</v>
+      </c>
+      <c r="G228" s="21">
+        <v>0.214</v>
       </c>
       <c r="H228" s="15"/>
       <c r="I228" s="15"/>
@@ -14435,27 +14523,27 @@
       <c r="Y228" s="15"/>
       <c r="Z228" s="15"/>
     </row>
-    <row r="229" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="16" t="s">
-        <v>407</v>
-      </c>
-      <c r="B229" s="18" t="s">
-        <v>625</v>
-      </c>
-      <c r="C229" s="18" t="s">
-        <v>408</v>
-      </c>
-      <c r="D229" s="19">
-        <v>23</v>
-      </c>
-      <c r="E229" s="20" t="s">
-        <v>1047</v>
-      </c>
-      <c r="F229" s="21">
-        <v>24</v>
-      </c>
-      <c r="G229" s="21">
-        <v>0.253</v>
+    <row r="229" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="B229" s="22" t="s">
+        <v>624</v>
+      </c>
+      <c r="C229" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="D229" s="23">
+        <v>4</v>
+      </c>
+      <c r="E229" s="24" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F229" s="25">
+        <v>18</v>
+      </c>
+      <c r="G229" s="25">
+        <v>0.09</v>
       </c>
       <c r="H229" s="15"/>
       <c r="I229" s="15"/>
@@ -14477,27 +14565,27 @@
       <c r="Y229" s="15"/>
       <c r="Z229" s="15"/>
     </row>
-    <row r="230" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="B230" s="22" t="s">
-        <v>626</v>
-      </c>
-      <c r="C230" s="22" t="s">
-        <v>410</v>
-      </c>
-      <c r="D230" s="23">
-        <v>22</v>
-      </c>
-      <c r="E230" s="24" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F230" s="25">
+    <row r="230" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="B230" s="18" t="s">
+        <v>625</v>
+      </c>
+      <c r="C230" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="D230" s="19">
+        <v>23</v>
+      </c>
+      <c r="E230" s="20" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F230" s="21">
         <v>24</v>
       </c>
-      <c r="G230" s="25">
-        <v>0.24</v>
+      <c r="G230" s="21">
+        <v>0.253</v>
       </c>
       <c r="H230" s="15"/>
       <c r="I230" s="15"/>
@@ -14519,26 +14607,26 @@
       <c r="Y230" s="15"/>
       <c r="Z230" s="15"/>
     </row>
-    <row r="231" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="16" t="s">
-        <v>413</v>
-      </c>
-      <c r="B231" s="18" t="s">
-        <v>627</v>
-      </c>
-      <c r="C231" s="18" t="s">
-        <v>414</v>
-      </c>
-      <c r="D231" s="19">
-        <v>6</v>
-      </c>
-      <c r="E231" s="20" t="s">
-        <v>1049</v>
-      </c>
-      <c r="F231" s="21">
-        <v>21.6</v>
-      </c>
-      <c r="G231" s="21">
+    <row r="231" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="B231" s="22" t="s">
+        <v>626</v>
+      </c>
+      <c r="C231" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="D231" s="23">
+        <v>22</v>
+      </c>
+      <c r="E231" s="24" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F231" s="25">
+        <v>24</v>
+      </c>
+      <c r="G231" s="25">
         <v>0.24</v>
       </c>
       <c r="H231" s="15"/>
@@ -14561,27 +14649,27 @@
       <c r="Y231" s="15"/>
       <c r="Z231" s="15"/>
     </row>
-    <row r="232" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="17" t="s">
-        <v>411</v>
-      </c>
-      <c r="B232" s="22" t="s">
-        <v>628</v>
-      </c>
-      <c r="C232" s="22" t="s">
-        <v>412</v>
-      </c>
-      <c r="D232" s="23">
-        <v>2</v>
-      </c>
-      <c r="E232" s="24" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F232" s="25">
-        <v>21.9</v>
-      </c>
-      <c r="G232" s="25">
-        <v>0.24299999999999999</v>
+    <row r="232" spans="1:26" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="B232" s="18" t="s">
+        <v>627</v>
+      </c>
+      <c r="C232" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="D232" s="19">
+        <v>6</v>
+      </c>
+      <c r="E232" s="20" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F232" s="21">
+        <v>21.6</v>
+      </c>
+      <c r="G232" s="21">
+        <v>0.24</v>
       </c>
       <c r="H232" s="15"/>
       <c r="I232" s="15"/>
@@ -14604,26 +14692,26 @@
       <c r="Z232" s="15"/>
     </row>
     <row r="233" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="16" t="s">
-        <v>415</v>
-      </c>
-      <c r="B233" s="18" t="s">
-        <v>629</v>
-      </c>
-      <c r="C233" s="18" t="s">
-        <v>122</v>
-      </c>
-      <c r="D233" s="19">
-        <v>14</v>
-      </c>
-      <c r="E233" s="20" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F233" s="21">
-        <v>18</v>
-      </c>
-      <c r="G233" s="21">
-        <v>0.2</v>
+      <c r="A233" s="17" t="s">
+        <v>411</v>
+      </c>
+      <c r="B233" s="22" t="s">
+        <v>628</v>
+      </c>
+      <c r="C233" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="D233" s="23">
+        <v>2</v>
+      </c>
+      <c r="E233" s="24" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F233" s="25">
+        <v>21.9</v>
+      </c>
+      <c r="G233" s="25">
+        <v>0.24299999999999999</v>
       </c>
       <c r="H233" s="15"/>
       <c r="I233" s="15"/>
@@ -14645,27 +14733,27 @@
       <c r="Y233" s="15"/>
       <c r="Z233" s="15"/>
     </row>
-    <row r="234" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="17" t="s">
-        <v>416</v>
-      </c>
-      <c r="B234" s="22" t="s">
-        <v>630</v>
-      </c>
-      <c r="C234" s="22" t="s">
-        <v>417</v>
-      </c>
-      <c r="D234" s="23">
-        <v>2</v>
-      </c>
-      <c r="E234" s="24" t="s">
-        <v>1052</v>
-      </c>
-      <c r="F234" s="25">
-        <v>22.8</v>
-      </c>
-      <c r="G234" s="25">
-        <v>0.26800000000000002</v>
+    <row r="234" spans="1:26" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A234" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="B234" s="18" t="s">
+        <v>629</v>
+      </c>
+      <c r="C234" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="D234" s="19">
+        <v>14</v>
+      </c>
+      <c r="E234" s="20" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F234" s="21">
+        <v>18</v>
+      </c>
+      <c r="G234" s="21">
+        <v>0.2</v>
       </c>
       <c r="H234" s="15"/>
       <c r="I234" s="15"/>
@@ -14688,26 +14776,26 @@
       <c r="Z234" s="15"/>
     </row>
     <row r="235" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="31" t="s">
-        <v>418</v>
-      </c>
-      <c r="B235" s="32" t="s">
-        <v>631</v>
-      </c>
-      <c r="C235" s="32" t="s">
-        <v>419</v>
-      </c>
-      <c r="D235" s="33">
+      <c r="A235" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="B235" s="22" t="s">
+        <v>630</v>
+      </c>
+      <c r="C235" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="D235" s="23">
         <v>2</v>
       </c>
-      <c r="E235" s="32" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F235" s="21">
-        <v>28.9</v>
-      </c>
-      <c r="G235" s="21">
-        <v>0.32100000000000001</v>
+      <c r="E235" s="24" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F235" s="25">
+        <v>22.8</v>
+      </c>
+      <c r="G235" s="25">
+        <v>0.26800000000000002</v>
       </c>
       <c r="H235" s="15"/>
       <c r="I235" s="15"/>
@@ -14729,14 +14817,28 @@
       <c r="Y235" s="15"/>
       <c r="Z235" s="15"/>
     </row>
-    <row r="236" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="15"/>
-      <c r="B236" s="15"/>
-      <c r="C236" s="15"/>
-      <c r="D236" s="15"/>
-      <c r="E236" s="15"/>
-      <c r="F236" s="15"/>
-      <c r="G236" s="15"/>
+    <row r="236" spans="1:26" ht="75.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A236" s="31" t="s">
+        <v>418</v>
+      </c>
+      <c r="B236" s="32" t="s">
+        <v>631</v>
+      </c>
+      <c r="C236" s="32" t="s">
+        <v>419</v>
+      </c>
+      <c r="D236" s="33">
+        <v>2</v>
+      </c>
+      <c r="E236" s="32" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F236" s="21">
+        <v>28.9</v>
+      </c>
+      <c r="G236" s="21">
+        <v>0.32100000000000001</v>
+      </c>
       <c r="H236" s="15"/>
       <c r="I236" s="15"/>
       <c r="J236" s="15"/>
@@ -36261,12 +36363,41 @@
       <c r="Y1004" s="15"/>
       <c r="Z1004" s="15"/>
     </row>
+    <row r="1005" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1005" s="15"/>
+      <c r="B1005" s="15"/>
+      <c r="C1005" s="15"/>
+      <c r="D1005" s="15"/>
+      <c r="E1005" s="15"/>
+      <c r="F1005" s="15"/>
+      <c r="G1005" s="15"/>
+      <c r="H1005" s="15"/>
+      <c r="I1005" s="15"/>
+      <c r="J1005" s="15"/>
+      <c r="K1005" s="15"/>
+      <c r="L1005" s="15"/>
+      <c r="M1005" s="15"/>
+      <c r="N1005" s="15"/>
+      <c r="O1005" s="15"/>
+      <c r="P1005" s="15"/>
+      <c r="Q1005" s="15"/>
+      <c r="R1005" s="15"/>
+      <c r="S1005" s="15"/>
+      <c r="T1005" s="15"/>
+      <c r="U1005" s="15"/>
+      <c r="V1005" s="15"/>
+      <c r="W1005" s="15"/>
+      <c r="X1005" s="15"/>
+      <c r="Y1005" s="15"/>
+      <c r="Z1005" s="15"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z235">
-    <sortCondition ref="A2:A235"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Z236">
+    <sortCondition ref="A2:A236"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
